--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="UIText" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="182">
   <si>
     <t>id</t>
   </si>
@@ -470,6 +470,12 @@
     <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
   </si>
   <si>
+    <t>通用</t>
+  </si>
+  <si>
+    <t>魔王专属</t>
+  </si>
+  <si>
     <t>弹窗</t>
   </si>
   <si>
@@ -540,6 +546,15 @@
   </si>
   <si>
     <t>排序：名字</t>
+  </si>
+  <si>
+    <t>稀有度:{0}</t>
+  </si>
+  <si>
+    <t>所属:{0}</t>
+  </si>
+  <si>
+    <t>道具名字:{0}</t>
   </si>
   <si>
     <t>没有足够的魔晶</t>
@@ -1525,7 +1540,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D264"/>
+  <dimension ref="A1:D269"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -3270,26 +3285,26 @@
         <v>13</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" customFormat="1" spans="1:4">
       <c r="A125">
-        <v>1000001</v>
+        <v>90001</v>
       </c>
       <c r="B125">
-        <v>1000001</v>
+        <v>90001</v>
       </c>
       <c r="C125" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D125" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" customFormat="1" spans="1:4">
       <c r="A126">
-        <v>1000002</v>
+        <v>90002</v>
       </c>
       <c r="B126">
-        <v>1000002</v>
+        <v>90002</v>
       </c>
       <c r="C126" t="s">
         <v>148</v>
@@ -3300,69 +3315,69 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127">
-        <v>1001001</v>
+        <v>1000001</v>
       </c>
       <c r="B127">
-        <v>1001001</v>
+        <v>1000001</v>
       </c>
       <c r="C127" t="s">
+        <v>132</v>
+      </c>
+      <c r="D127" t="s">
         <v>149</v>
       </c>
-      <c r="D127" t="s">
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128">
+        <v>1000002</v>
+      </c>
+      <c r="B128">
+        <v>1000002</v>
+      </c>
+      <c r="C128" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="128" ht="12" customHeight="1" spans="1:4">
-      <c r="A128">
-        <v>1002001</v>
-      </c>
-      <c r="B128">
-        <v>1002001</v>
-      </c>
-      <c r="C128" t="s">
-        <v>151</v>
-      </c>
       <c r="D128" t="s">
-        <v>152</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129">
-        <v>1002002</v>
+        <v>1001001</v>
       </c>
       <c r="B129">
-        <v>1002002</v>
+        <v>1001001</v>
       </c>
       <c r="C129" t="s">
+        <v>151</v>
+      </c>
+      <c r="D129" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="130" ht="12" customHeight="1" spans="1:4">
+      <c r="A130">
+        <v>1002001</v>
+      </c>
+      <c r="B130">
+        <v>1002001</v>
+      </c>
+      <c r="C130" t="s">
         <v>153</v>
       </c>
-      <c r="D129" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4">
-      <c r="A130">
-        <v>1003001</v>
-      </c>
-      <c r="B130">
-        <v>1003001</v>
-      </c>
-      <c r="C130" t="s">
+      <c r="D130" t="s">
         <v>154</v>
-      </c>
-      <c r="D130" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131">
-        <v>1003002</v>
+        <v>1002002</v>
       </c>
       <c r="B131">
-        <v>1003002</v>
+        <v>1002002</v>
       </c>
       <c r="C131" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D131" t="s">
         <v>13</v>
@@ -3370,27 +3385,27 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132">
-        <v>1004001</v>
+        <v>1003001</v>
       </c>
       <c r="B132">
-        <v>1004001</v>
+        <v>1003001</v>
       </c>
       <c r="C132" t="s">
+        <v>156</v>
+      </c>
+      <c r="D132" t="s">
         <v>157</v>
-      </c>
-      <c r="D132" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133">
-        <v>1004002</v>
+        <v>1003002</v>
       </c>
       <c r="B133">
-        <v>1004002</v>
+        <v>1003002</v>
       </c>
       <c r="C133" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="D133" t="s">
         <v>13</v>
@@ -3398,10 +3413,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134">
-        <v>1005001</v>
+        <v>1004001</v>
       </c>
       <c r="B134">
-        <v>1005001</v>
+        <v>1004001</v>
       </c>
       <c r="C134" t="s">
         <v>159</v>
@@ -3412,13 +3427,13 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135">
-        <v>1005002</v>
+        <v>1004002</v>
       </c>
       <c r="B135">
-        <v>1005002</v>
+        <v>1004002</v>
       </c>
       <c r="C135" t="s">
-        <v>161</v>
+        <v>31</v>
       </c>
       <c r="D135" t="s">
         <v>13</v>
@@ -3426,41 +3441,41 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136">
-        <v>1005003</v>
+        <v>1005001</v>
       </c>
       <c r="B136">
-        <v>1005003</v>
+        <v>1005001</v>
       </c>
       <c r="C136" t="s">
+        <v>161</v>
+      </c>
+      <c r="D136" t="s">
         <v>162</v>
-      </c>
-      <c r="D136" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137">
-        <v>2000001</v>
+        <v>1005002</v>
       </c>
       <c r="B137">
-        <v>2000001</v>
+        <v>1005002</v>
       </c>
       <c r="C137" t="s">
         <v>163</v>
       </c>
       <c r="D137" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138">
-        <v>2000002</v>
+        <v>1005003</v>
       </c>
       <c r="B138">
-        <v>2000002</v>
+        <v>1005003</v>
       </c>
       <c r="C138" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D138" t="s">
         <v>13</v>
@@ -3468,24 +3483,24 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139">
-        <v>2000003</v>
+        <v>2000001</v>
       </c>
       <c r="B139">
-        <v>2000003</v>
+        <v>2000001</v>
       </c>
       <c r="C139" t="s">
+        <v>165</v>
+      </c>
+      <c r="D139" t="s">
         <v>166</v>
-      </c>
-      <c r="D139" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140">
-        <v>2000004</v>
+        <v>2000002</v>
       </c>
       <c r="B140">
-        <v>2000004</v>
+        <v>2000002</v>
       </c>
       <c r="C140" t="s">
         <v>167</v>
@@ -3496,10 +3511,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141">
-        <v>2000005</v>
+        <v>2000003</v>
       </c>
       <c r="B141">
-        <v>2000005</v>
+        <v>2000003</v>
       </c>
       <c r="C141" t="s">
         <v>168</v>
@@ -3510,10 +3525,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="B142">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="C142" t="s">
         <v>169</v>
@@ -3524,10 +3539,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143">
-        <v>2000007</v>
+        <v>2000005</v>
       </c>
       <c r="B143">
-        <v>2000007</v>
+        <v>2000005</v>
       </c>
       <c r="C143" t="s">
         <v>170</v>
@@ -3536,29 +3551,29 @@
         <v>13</v>
       </c>
     </row>
-    <row r="144" ht="12" customHeight="1" spans="1:4">
+    <row r="144" spans="1:4">
       <c r="A144">
-        <v>3000001</v>
+        <v>2000006</v>
       </c>
       <c r="B144">
-        <v>3000001</v>
+        <v>2000006</v>
       </c>
       <c r="C144" t="s">
         <v>171</v>
       </c>
       <c r="D144" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145">
-        <v>3000002</v>
+        <v>2000007</v>
       </c>
       <c r="B145">
-        <v>3000002</v>
+        <v>2000007</v>
       </c>
       <c r="C145" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D145" t="s">
         <v>13</v>
@@ -3566,13 +3581,13 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146">
-        <v>3000003</v>
+        <v>2000008</v>
       </c>
       <c r="B146">
-        <v>3000003</v>
+        <v>2000008</v>
       </c>
       <c r="C146" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D146" t="s">
         <v>13</v>
@@ -3580,13 +3595,13 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147">
-        <v>3000004</v>
+        <v>2000009</v>
       </c>
       <c r="B147">
-        <v>3000004</v>
+        <v>2000009</v>
       </c>
       <c r="C147" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D147" t="s">
         <v>13</v>
@@ -3594,23 +3609,88 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148">
+        <v>2000010</v>
+      </c>
+      <c r="B148">
+        <v>2000010</v>
+      </c>
+      <c r="C148" t="s">
+        <v>175</v>
+      </c>
+      <c r="D148" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="149" ht="12" customHeight="1" spans="1:4">
+      <c r="A149">
+        <v>3000001</v>
+      </c>
+      <c r="B149">
+        <v>3000001</v>
+      </c>
+      <c r="C149" t="s">
+        <v>176</v>
+      </c>
+      <c r="D149" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150">
+        <v>3000002</v>
+      </c>
+      <c r="B150">
+        <v>3000002</v>
+      </c>
+      <c r="C150" t="s">
+        <v>178</v>
+      </c>
+      <c r="D150" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151">
+        <v>3000003</v>
+      </c>
+      <c r="B151">
+        <v>3000003</v>
+      </c>
+      <c r="C151" t="s">
+        <v>179</v>
+      </c>
+      <c r="D151" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152">
+        <v>3000004</v>
+      </c>
+      <c r="B152">
+        <v>3000004</v>
+      </c>
+      <c r="C152" t="s">
+        <v>180</v>
+      </c>
+      <c r="D152" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153">
         <v>3000005</v>
       </c>
-      <c r="B148">
+      <c r="B153">
         <v>3000005</v>
       </c>
-      <c r="C148" t="s">
-        <v>176</v>
-      </c>
-      <c r="D148" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="177" ht="12" customHeight="1"/>
-    <row r="178" ht="12" customHeight="1"/>
-    <row r="179" ht="12" customHeight="1"/>
-    <row r="180" ht="12" customHeight="1"/>
-    <row r="181" ht="12" customHeight="1"/>
+      <c r="C153" t="s">
+        <v>181</v>
+      </c>
+      <c r="D153" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="182" ht="12" customHeight="1"/>
     <row r="183" ht="12" customHeight="1"/>
     <row r="184" ht="12" customHeight="1"/>
@@ -3641,9 +3721,14 @@
     <row r="209" ht="12" customHeight="1"/>
     <row r="210" ht="12" customHeight="1"/>
     <row r="211" ht="12" customHeight="1"/>
-    <row r="212" customHeight="1"/>
-    <row r="263" ht="12" customHeight="1"/>
-    <row r="264" ht="12" customHeight="1"/>
+    <row r="212" ht="12" customHeight="1"/>
+    <row r="213" ht="12" customHeight="1"/>
+    <row r="214" ht="12" customHeight="1"/>
+    <row r="215" ht="12" customHeight="1"/>
+    <row r="216" ht="12" customHeight="1"/>
+    <row r="217" customHeight="1"/>
+    <row r="268" ht="12" customHeight="1"/>
+    <row r="269" ht="12" customHeight="1"/>
   </sheetData>
   <sortState ref="A4:D88">
     <sortCondition ref="A4"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="UIText" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="183">
   <si>
     <t>id</t>
   </si>
@@ -384,6 +384,9 @@
   </si>
   <si>
     <t>是否提交议案《{0}》？</t>
+  </si>
+  <si>
+    <t>没有可孕育的生物</t>
   </si>
   <si>
     <t>献祭升级</t>
@@ -1540,7 +1543,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D269"/>
+  <dimension ref="A1:D270"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -2951,38 +2954,38 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101">
-        <v>60000</v>
+        <v>54001</v>
       </c>
       <c r="B101">
-        <v>60000</v>
+        <v>54001</v>
       </c>
       <c r="C101" t="s">
         <v>119</v>
       </c>
       <c r="D101" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102">
-        <v>60001</v>
+        <v>60000</v>
       </c>
       <c r="B102">
-        <v>60001</v>
+        <v>60000</v>
       </c>
       <c r="C102" t="s">
+        <v>120</v>
+      </c>
+      <c r="D102" t="s">
         <v>121</v>
-      </c>
-      <c r="D102" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103">
-        <v>60002</v>
+        <v>60001</v>
       </c>
       <c r="B103">
-        <v>60002</v>
+        <v>60001</v>
       </c>
       <c r="C103" t="s">
         <v>122</v>
@@ -2993,10 +2996,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104">
-        <v>61001</v>
+        <v>60002</v>
       </c>
       <c r="B104">
-        <v>61001</v>
+        <v>60002</v>
       </c>
       <c r="C104" t="s">
         <v>123</v>
@@ -3007,10 +3010,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105">
-        <v>61002</v>
+        <v>61001</v>
       </c>
       <c r="B105">
-        <v>61002</v>
+        <v>61001</v>
       </c>
       <c r="C105" t="s">
         <v>124</v>
@@ -3021,10 +3024,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106">
-        <v>61003</v>
+        <v>61002</v>
       </c>
       <c r="B106">
-        <v>61003</v>
+        <v>61002</v>
       </c>
       <c r="C106" t="s">
         <v>125</v>
@@ -3035,38 +3038,38 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107">
-        <v>62001</v>
+        <v>61003</v>
       </c>
       <c r="B107">
-        <v>62001</v>
+        <v>61003</v>
       </c>
       <c r="C107" t="s">
         <v>126</v>
       </c>
       <c r="D107" t="s">
-        <v>127</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108">
-        <v>62002</v>
+        <v>62001</v>
       </c>
       <c r="B108">
-        <v>62002</v>
+        <v>62001</v>
       </c>
       <c r="C108" t="s">
+        <v>127</v>
+      </c>
+      <c r="D108" t="s">
         <v>128</v>
-      </c>
-      <c r="D108" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109">
-        <v>62003</v>
+        <v>62002</v>
       </c>
       <c r="B109">
-        <v>62003</v>
+        <v>62002</v>
       </c>
       <c r="C109" t="s">
         <v>129</v>
@@ -3077,13 +3080,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110">
-        <v>62004</v>
+        <v>62003</v>
       </c>
       <c r="B110">
-        <v>62004</v>
+        <v>62003</v>
       </c>
       <c r="C110" t="s">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="D110" t="s">
         <v>13</v>
@@ -3091,38 +3094,38 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111">
-        <v>63001</v>
+        <v>62004</v>
       </c>
       <c r="B111">
-        <v>63001</v>
+        <v>62004</v>
       </c>
       <c r="C111" t="s">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="D111" t="s">
-        <v>131</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112">
-        <v>63002</v>
+        <v>63001</v>
       </c>
       <c r="B112">
-        <v>63002</v>
+        <v>63001</v>
       </c>
       <c r="C112" t="s">
+        <v>131</v>
+      </c>
+      <c r="D112" t="s">
         <v>132</v>
-      </c>
-      <c r="D112" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113">
-        <v>63003</v>
+        <v>63002</v>
       </c>
       <c r="B113">
-        <v>63003</v>
+        <v>63002</v>
       </c>
       <c r="C113" t="s">
         <v>133</v>
@@ -3133,52 +3136,52 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114">
-        <v>70001</v>
+        <v>63003</v>
       </c>
       <c r="B114">
-        <v>70001</v>
+        <v>63003</v>
       </c>
       <c r="C114" t="s">
         <v>134</v>
       </c>
       <c r="D114" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115">
+        <v>70001</v>
+      </c>
+      <c r="B115">
+        <v>70001</v>
+      </c>
+      <c r="C115" t="s">
+        <v>135</v>
+      </c>
+      <c r="D115" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116">
         <v>80001</v>
       </c>
-      <c r="B115">
+      <c r="B116">
         <v>80001</v>
       </c>
-      <c r="C115" t="s">
-        <v>136</v>
-      </c>
-      <c r="D115" t="s">
+      <c r="C116" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="116" customFormat="1" spans="1:4">
-      <c r="A116">
-        <v>80002</v>
-      </c>
-      <c r="B116">
-        <v>80002</v>
-      </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
         <v>138</v>
-      </c>
-      <c r="D116" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="117" customFormat="1" spans="1:4">
       <c r="A117">
-        <v>80003</v>
+        <v>80002</v>
       </c>
       <c r="B117">
-        <v>80003</v>
+        <v>80002</v>
       </c>
       <c r="C117" t="s">
         <v>139</v>
@@ -3189,10 +3192,10 @@
     </row>
     <row r="118" customFormat="1" spans="1:4">
       <c r="A118">
-        <v>80004</v>
+        <v>80003</v>
       </c>
       <c r="B118">
-        <v>80004</v>
+        <v>80003</v>
       </c>
       <c r="C118" t="s">
         <v>140</v>
@@ -3203,10 +3206,10 @@
     </row>
     <row r="119" customFormat="1" spans="1:4">
       <c r="A119">
-        <v>80005</v>
+        <v>80004</v>
       </c>
       <c r="B119">
-        <v>80005</v>
+        <v>80004</v>
       </c>
       <c r="C119" t="s">
         <v>141</v>
@@ -3217,10 +3220,10 @@
     </row>
     <row r="120" customFormat="1" spans="1:4">
       <c r="A120">
-        <v>80006</v>
+        <v>80005</v>
       </c>
       <c r="B120">
-        <v>80006</v>
+        <v>80005</v>
       </c>
       <c r="C120" t="s">
         <v>142</v>
@@ -3231,10 +3234,10 @@
     </row>
     <row r="121" customFormat="1" spans="1:4">
       <c r="A121">
-        <v>80007</v>
+        <v>80006</v>
       </c>
       <c r="B121">
-        <v>80007</v>
+        <v>80006</v>
       </c>
       <c r="C121" t="s">
         <v>143</v>
@@ -3245,10 +3248,10 @@
     </row>
     <row r="122" customFormat="1" spans="1:4">
       <c r="A122">
-        <v>80008</v>
+        <v>80007</v>
       </c>
       <c r="B122">
-        <v>80008</v>
+        <v>80007</v>
       </c>
       <c r="C122" t="s">
         <v>144</v>
@@ -3259,10 +3262,10 @@
     </row>
     <row r="123" customFormat="1" spans="1:4">
       <c r="A123">
-        <v>80009</v>
+        <v>80008</v>
       </c>
       <c r="B123">
-        <v>80009</v>
+        <v>80008</v>
       </c>
       <c r="C123" t="s">
         <v>145</v>
@@ -3273,10 +3276,10 @@
     </row>
     <row r="124" customFormat="1" spans="1:4">
       <c r="A124">
-        <v>80010</v>
+        <v>80009</v>
       </c>
       <c r="B124">
-        <v>80010</v>
+        <v>80009</v>
       </c>
       <c r="C124" t="s">
         <v>146</v>
@@ -3287,192 +3290,192 @@
     </row>
     <row r="125" customFormat="1" spans="1:4">
       <c r="A125">
-        <v>90001</v>
+        <v>80010</v>
       </c>
       <c r="B125">
-        <v>90001</v>
+        <v>80010</v>
       </c>
       <c r="C125" t="s">
         <v>147</v>
       </c>
       <c r="D125" t="s">
-        <v>147</v>
+        <v>13</v>
       </c>
     </row>
     <row r="126" customFormat="1" spans="1:4">
       <c r="A126">
-        <v>90002</v>
+        <v>90001</v>
       </c>
       <c r="B126">
-        <v>90002</v>
+        <v>90001</v>
       </c>
       <c r="C126" t="s">
         <v>148</v>
       </c>
       <c r="D126" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="127" customFormat="1" spans="1:4">
       <c r="A127">
-        <v>1000001</v>
+        <v>90002</v>
       </c>
       <c r="B127">
-        <v>1000001</v>
+        <v>90002</v>
       </c>
       <c r="C127" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D127" t="s">
-        <v>149</v>
+        <v>13</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128">
-        <v>1000002</v>
+        <v>1000001</v>
       </c>
       <c r="B128">
-        <v>1000002</v>
+        <v>1000001</v>
       </c>
       <c r="C128" t="s">
+        <v>133</v>
+      </c>
+      <c r="D128" t="s">
         <v>150</v>
-      </c>
-      <c r="D128" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129">
-        <v>1001001</v>
+        <v>1000002</v>
       </c>
       <c r="B129">
-        <v>1001001</v>
+        <v>1000002</v>
       </c>
       <c r="C129" t="s">
         <v>151</v>
       </c>
       <c r="D129" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130">
+        <v>1001001</v>
+      </c>
+      <c r="B130">
+        <v>1001001</v>
+      </c>
+      <c r="C130" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="130" ht="12" customHeight="1" spans="1:4">
-      <c r="A130">
+      <c r="D130" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="131" ht="12" customHeight="1" spans="1:4">
+      <c r="A131">
         <v>1002001</v>
       </c>
-      <c r="B130">
+      <c r="B131">
         <v>1002001</v>
       </c>
-      <c r="C130" t="s">
-        <v>153</v>
-      </c>
-      <c r="D130" t="s">
+      <c r="C131" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="131" spans="1:4">
-      <c r="A131">
-        <v>1002002</v>
-      </c>
-      <c r="B131">
-        <v>1002002</v>
-      </c>
-      <c r="C131" t="s">
+      <c r="D131" t="s">
         <v>155</v>
-      </c>
-      <c r="D131" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132">
-        <v>1003001</v>
+        <v>1002002</v>
       </c>
       <c r="B132">
-        <v>1003001</v>
+        <v>1002002</v>
       </c>
       <c r="C132" t="s">
         <v>156</v>
       </c>
       <c r="D132" t="s">
-        <v>157</v>
+        <v>13</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133">
-        <v>1003002</v>
+        <v>1003001</v>
       </c>
       <c r="B133">
-        <v>1003002</v>
+        <v>1003001</v>
       </c>
       <c r="C133" t="s">
+        <v>157</v>
+      </c>
+      <c r="D133" t="s">
         <v>158</v>
-      </c>
-      <c r="D133" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134">
-        <v>1004001</v>
+        <v>1003002</v>
       </c>
       <c r="B134">
-        <v>1004001</v>
+        <v>1003002</v>
       </c>
       <c r="C134" t="s">
         <v>159</v>
       </c>
       <c r="D134" t="s">
-        <v>160</v>
+        <v>13</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135">
-        <v>1004002</v>
+        <v>1004001</v>
       </c>
       <c r="B135">
-        <v>1004002</v>
+        <v>1004001</v>
       </c>
       <c r="C135" t="s">
-        <v>31</v>
+        <v>160</v>
       </c>
       <c r="D135" t="s">
-        <v>13</v>
+        <v>161</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136">
-        <v>1005001</v>
+        <v>1004002</v>
       </c>
       <c r="B136">
-        <v>1005001</v>
+        <v>1004002</v>
       </c>
       <c r="C136" t="s">
-        <v>161</v>
+        <v>31</v>
       </c>
       <c r="D136" t="s">
-        <v>162</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137">
-        <v>1005002</v>
+        <v>1005001</v>
       </c>
       <c r="B137">
-        <v>1005002</v>
+        <v>1005001</v>
       </c>
       <c r="C137" t="s">
+        <v>162</v>
+      </c>
+      <c r="D137" t="s">
         <v>163</v>
-      </c>
-      <c r="D137" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138">
-        <v>1005003</v>
+        <v>1005002</v>
       </c>
       <c r="B138">
-        <v>1005003</v>
+        <v>1005002</v>
       </c>
       <c r="C138" t="s">
         <v>164</v>
@@ -3483,38 +3486,38 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139">
-        <v>2000001</v>
+        <v>1005003</v>
       </c>
       <c r="B139">
-        <v>2000001</v>
+        <v>1005003</v>
       </c>
       <c r="C139" t="s">
         <v>165</v>
       </c>
       <c r="D139" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140">
-        <v>2000002</v>
+        <v>2000001</v>
       </c>
       <c r="B140">
-        <v>2000002</v>
+        <v>2000001</v>
       </c>
       <c r="C140" t="s">
+        <v>166</v>
+      </c>
+      <c r="D140" t="s">
         <v>167</v>
-      </c>
-      <c r="D140" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141">
-        <v>2000003</v>
+        <v>2000002</v>
       </c>
       <c r="B141">
-        <v>2000003</v>
+        <v>2000002</v>
       </c>
       <c r="C141" t="s">
         <v>168</v>
@@ -3525,10 +3528,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142">
-        <v>2000004</v>
+        <v>2000003</v>
       </c>
       <c r="B142">
-        <v>2000004</v>
+        <v>2000003</v>
       </c>
       <c r="C142" t="s">
         <v>169</v>
@@ -3539,10 +3542,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143">
-        <v>2000005</v>
+        <v>2000004</v>
       </c>
       <c r="B143">
-        <v>2000005</v>
+        <v>2000004</v>
       </c>
       <c r="C143" t="s">
         <v>170</v>
@@ -3553,10 +3556,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144">
-        <v>2000006</v>
+        <v>2000005</v>
       </c>
       <c r="B144">
-        <v>2000006</v>
+        <v>2000005</v>
       </c>
       <c r="C144" t="s">
         <v>171</v>
@@ -3567,10 +3570,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145">
-        <v>2000007</v>
+        <v>2000006</v>
       </c>
       <c r="B145">
-        <v>2000007</v>
+        <v>2000006</v>
       </c>
       <c r="C145" t="s">
         <v>172</v>
@@ -3581,10 +3584,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146">
-        <v>2000008</v>
+        <v>2000007</v>
       </c>
       <c r="B146">
-        <v>2000008</v>
+        <v>2000007</v>
       </c>
       <c r="C146" t="s">
         <v>173</v>
@@ -3595,10 +3598,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147">
-        <v>2000009</v>
+        <v>2000008</v>
       </c>
       <c r="B147">
-        <v>2000009</v>
+        <v>2000008</v>
       </c>
       <c r="C147" t="s">
         <v>174</v>
@@ -3609,10 +3612,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148">
-        <v>2000010</v>
+        <v>2000009</v>
       </c>
       <c r="B148">
-        <v>2000010</v>
+        <v>2000009</v>
       </c>
       <c r="C148" t="s">
         <v>175</v>
@@ -3621,40 +3624,40 @@
         <v>13</v>
       </c>
     </row>
-    <row r="149" ht="12" customHeight="1" spans="1:4">
+    <row r="149" spans="1:4">
       <c r="A149">
-        <v>3000001</v>
+        <v>2000010</v>
       </c>
       <c r="B149">
-        <v>3000001</v>
+        <v>2000010</v>
       </c>
       <c r="C149" t="s">
         <v>176</v>
       </c>
       <c r="D149" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="150" ht="12" customHeight="1" spans="1:4">
+      <c r="A150">
+        <v>3000001</v>
+      </c>
+      <c r="B150">
+        <v>3000001</v>
+      </c>
+      <c r="C150" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="150" spans="1:4">
-      <c r="A150">
-        <v>3000002</v>
-      </c>
-      <c r="B150">
-        <v>3000002</v>
-      </c>
-      <c r="C150" t="s">
+      <c r="D150" t="s">
         <v>178</v>
-      </c>
-      <c r="D150" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151">
-        <v>3000003</v>
+        <v>3000002</v>
       </c>
       <c r="B151">
-        <v>3000003</v>
+        <v>3000002</v>
       </c>
       <c r="C151" t="s">
         <v>179</v>
@@ -3665,10 +3668,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152">
-        <v>3000004</v>
+        <v>3000003</v>
       </c>
       <c r="B152">
-        <v>3000004</v>
+        <v>3000003</v>
       </c>
       <c r="C152" t="s">
         <v>180</v>
@@ -3679,10 +3682,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153">
-        <v>3000005</v>
+        <v>3000004</v>
       </c>
       <c r="B153">
-        <v>3000005</v>
+        <v>3000004</v>
       </c>
       <c r="C153" t="s">
         <v>181</v>
@@ -3691,7 +3694,20 @@
         <v>13</v>
       </c>
     </row>
-    <row r="182" ht="12" customHeight="1"/>
+    <row r="154" spans="1:4">
+      <c r="A154">
+        <v>3000005</v>
+      </c>
+      <c r="B154">
+        <v>3000005</v>
+      </c>
+      <c r="C154" t="s">
+        <v>182</v>
+      </c>
+      <c r="D154" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="183" ht="12" customHeight="1"/>
     <row r="184" ht="12" customHeight="1"/>
     <row r="185" ht="12" customHeight="1"/>
@@ -3726,9 +3742,10 @@
     <row r="214" ht="12" customHeight="1"/>
     <row r="215" ht="12" customHeight="1"/>
     <row r="216" ht="12" customHeight="1"/>
-    <row r="217" customHeight="1"/>
-    <row r="268" ht="12" customHeight="1"/>
+    <row r="217" ht="12" customHeight="1"/>
+    <row r="218" customHeight="1"/>
     <row r="269" ht="12" customHeight="1"/>
+    <row r="270" ht="12" customHeight="1"/>
   </sheetData>
   <sortState ref="A4:D88">
     <sortCondition ref="A4"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="UIText" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="184">
   <si>
     <t>id</t>
   </si>
@@ -303,6 +303,9 @@
   </si>
   <si>
     <t>返回主界面</t>
+  </si>
+  <si>
+    <t>退出战斗</t>
   </si>
   <si>
     <t>伤害</t>
@@ -1543,7 +1546,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D270"/>
+  <dimension ref="A1:D271"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -2590,38 +2593,38 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75">
-        <v>50001</v>
+        <v>49004</v>
       </c>
       <c r="B75">
-        <v>50001</v>
+        <v>49004</v>
       </c>
       <c r="C75" t="s">
         <v>92</v>
       </c>
       <c r="D75" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="B76">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C76" t="s">
+        <v>93</v>
+      </c>
+      <c r="D76" t="s">
         <v>94</v>
-      </c>
-      <c r="D76" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="B77">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C77" t="s">
         <v>95</v>
@@ -2632,10 +2635,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="B78">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C78" t="s">
         <v>96</v>
@@ -2646,10 +2649,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79">
-        <v>50101</v>
+        <v>50004</v>
       </c>
       <c r="B79">
-        <v>50101</v>
+        <v>50004</v>
       </c>
       <c r="C79" t="s">
         <v>97</v>
@@ -2660,38 +2663,38 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80">
-        <v>51001</v>
+        <v>50101</v>
       </c>
       <c r="B80">
-        <v>51001</v>
+        <v>50101</v>
       </c>
       <c r="C80" t="s">
         <v>98</v>
       </c>
       <c r="D80" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81">
-        <v>51002</v>
+        <v>51001</v>
       </c>
       <c r="B81">
-        <v>51002</v>
+        <v>51001</v>
       </c>
       <c r="C81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D81" t="s">
         <v>100</v>
-      </c>
-      <c r="D81" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82">
-        <v>51003</v>
+        <v>51002</v>
       </c>
       <c r="B82">
-        <v>51003</v>
+        <v>51002</v>
       </c>
       <c r="C82" t="s">
         <v>101</v>
@@ -2702,41 +2705,41 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83">
-        <v>52001</v>
+        <v>51003</v>
       </c>
       <c r="B83">
-        <v>52001</v>
+        <v>51003</v>
       </c>
       <c r="C83" t="s">
         <v>102</v>
       </c>
       <c r="D83" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84">
+        <v>52001</v>
+      </c>
+      <c r="B84">
+        <v>52001</v>
+      </c>
+      <c r="C84" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="84" ht="12" customHeight="1" spans="1:4">
-      <c r="A84">
+      <c r="D84" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="85" ht="12" customHeight="1" spans="1:4">
+      <c r="A85">
         <v>52002</v>
       </c>
-      <c r="B84">
+      <c r="B85">
         <v>52002</v>
       </c>
-      <c r="C84" t="s">
-        <v>101</v>
-      </c>
-      <c r="D84" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85">
-        <v>52003</v>
-      </c>
-      <c r="B85">
-        <v>52003</v>
-      </c>
       <c r="C85" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D85" t="s">
         <v>13</v>
@@ -2744,10 +2747,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86">
-        <v>52004</v>
+        <v>52003</v>
       </c>
       <c r="B86">
-        <v>52004</v>
+        <v>52003</v>
       </c>
       <c r="C86" t="s">
         <v>105</v>
@@ -2758,10 +2761,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87">
-        <v>52005</v>
+        <v>52004</v>
       </c>
       <c r="B87">
-        <v>52005</v>
+        <v>52004</v>
       </c>
       <c r="C87" t="s">
         <v>106</v>
@@ -2772,38 +2775,38 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88">
-        <v>53000</v>
+        <v>52005</v>
       </c>
       <c r="B88">
-        <v>53000</v>
+        <v>52005</v>
       </c>
       <c r="C88" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="D88" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89">
-        <v>53001</v>
+        <v>53000</v>
       </c>
       <c r="B89">
-        <v>53001</v>
+        <v>53000</v>
       </c>
       <c r="C89" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="D89" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90">
-        <v>53002</v>
+        <v>53001</v>
       </c>
       <c r="B90">
-        <v>53002</v>
+        <v>53001</v>
       </c>
       <c r="C90" t="s">
         <v>108</v>
@@ -2814,10 +2817,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91">
-        <v>53003</v>
+        <v>53002</v>
       </c>
       <c r="B91">
-        <v>53003</v>
+        <v>53002</v>
       </c>
       <c r="C91" t="s">
         <v>109</v>
@@ -2828,10 +2831,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92">
-        <v>53004</v>
+        <v>53003</v>
       </c>
       <c r="B92">
-        <v>53004</v>
+        <v>53003</v>
       </c>
       <c r="C92" t="s">
         <v>110</v>
@@ -2842,10 +2845,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93">
-        <v>53005</v>
+        <v>53004</v>
       </c>
       <c r="B93">
-        <v>53005</v>
+        <v>53004</v>
       </c>
       <c r="C93" t="s">
         <v>111</v>
@@ -2856,10 +2859,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94">
-        <v>53006</v>
+        <v>53005</v>
       </c>
       <c r="B94">
-        <v>53006</v>
+        <v>53005</v>
       </c>
       <c r="C94" t="s">
         <v>112</v>
@@ -2870,10 +2873,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95">
-        <v>53007</v>
+        <v>53006</v>
       </c>
       <c r="B95">
-        <v>53007</v>
+        <v>53006</v>
       </c>
       <c r="C95" t="s">
         <v>113</v>
@@ -2884,10 +2887,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96">
-        <v>53008</v>
+        <v>53007</v>
       </c>
       <c r="B96">
-        <v>53008</v>
+        <v>53007</v>
       </c>
       <c r="C96" t="s">
         <v>114</v>
@@ -2898,10 +2901,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97">
-        <v>53009</v>
+        <v>53008</v>
       </c>
       <c r="B97">
-        <v>53009</v>
+        <v>53008</v>
       </c>
       <c r="C97" t="s">
         <v>115</v>
@@ -2912,10 +2915,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98">
-        <v>53010</v>
+        <v>53009</v>
       </c>
       <c r="B98">
-        <v>53010</v>
+        <v>53009</v>
       </c>
       <c r="C98" t="s">
         <v>116</v>
@@ -2926,10 +2929,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99">
-        <v>53011</v>
+        <v>53010</v>
       </c>
       <c r="B99">
-        <v>53011</v>
+        <v>53010</v>
       </c>
       <c r="C99" t="s">
         <v>117</v>
@@ -2940,10 +2943,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100">
-        <v>53012</v>
+        <v>53011</v>
       </c>
       <c r="B100">
-        <v>53012</v>
+        <v>53011</v>
       </c>
       <c r="C100" t="s">
         <v>118</v>
@@ -2954,10 +2957,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101">
-        <v>54001</v>
+        <v>53012</v>
       </c>
       <c r="B101">
-        <v>54001</v>
+        <v>53012</v>
       </c>
       <c r="C101" t="s">
         <v>119</v>
@@ -2968,38 +2971,38 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102">
-        <v>60000</v>
+        <v>54001</v>
       </c>
       <c r="B102">
-        <v>60000</v>
+        <v>54001</v>
       </c>
       <c r="C102" t="s">
         <v>120</v>
       </c>
       <c r="D102" t="s">
-        <v>121</v>
+        <v>13</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103">
-        <v>60001</v>
+        <v>60000</v>
       </c>
       <c r="B103">
-        <v>60001</v>
+        <v>60000</v>
       </c>
       <c r="C103" t="s">
+        <v>121</v>
+      </c>
+      <c r="D103" t="s">
         <v>122</v>
-      </c>
-      <c r="D103" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104">
-        <v>60002</v>
+        <v>60001</v>
       </c>
       <c r="B104">
-        <v>60002</v>
+        <v>60001</v>
       </c>
       <c r="C104" t="s">
         <v>123</v>
@@ -3010,10 +3013,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105">
-        <v>61001</v>
+        <v>60002</v>
       </c>
       <c r="B105">
-        <v>61001</v>
+        <v>60002</v>
       </c>
       <c r="C105" t="s">
         <v>124</v>
@@ -3024,10 +3027,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106">
-        <v>61002</v>
+        <v>61001</v>
       </c>
       <c r="B106">
-        <v>61002</v>
+        <v>61001</v>
       </c>
       <c r="C106" t="s">
         <v>125</v>
@@ -3038,10 +3041,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107">
-        <v>61003</v>
+        <v>61002</v>
       </c>
       <c r="B107">
-        <v>61003</v>
+        <v>61002</v>
       </c>
       <c r="C107" t="s">
         <v>126</v>
@@ -3052,38 +3055,38 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108">
-        <v>62001</v>
+        <v>61003</v>
       </c>
       <c r="B108">
-        <v>62001</v>
+        <v>61003</v>
       </c>
       <c r="C108" t="s">
         <v>127</v>
       </c>
       <c r="D108" t="s">
-        <v>128</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109">
-        <v>62002</v>
+        <v>62001</v>
       </c>
       <c r="B109">
-        <v>62002</v>
+        <v>62001</v>
       </c>
       <c r="C109" t="s">
+        <v>128</v>
+      </c>
+      <c r="D109" t="s">
         <v>129</v>
-      </c>
-      <c r="D109" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110">
-        <v>62003</v>
+        <v>62002</v>
       </c>
       <c r="B110">
-        <v>62003</v>
+        <v>62002</v>
       </c>
       <c r="C110" t="s">
         <v>130</v>
@@ -3094,13 +3097,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111">
-        <v>62004</v>
+        <v>62003</v>
       </c>
       <c r="B111">
-        <v>62004</v>
+        <v>62003</v>
       </c>
       <c r="C111" t="s">
-        <v>69</v>
+        <v>131</v>
       </c>
       <c r="D111" t="s">
         <v>13</v>
@@ -3108,38 +3111,38 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112">
-        <v>63001</v>
+        <v>62004</v>
       </c>
       <c r="B112">
-        <v>63001</v>
+        <v>62004</v>
       </c>
       <c r="C112" t="s">
-        <v>131</v>
+        <v>69</v>
       </c>
       <c r="D112" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113">
-        <v>63002</v>
+        <v>63001</v>
       </c>
       <c r="B113">
-        <v>63002</v>
+        <v>63001</v>
       </c>
       <c r="C113" t="s">
+        <v>132</v>
+      </c>
+      <c r="D113" t="s">
         <v>133</v>
-      </c>
-      <c r="D113" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114">
-        <v>63003</v>
+        <v>63002</v>
       </c>
       <c r="B114">
-        <v>63003</v>
+        <v>63002</v>
       </c>
       <c r="C114" t="s">
         <v>134</v>
@@ -3150,52 +3153,52 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115">
-        <v>70001</v>
+        <v>63003</v>
       </c>
       <c r="B115">
-        <v>70001</v>
+        <v>63003</v>
       </c>
       <c r="C115" t="s">
         <v>135</v>
       </c>
       <c r="D115" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116">
+        <v>70001</v>
+      </c>
+      <c r="B116">
+        <v>70001</v>
+      </c>
+      <c r="C116" t="s">
+        <v>136</v>
+      </c>
+      <c r="D116" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117">
         <v>80001</v>
       </c>
-      <c r="B116">
+      <c r="B117">
         <v>80001</v>
       </c>
-      <c r="C116" t="s">
-        <v>137</v>
-      </c>
-      <c r="D116" t="s">
+      <c r="C117" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="117" customFormat="1" spans="1:4">
-      <c r="A117">
-        <v>80002</v>
-      </c>
-      <c r="B117">
-        <v>80002</v>
-      </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
         <v>139</v>
-      </c>
-      <c r="D117" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="118" customFormat="1" spans="1:4">
       <c r="A118">
-        <v>80003</v>
+        <v>80002</v>
       </c>
       <c r="B118">
-        <v>80003</v>
+        <v>80002</v>
       </c>
       <c r="C118" t="s">
         <v>140</v>
@@ -3206,10 +3209,10 @@
     </row>
     <row r="119" customFormat="1" spans="1:4">
       <c r="A119">
-        <v>80004</v>
+        <v>80003</v>
       </c>
       <c r="B119">
-        <v>80004</v>
+        <v>80003</v>
       </c>
       <c r="C119" t="s">
         <v>141</v>
@@ -3220,10 +3223,10 @@
     </row>
     <row r="120" customFormat="1" spans="1:4">
       <c r="A120">
-        <v>80005</v>
+        <v>80004</v>
       </c>
       <c r="B120">
-        <v>80005</v>
+        <v>80004</v>
       </c>
       <c r="C120" t="s">
         <v>142</v>
@@ -3234,10 +3237,10 @@
     </row>
     <row r="121" customFormat="1" spans="1:4">
       <c r="A121">
-        <v>80006</v>
+        <v>80005</v>
       </c>
       <c r="B121">
-        <v>80006</v>
+        <v>80005</v>
       </c>
       <c r="C121" t="s">
         <v>143</v>
@@ -3248,10 +3251,10 @@
     </row>
     <row r="122" customFormat="1" spans="1:4">
       <c r="A122">
-        <v>80007</v>
+        <v>80006</v>
       </c>
       <c r="B122">
-        <v>80007</v>
+        <v>80006</v>
       </c>
       <c r="C122" t="s">
         <v>144</v>
@@ -3262,10 +3265,10 @@
     </row>
     <row r="123" customFormat="1" spans="1:4">
       <c r="A123">
-        <v>80008</v>
+        <v>80007</v>
       </c>
       <c r="B123">
-        <v>80008</v>
+        <v>80007</v>
       </c>
       <c r="C123" t="s">
         <v>145</v>
@@ -3276,10 +3279,10 @@
     </row>
     <row r="124" customFormat="1" spans="1:4">
       <c r="A124">
-        <v>80009</v>
+        <v>80008</v>
       </c>
       <c r="B124">
-        <v>80009</v>
+        <v>80008</v>
       </c>
       <c r="C124" t="s">
         <v>146</v>
@@ -3290,10 +3293,10 @@
     </row>
     <row r="125" customFormat="1" spans="1:4">
       <c r="A125">
-        <v>80010</v>
+        <v>80009</v>
       </c>
       <c r="B125">
-        <v>80010</v>
+        <v>80009</v>
       </c>
       <c r="C125" t="s">
         <v>147</v>
@@ -3304,192 +3307,192 @@
     </row>
     <row r="126" customFormat="1" spans="1:4">
       <c r="A126">
-        <v>90001</v>
+        <v>80010</v>
       </c>
       <c r="B126">
-        <v>90001</v>
+        <v>80010</v>
       </c>
       <c r="C126" t="s">
         <v>148</v>
       </c>
       <c r="D126" t="s">
-        <v>148</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127" customFormat="1" spans="1:4">
       <c r="A127">
-        <v>90002</v>
+        <v>90001</v>
       </c>
       <c r="B127">
-        <v>90002</v>
+        <v>90001</v>
       </c>
       <c r="C127" t="s">
         <v>149</v>
       </c>
       <c r="D127" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="128" customFormat="1" spans="1:4">
       <c r="A128">
-        <v>1000001</v>
+        <v>90002</v>
       </c>
       <c r="B128">
-        <v>1000001</v>
+        <v>90002</v>
       </c>
       <c r="C128" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="D128" t="s">
-        <v>150</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129">
-        <v>1000002</v>
+        <v>1000001</v>
       </c>
       <c r="B129">
-        <v>1000002</v>
+        <v>1000001</v>
       </c>
       <c r="C129" t="s">
+        <v>134</v>
+      </c>
+      <c r="D129" t="s">
         <v>151</v>
-      </c>
-      <c r="D129" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130">
-        <v>1001001</v>
+        <v>1000002</v>
       </c>
       <c r="B130">
-        <v>1001001</v>
+        <v>1000002</v>
       </c>
       <c r="C130" t="s">
         <v>152</v>
       </c>
       <c r="D130" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131">
+        <v>1001001</v>
+      </c>
+      <c r="B131">
+        <v>1001001</v>
+      </c>
+      <c r="C131" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="131" ht="12" customHeight="1" spans="1:4">
-      <c r="A131">
+      <c r="D131" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="132" ht="12" customHeight="1" spans="1:4">
+      <c r="A132">
         <v>1002001</v>
       </c>
-      <c r="B131">
+      <c r="B132">
         <v>1002001</v>
       </c>
-      <c r="C131" t="s">
-        <v>154</v>
-      </c>
-      <c r="D131" t="s">
+      <c r="C132" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="132" spans="1:4">
-      <c r="A132">
-        <v>1002002</v>
-      </c>
-      <c r="B132">
-        <v>1002002</v>
-      </c>
-      <c r="C132" t="s">
+      <c r="D132" t="s">
         <v>156</v>
-      </c>
-      <c r="D132" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133">
-        <v>1003001</v>
+        <v>1002002</v>
       </c>
       <c r="B133">
-        <v>1003001</v>
+        <v>1002002</v>
       </c>
       <c r="C133" t="s">
         <v>157</v>
       </c>
       <c r="D133" t="s">
-        <v>158</v>
+        <v>13</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134">
-        <v>1003002</v>
+        <v>1003001</v>
       </c>
       <c r="B134">
-        <v>1003002</v>
+        <v>1003001</v>
       </c>
       <c r="C134" t="s">
+        <v>158</v>
+      </c>
+      <c r="D134" t="s">
         <v>159</v>
-      </c>
-      <c r="D134" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135">
-        <v>1004001</v>
+        <v>1003002</v>
       </c>
       <c r="B135">
-        <v>1004001</v>
+        <v>1003002</v>
       </c>
       <c r="C135" t="s">
         <v>160</v>
       </c>
       <c r="D135" t="s">
-        <v>161</v>
+        <v>13</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136">
-        <v>1004002</v>
+        <v>1004001</v>
       </c>
       <c r="B136">
-        <v>1004002</v>
+        <v>1004001</v>
       </c>
       <c r="C136" t="s">
-        <v>31</v>
+        <v>161</v>
       </c>
       <c r="D136" t="s">
-        <v>13</v>
+        <v>162</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137">
-        <v>1005001</v>
+        <v>1004002</v>
       </c>
       <c r="B137">
-        <v>1005001</v>
+        <v>1004002</v>
       </c>
       <c r="C137" t="s">
-        <v>162</v>
+        <v>31</v>
       </c>
       <c r="D137" t="s">
-        <v>163</v>
+        <v>13</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138">
-        <v>1005002</v>
+        <v>1005001</v>
       </c>
       <c r="B138">
-        <v>1005002</v>
+        <v>1005001</v>
       </c>
       <c r="C138" t="s">
+        <v>163</v>
+      </c>
+      <c r="D138" t="s">
         <v>164</v>
-      </c>
-      <c r="D138" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139">
-        <v>1005003</v>
+        <v>1005002</v>
       </c>
       <c r="B139">
-        <v>1005003</v>
+        <v>1005002</v>
       </c>
       <c r="C139" t="s">
         <v>165</v>
@@ -3500,38 +3503,38 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140">
-        <v>2000001</v>
+        <v>1005003</v>
       </c>
       <c r="B140">
-        <v>2000001</v>
+        <v>1005003</v>
       </c>
       <c r="C140" t="s">
         <v>166</v>
       </c>
       <c r="D140" t="s">
-        <v>167</v>
+        <v>13</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141">
-        <v>2000002</v>
+        <v>2000001</v>
       </c>
       <c r="B141">
-        <v>2000002</v>
+        <v>2000001</v>
       </c>
       <c r="C141" t="s">
+        <v>167</v>
+      </c>
+      <c r="D141" t="s">
         <v>168</v>
-      </c>
-      <c r="D141" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142">
-        <v>2000003</v>
+        <v>2000002</v>
       </c>
       <c r="B142">
-        <v>2000003</v>
+        <v>2000002</v>
       </c>
       <c r="C142" t="s">
         <v>169</v>
@@ -3542,10 +3545,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143">
-        <v>2000004</v>
+        <v>2000003</v>
       </c>
       <c r="B143">
-        <v>2000004</v>
+        <v>2000003</v>
       </c>
       <c r="C143" t="s">
         <v>170</v>
@@ -3556,10 +3559,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144">
-        <v>2000005</v>
+        <v>2000004</v>
       </c>
       <c r="B144">
-        <v>2000005</v>
+        <v>2000004</v>
       </c>
       <c r="C144" t="s">
         <v>171</v>
@@ -3570,10 +3573,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145">
-        <v>2000006</v>
+        <v>2000005</v>
       </c>
       <c r="B145">
-        <v>2000006</v>
+        <v>2000005</v>
       </c>
       <c r="C145" t="s">
         <v>172</v>
@@ -3584,10 +3587,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146">
-        <v>2000007</v>
+        <v>2000006</v>
       </c>
       <c r="B146">
-        <v>2000007</v>
+        <v>2000006</v>
       </c>
       <c r="C146" t="s">
         <v>173</v>
@@ -3598,10 +3601,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147">
-        <v>2000008</v>
+        <v>2000007</v>
       </c>
       <c r="B147">
-        <v>2000008</v>
+        <v>2000007</v>
       </c>
       <c r="C147" t="s">
         <v>174</v>
@@ -3612,10 +3615,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148">
-        <v>2000009</v>
+        <v>2000008</v>
       </c>
       <c r="B148">
-        <v>2000009</v>
+        <v>2000008</v>
       </c>
       <c r="C148" t="s">
         <v>175</v>
@@ -3626,10 +3629,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149">
-        <v>2000010</v>
+        <v>2000009</v>
       </c>
       <c r="B149">
-        <v>2000010</v>
+        <v>2000009</v>
       </c>
       <c r="C149" t="s">
         <v>176</v>
@@ -3638,40 +3641,40 @@
         <v>13</v>
       </c>
     </row>
-    <row r="150" ht="12" customHeight="1" spans="1:4">
+    <row r="150" spans="1:4">
       <c r="A150">
-        <v>3000001</v>
+        <v>2000010</v>
       </c>
       <c r="B150">
-        <v>3000001</v>
+        <v>2000010</v>
       </c>
       <c r="C150" t="s">
         <v>177</v>
       </c>
       <c r="D150" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="151" ht="12" customHeight="1" spans="1:4">
+      <c r="A151">
+        <v>3000001</v>
+      </c>
+      <c r="B151">
+        <v>3000001</v>
+      </c>
+      <c r="C151" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="151" spans="1:4">
-      <c r="A151">
-        <v>3000002</v>
-      </c>
-      <c r="B151">
-        <v>3000002</v>
-      </c>
-      <c r="C151" t="s">
+      <c r="D151" t="s">
         <v>179</v>
-      </c>
-      <c r="D151" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152">
-        <v>3000003</v>
+        <v>3000002</v>
       </c>
       <c r="B152">
-        <v>3000003</v>
+        <v>3000002</v>
       </c>
       <c r="C152" t="s">
         <v>180</v>
@@ -3682,10 +3685,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153">
-        <v>3000004</v>
+        <v>3000003</v>
       </c>
       <c r="B153">
-        <v>3000004</v>
+        <v>3000003</v>
       </c>
       <c r="C153" t="s">
         <v>181</v>
@@ -3696,10 +3699,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154">
-        <v>3000005</v>
+        <v>3000004</v>
       </c>
       <c r="B154">
-        <v>3000005</v>
+        <v>3000004</v>
       </c>
       <c r="C154" t="s">
         <v>182</v>
@@ -3708,7 +3711,20 @@
         <v>13</v>
       </c>
     </row>
-    <row r="183" ht="12" customHeight="1"/>
+    <row r="155" spans="1:4">
+      <c r="A155">
+        <v>3000005</v>
+      </c>
+      <c r="B155">
+        <v>3000005</v>
+      </c>
+      <c r="C155" t="s">
+        <v>183</v>
+      </c>
+      <c r="D155" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="184" ht="12" customHeight="1"/>
     <row r="185" ht="12" customHeight="1"/>
     <row r="186" ht="12" customHeight="1"/>
@@ -3743,9 +3759,10 @@
     <row r="215" ht="12" customHeight="1"/>
     <row r="216" ht="12" customHeight="1"/>
     <row r="217" ht="12" customHeight="1"/>
-    <row r="218" customHeight="1"/>
-    <row r="269" ht="12" customHeight="1"/>
+    <row r="218" ht="12" customHeight="1"/>
+    <row r="219" customHeight="1"/>
     <row r="270" ht="12" customHeight="1"/>
+    <row r="271" ht="12" customHeight="1"/>
   </sheetData>
   <sortState ref="A4:D88">
     <sortCondition ref="A4"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="196">
   <si>
     <t>id</t>
   </si>
@@ -441,6 +441,9 @@
   </si>
   <si>
     <t>是否以此外观完成转生？</t>
+  </si>
+  <si>
+    <t>统计</t>
   </si>
   <si>
     <t>贿赂</t>
@@ -1580,7 +1583,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D273"/>
+  <dimension ref="A1:D275"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="9.375" style="1" customWidth="1"/>
@@ -3243,69 +3246,69 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119">
-        <v>70001</v>
+        <v>64001</v>
       </c>
       <c r="B119">
-        <v>70001</v>
+        <v>64001</v>
       </c>
       <c r="C119" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="D119" t="s">
-        <v>139</v>
+        <v>59</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120">
-        <v>80001</v>
+        <v>64002</v>
       </c>
       <c r="B120">
-        <v>80001</v>
+        <v>64002</v>
       </c>
       <c r="C120" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D120" t="s">
-        <v>141</v>
+        <v>13</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121">
-        <v>80002</v>
+        <v>70001</v>
       </c>
       <c r="B121">
-        <v>80002</v>
+        <v>70001</v>
       </c>
       <c r="C121" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D121" t="s">
-        <v>13</v>
+        <v>140</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122">
-        <v>80003</v>
+        <v>80001</v>
       </c>
       <c r="B122">
-        <v>80003</v>
+        <v>80001</v>
       </c>
       <c r="C122" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D122" t="s">
-        <v>13</v>
+        <v>142</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123">
-        <v>80004</v>
+        <v>80002</v>
       </c>
       <c r="B123">
-        <v>80004</v>
+        <v>80002</v>
       </c>
       <c r="C123" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D123" t="s">
         <v>13</v>
@@ -3313,13 +3316,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124">
-        <v>80005</v>
+        <v>80003</v>
       </c>
       <c r="B124">
-        <v>80005</v>
+        <v>80003</v>
       </c>
       <c r="C124" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D124" t="s">
         <v>13</v>
@@ -3327,13 +3330,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125">
-        <v>80006</v>
+        <v>80004</v>
       </c>
       <c r="B125">
-        <v>80006</v>
+        <v>80004</v>
       </c>
       <c r="C125" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D125" t="s">
         <v>13</v>
@@ -3341,13 +3344,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126">
-        <v>80007</v>
+        <v>80005</v>
       </c>
       <c r="B126">
-        <v>80007</v>
+        <v>80005</v>
       </c>
       <c r="C126" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D126" t="s">
         <v>13</v>
@@ -3355,13 +3358,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127">
-        <v>80008</v>
+        <v>80006</v>
       </c>
       <c r="B127">
-        <v>80008</v>
+        <v>80006</v>
       </c>
       <c r="C127" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D127" t="s">
         <v>13</v>
@@ -3369,13 +3372,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128">
-        <v>80009</v>
+        <v>80007</v>
       </c>
       <c r="B128">
-        <v>80009</v>
+        <v>80007</v>
       </c>
       <c r="C128" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D128" t="s">
         <v>13</v>
@@ -3383,13 +3386,13 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129">
-        <v>80010</v>
+        <v>80008</v>
       </c>
       <c r="B129">
-        <v>80010</v>
+        <v>80008</v>
       </c>
       <c r="C129" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D129" t="s">
         <v>13</v>
@@ -3397,27 +3400,27 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130">
-        <v>90001</v>
+        <v>80009</v>
       </c>
       <c r="B130">
-        <v>90001</v>
+        <v>80009</v>
       </c>
       <c r="C130" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D130" t="s">
-        <v>151</v>
+        <v>13</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131">
-        <v>90002</v>
+        <v>80010</v>
       </c>
       <c r="B131">
-        <v>90002</v>
+        <v>80010</v>
       </c>
       <c r="C131" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D131" t="s">
         <v>13</v>
@@ -3425,97 +3428,97 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132">
-        <v>1000001</v>
+        <v>90001</v>
       </c>
       <c r="B132">
-        <v>1000001</v>
+        <v>90001</v>
       </c>
       <c r="C132" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D132" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133">
-        <v>1000002</v>
+        <v>90002</v>
       </c>
       <c r="B133">
-        <v>1000002</v>
+        <v>90002</v>
       </c>
       <c r="C133" t="s">
+        <v>153</v>
+      </c>
+      <c r="D133" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134">
+        <v>1000001</v>
+      </c>
+      <c r="B134">
+        <v>1000001</v>
+      </c>
+      <c r="C134" t="s">
+        <v>136</v>
+      </c>
+      <c r="D134" t="s">
         <v>154</v>
-      </c>
-      <c r="D133" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="134" ht="12" customHeight="1" spans="1:4">
-      <c r="A134">
-        <v>1001001</v>
-      </c>
-      <c r="B134">
-        <v>1001001</v>
-      </c>
-      <c r="C134" t="s">
-        <v>155</v>
-      </c>
-      <c r="D134" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135">
-        <v>1002001</v>
+        <v>1000002</v>
       </c>
       <c r="B135">
-        <v>1002001</v>
+        <v>1000002</v>
       </c>
       <c r="C135" t="s">
+        <v>155</v>
+      </c>
+      <c r="D135" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="136" ht="12" customHeight="1" spans="1:4">
+      <c r="A136">
+        <v>1001001</v>
+      </c>
+      <c r="B136">
+        <v>1001001</v>
+      </c>
+      <c r="C136" t="s">
+        <v>156</v>
+      </c>
+      <c r="D136" t="s">
         <v>157</v>
-      </c>
-      <c r="D135" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4">
-      <c r="A136">
-        <v>1002002</v>
-      </c>
-      <c r="B136">
-        <v>1002002</v>
-      </c>
-      <c r="C136" t="s">
-        <v>159</v>
-      </c>
-      <c r="D136" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137">
-        <v>1003001</v>
+        <v>1002001</v>
       </c>
       <c r="B137">
-        <v>1003001</v>
+        <v>1002001</v>
       </c>
       <c r="C137" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D137" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138">
-        <v>1003002</v>
+        <v>1002002</v>
       </c>
       <c r="B138">
-        <v>1003002</v>
+        <v>1002002</v>
       </c>
       <c r="C138" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D138" t="s">
         <v>13</v>
@@ -3523,27 +3526,27 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139">
-        <v>1004001</v>
+        <v>1003001</v>
       </c>
       <c r="B139">
-        <v>1004001</v>
+        <v>1003001</v>
       </c>
       <c r="C139" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D139" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140">
-        <v>1004002</v>
+        <v>1003002</v>
       </c>
       <c r="B140">
-        <v>1004002</v>
+        <v>1003002</v>
       </c>
       <c r="C140" t="s">
-        <v>31</v>
+        <v>163</v>
       </c>
       <c r="D140" t="s">
         <v>13</v>
@@ -3551,27 +3554,27 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141">
-        <v>1005001</v>
+        <v>1004001</v>
       </c>
       <c r="B141">
-        <v>1005001</v>
+        <v>1004001</v>
       </c>
       <c r="C141" t="s">
+        <v>164</v>
+      </c>
+      <c r="D141" t="s">
         <v>165</v>
-      </c>
-      <c r="D141" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142">
-        <v>1005002</v>
+        <v>1004002</v>
       </c>
       <c r="B142">
-        <v>1005002</v>
+        <v>1004002</v>
       </c>
       <c r="C142" t="s">
-        <v>167</v>
+        <v>31</v>
       </c>
       <c r="D142" t="s">
         <v>13</v>
@@ -3579,41 +3582,41 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143">
-        <v>1005003</v>
+        <v>1005001</v>
       </c>
       <c r="B143">
-        <v>1005003</v>
+        <v>1005001</v>
       </c>
       <c r="C143" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D143" t="s">
-        <v>13</v>
+        <v>167</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144">
-        <v>2000001</v>
+        <v>1005002</v>
       </c>
       <c r="B144">
-        <v>2000001</v>
+        <v>1005002</v>
       </c>
       <c r="C144" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D144" t="s">
-        <v>170</v>
+        <v>13</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145">
-        <v>2000002</v>
+        <v>1005003</v>
       </c>
       <c r="B145">
-        <v>2000002</v>
+        <v>1005003</v>
       </c>
       <c r="C145" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D145" t="s">
         <v>13</v>
@@ -3621,27 +3624,27 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146">
-        <v>2000003</v>
+        <v>2000001</v>
       </c>
       <c r="B146">
-        <v>2000003</v>
+        <v>2000001</v>
       </c>
       <c r="C146" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D146" t="s">
-        <v>13</v>
+        <v>171</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147">
-        <v>2000004</v>
+        <v>2000002</v>
       </c>
       <c r="B147">
-        <v>2000004</v>
+        <v>2000002</v>
       </c>
       <c r="C147" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D147" t="s">
         <v>13</v>
@@ -3649,13 +3652,13 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148">
-        <v>2000005</v>
+        <v>2000003</v>
       </c>
       <c r="B148">
-        <v>2000005</v>
+        <v>2000003</v>
       </c>
       <c r="C148" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D148" t="s">
         <v>13</v>
@@ -3663,13 +3666,13 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="B149">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="C149" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D149" t="s">
         <v>13</v>
@@ -3677,13 +3680,13 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150">
-        <v>2000007</v>
+        <v>2000005</v>
       </c>
       <c r="B150">
-        <v>2000007</v>
+        <v>2000005</v>
       </c>
       <c r="C150" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D150" t="s">
         <v>13</v>
@@ -3691,13 +3694,13 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151">
-        <v>2000008</v>
+        <v>2000006</v>
       </c>
       <c r="B151">
-        <v>2000008</v>
+        <v>2000006</v>
       </c>
       <c r="C151" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D151" t="s">
         <v>13</v>
@@ -3705,27 +3708,27 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152">
-        <v>2000009</v>
+        <v>2000007</v>
       </c>
       <c r="B152">
-        <v>2000009</v>
+        <v>2000007</v>
       </c>
       <c r="C152" t="s">
+        <v>177</v>
+      </c>
+      <c r="D152" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153">
+        <v>2000008</v>
+      </c>
+      <c r="B153">
+        <v>2000008</v>
+      </c>
+      <c r="C153" t="s">
         <v>178</v>
-      </c>
-      <c r="D152" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="153" ht="12" customHeight="1" spans="1:4">
-      <c r="A153">
-        <v>2000010</v>
-      </c>
-      <c r="B153">
-        <v>2000010</v>
-      </c>
-      <c r="C153" t="s">
-        <v>179</v>
       </c>
       <c r="D153" t="s">
         <v>13</v>
@@ -3733,27 +3736,27 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154">
-        <v>3000001</v>
+        <v>2000009</v>
       </c>
       <c r="B154">
-        <v>3000001</v>
+        <v>2000009</v>
       </c>
       <c r="C154" t="s">
+        <v>179</v>
+      </c>
+      <c r="D154" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="155" ht="12" customHeight="1" spans="1:4">
+      <c r="A155">
+        <v>2000010</v>
+      </c>
+      <c r="B155">
+        <v>2000010</v>
+      </c>
+      <c r="C155" t="s">
         <v>180</v>
-      </c>
-      <c r="D154" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4">
-      <c r="A155">
-        <v>3000002</v>
-      </c>
-      <c r="B155">
-        <v>3000002</v>
-      </c>
-      <c r="C155" t="s">
-        <v>182</v>
       </c>
       <c r="D155" t="s">
         <v>13</v>
@@ -3761,27 +3764,27 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156">
-        <v>3000003</v>
+        <v>3000001</v>
       </c>
       <c r="B156">
-        <v>3000003</v>
+        <v>3000001</v>
       </c>
       <c r="C156" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D156" t="s">
-        <v>13</v>
+        <v>182</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157">
-        <v>3000004</v>
+        <v>3000002</v>
       </c>
       <c r="B157">
-        <v>3000004</v>
+        <v>3000002</v>
       </c>
       <c r="C157" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D157" t="s">
         <v>13</v>
@@ -3789,13 +3792,13 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158">
-        <v>3000005</v>
+        <v>3000003</v>
       </c>
       <c r="B158">
-        <v>3000005</v>
+        <v>3000003</v>
       </c>
       <c r="C158" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D158" t="s">
         <v>13</v>
@@ -3803,27 +3806,27 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159">
-        <v>4000006</v>
+        <v>3000004</v>
       </c>
       <c r="B159">
-        <v>4000006</v>
+        <v>3000004</v>
       </c>
       <c r="C159" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D159" t="s">
-        <v>187</v>
+        <v>13</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160">
-        <v>4000008</v>
+        <v>3000005</v>
       </c>
       <c r="B160">
-        <v>4000008</v>
+        <v>3000005</v>
       </c>
       <c r="C160" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D160" t="s">
         <v>13</v>
@@ -3831,27 +3834,27 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161">
-        <v>4000010</v>
+        <v>4000006</v>
       </c>
       <c r="B161">
-        <v>4000010</v>
+        <v>4000006</v>
       </c>
       <c r="C161" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D161" t="s">
-        <v>13</v>
+        <v>188</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162">
-        <v>4000011</v>
+        <v>4000008</v>
       </c>
       <c r="B162">
-        <v>4000011</v>
+        <v>4000008</v>
       </c>
       <c r="C162" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D162" t="s">
         <v>13</v>
@@ -3859,13 +3862,13 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163">
-        <v>4000012</v>
+        <v>4000010</v>
       </c>
       <c r="B163">
-        <v>4000012</v>
+        <v>4000010</v>
       </c>
       <c r="C163" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D163" t="s">
         <v>13</v>
@@ -3873,13 +3876,13 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164">
-        <v>4000013</v>
+        <v>4000011</v>
       </c>
       <c r="B164">
-        <v>4000013</v>
+        <v>4000011</v>
       </c>
       <c r="C164" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D164" t="s">
         <v>13</v>
@@ -3887,13 +3890,13 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165">
-        <v>4000014</v>
+        <v>4000012</v>
       </c>
       <c r="B165">
-        <v>4000014</v>
+        <v>4000012</v>
       </c>
       <c r="C165" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D165" t="s">
         <v>13</v>
@@ -3901,20 +3904,46 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166">
+        <v>4000013</v>
+      </c>
+      <c r="B166">
+        <v>4000013</v>
+      </c>
+      <c r="C166" t="s">
+        <v>193</v>
+      </c>
+      <c r="D166" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167">
+        <v>4000014</v>
+      </c>
+      <c r="B167">
+        <v>4000014</v>
+      </c>
+      <c r="C167" t="s">
+        <v>194</v>
+      </c>
+      <c r="D167" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168">
         <v>4000015</v>
       </c>
-      <c r="B166">
+      <c r="B168">
         <v>4000015</v>
       </c>
-      <c r="C166" t="s">
-        <v>194</v>
-      </c>
-      <c r="D166" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="186" ht="12" customHeight="1"/>
-    <row r="187" ht="12" customHeight="1"/>
+      <c r="C168" t="s">
+        <v>195</v>
+      </c>
+      <c r="D168" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="188" ht="12" customHeight="1"/>
     <row r="189" ht="12" customHeight="1"/>
     <row r="190" ht="12" customHeight="1"/>
@@ -3948,8 +3977,10 @@
     <row r="218" ht="12" customHeight="1"/>
     <row r="219" ht="12" customHeight="1"/>
     <row r="220" ht="12" customHeight="1"/>
-    <row r="272" ht="12" customHeight="1"/>
-    <row r="273" ht="12" customHeight="1"/>
+    <row r="221" ht="12" customHeight="1"/>
+    <row r="222" ht="12" customHeight="1"/>
+    <row r="274" ht="12" customHeight="1"/>
+    <row r="275" ht="12" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D175"/>
+  <dimension ref="A1:D176"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.375" customWidth="1" style="1" min="1" max="1"/>
@@ -3058,18 +3058,18 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="n">
+      <c r="A112" s="0" t="n">
         <v>55007</v>
       </c>
-      <c r="B112" t="n">
+      <c r="B112" s="0" t="n">
         <v>55007</v>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C112" s="0" t="inlineStr">
         <is>
           <t>警报：正义的伙伴们正在靠近…</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D112" s="0" t="inlineStr">
         <is>
           <t>|</t>
         </is>
@@ -3976,51 +3976,51 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="0" t="n">
-        <v>3000001</v>
-      </c>
-      <c r="B163" s="0" t="n">
-        <v>3000001</v>
-      </c>
-      <c r="C163" s="0" t="inlineStr">
-        <is>
-          <t>没有足够的魔晶</t>
-        </is>
-      </c>
-      <c r="D163" s="0" t="inlineStr">
-        <is>
-          <t>Toast</t>
+      <c r="A163" t="n">
+        <v>2000011</v>
+      </c>
+      <c r="B163" t="n">
+        <v>2000011</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>排序：同类</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>3000002</v>
+        <v>3000001</v>
       </c>
       <c r="B164" s="0" t="n">
-        <v>3000002</v>
+        <v>3000001</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="D164" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>3000003</v>
+        <v>3000002</v>
       </c>
       <c r="B165" s="0" t="n">
-        <v>3000003</v>
+        <v>3000002</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>修改名字成功！</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="D165" s="0" t="inlineStr">
@@ -4031,14 +4031,14 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>3000004</v>
+        <v>3000003</v>
       </c>
       <c r="B166" s="0" t="n">
-        <v>3000004</v>
+        <v>3000003</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物！</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="D166" s="0" t="inlineStr">
@@ -4049,14 +4049,14 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>3000005</v>
+        <v>3000004</v>
       </c>
       <c r="B167" s="0" t="n">
-        <v>3000005</v>
+        <v>3000004</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>转生成功！</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="D167" s="0" t="inlineStr">
@@ -4067,50 +4067,50 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>4000006</v>
+        <v>3000005</v>
       </c>
       <c r="B168" s="0" t="n">
-        <v>4000006</v>
+        <v>3000005</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="D168" s="0" t="inlineStr">
         <is>
-          <t>Achievement-进度</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>4000008</v>
+        <v>4000006</v>
       </c>
       <c r="B169" s="0" t="n">
-        <v>4000008</v>
+        <v>4000006</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>领取成功！</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="D169" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Achievement-进度</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>4000010</v>
+        <v>4000008</v>
       </c>
       <c r="B170" s="0" t="n">
-        <v>4000010</v>
+        <v>4000008</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>游玩时间</t>
+          <t>领取成功！</t>
         </is>
       </c>
       <c r="D170" s="0" t="inlineStr">
@@ -4121,14 +4121,14 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>4000011</v>
+        <v>4000010</v>
       </c>
       <c r="B171" s="0" t="n">
-        <v>4000011</v>
+        <v>4000010</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>总击杀数</t>
+          <t>游玩时间</t>
         </is>
       </c>
       <c r="D171" s="0" t="inlineStr">
@@ -4139,14 +4139,14 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>4000012</v>
+        <v>4000011</v>
       </c>
       <c r="B172" s="0" t="n">
-        <v>4000012</v>
+        <v>4000011</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>征服通关</t>
+          <t>总击杀数</t>
         </is>
       </c>
       <c r="D172" s="0" t="inlineStr">
@@ -4157,14 +4157,14 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>4000013</v>
+        <v>4000012</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>4000013</v>
+        <v>4000012</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>难度{0}</t>
+          <t>征服通关</t>
         </is>
       </c>
       <c r="D173" s="0" t="inlineStr">
@@ -4175,14 +4175,14 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>4000014</v>
+        <v>4000013</v>
       </c>
       <c r="B174" s="0" t="n">
-        <v>4000014</v>
+        <v>4000013</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>难度{0}</t>
         </is>
       </c>
       <c r="D174" s="0" t="inlineStr">
@@ -4193,17 +4193,35 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="B175" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="C175" s="0" t="inlineStr">
+        <is>
+          <t>{0}时{1}分</t>
+        </is>
+      </c>
+      <c r="D175" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="0" t="n">
         <v>4000015</v>
       </c>
-      <c r="B175" s="0" t="n">
+      <c r="B176" s="0" t="n">
         <v>4000015</v>
       </c>
-      <c r="C175" s="0" t="inlineStr">
+      <c r="C176" s="0" t="inlineStr">
         <is>
           <t>总通关次数</t>
         </is>
       </c>
-      <c r="D175" s="0" t="inlineStr">
+      <c r="D176" s="0" t="inlineStr">
         <is>
           <t>|</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D176"/>
+  <dimension ref="A1:D180"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.375" customWidth="1" style="1" min="1" max="1"/>
@@ -2537,50 +2537,50 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>50101</v>
+        <v>50005</v>
       </c>
       <c r="B83" s="0" t="n">
-        <v>50101</v>
+        <v>50005</v>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t>继续</t>
+          <t>当前征程：{0}/{1}</t>
         </is>
       </c>
       <c r="D83" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗主界面</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="0" t="n">
-        <v>51001</v>
-      </c>
-      <c r="B84" s="0" t="n">
-        <v>51001</v>
-      </c>
-      <c r="C84" s="0" t="inlineStr">
-        <is>
-          <t>深渊馈赠</t>
-        </is>
-      </c>
-      <c r="D84" s="0" t="inlineStr">
-        <is>
-          <t>战斗深渊馈赠</t>
+      <c r="A84" t="n">
+        <v>50006</v>
+      </c>
+      <c r="B84" t="n">
+        <v>50006</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>魔力不足</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>51002</v>
+        <v>50101</v>
       </c>
       <c r="B85" s="0" t="n">
-        <v>51002</v>
+        <v>50101</v>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>选择一个深渊馈赠</t>
+          <t>继续</t>
         </is>
       </c>
       <c r="D85" s="0" t="inlineStr">
@@ -2591,46 +2591,46 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>51003</v>
+        <v>51001</v>
       </c>
       <c r="B86" s="0" t="n">
-        <v>51003</v>
+        <v>51001</v>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>跳过</t>
+          <t>深渊馈赠</t>
         </is>
       </c>
       <c r="D86" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗深渊馈赠</t>
         </is>
       </c>
     </row>
     <row r="87" ht="12" customHeight="1" s="1">
       <c r="A87" s="0" t="n">
-        <v>52001</v>
+        <v>51002</v>
       </c>
       <c r="B87" s="0" t="n">
-        <v>52001</v>
+        <v>51002</v>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>选择奖励</t>
+          <t>选择一个深渊馈赠</t>
         </is>
       </c>
       <c r="D87" s="0" t="inlineStr">
         <is>
-          <t>奖励选择</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>52002</v>
+        <v>51003</v>
       </c>
       <c r="B88" s="0" t="n">
-        <v>52002</v>
+        <v>51003</v>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
@@ -2645,32 +2645,32 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>52003</v>
+        <v>52001</v>
       </c>
       <c r="B89" s="0" t="n">
-        <v>52003</v>
+        <v>52001</v>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>剩余可选择次数{0}/{1}</t>
+          <t>选择奖励</t>
         </is>
       </c>
       <c r="D89" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>奖励选择</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>52004</v>
+        <v>52002</v>
       </c>
       <c r="B90" s="0" t="n">
-        <v>52004</v>
+        <v>52002</v>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>没有可选择次数</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="D90" s="0" t="inlineStr">
@@ -2681,14 +2681,14 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>52005</v>
+        <v>52003</v>
       </c>
       <c r="B91" s="0" t="n">
-        <v>52005</v>
+        <v>52003</v>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t>还有可选择次数，是否仍要结束选择奖励？</t>
+          <t>剩余可选择次数{0}/{1}</t>
         </is>
       </c>
       <c r="D91" s="0" t="inlineStr">
@@ -2699,32 +2699,32 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>53000</v>
+        <v>52004</v>
       </c>
       <c r="B92" s="0" t="n">
-        <v>53000</v>
+        <v>52004</v>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t>终焉议会</t>
+          <t>没有可选择次数</t>
         </is>
       </c>
       <c r="D92" s="0" t="inlineStr">
         <is>
-          <t>终焉议会</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>53001</v>
+        <v>52005</v>
       </c>
       <c r="B93" s="0" t="n">
-        <v>53001</v>
+        <v>52005</v>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t>选择一个议案</t>
+          <t>还有可选择次数，是否仍要结束选择奖励？</t>
         </is>
       </c>
       <c r="D93" s="0" t="inlineStr">
@@ -2735,32 +2735,32 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>53002</v>
+        <v>53000</v>
       </c>
       <c r="B94" s="0" t="n">
-        <v>53002</v>
+        <v>53000</v>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t>是否提交议案《{0}》，并且前往终焉议会？</t>
+          <t>终焉议会</t>
         </is>
       </c>
       <c r="D94" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>终焉议会</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>53003</v>
+        <v>53001</v>
       </c>
       <c r="B95" s="0" t="n">
-        <v>53003</v>
+        <v>53001</v>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t>通过率   {0}%</t>
+          <t>选择一个议案</t>
         </is>
       </c>
       <c r="D95" s="0" t="inlineStr">
@@ -2771,14 +2771,14 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>53004</v>
+        <v>53002</v>
       </c>
       <c r="B96" s="0" t="n">
-        <v>53004</v>
+        <v>53002</v>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t>开始投票</t>
+          <t>是否提交议案《{0}》，并且前往终焉议会？</t>
         </is>
       </c>
       <c r="D96" s="0" t="inlineStr">
@@ -2789,14 +2789,14 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>53005</v>
+        <v>53003</v>
       </c>
       <c r="B97" s="0" t="n">
-        <v>53005</v>
+        <v>53003</v>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>离开议会</t>
+          <t>通过率   {0}%</t>
         </is>
       </c>
       <c r="D97" s="0" t="inlineStr">
@@ -2807,14 +2807,14 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>53006</v>
+        <v>53004</v>
       </c>
       <c r="B98" s="0" t="n">
-        <v>53006</v>
+        <v>53004</v>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>赞成</t>
+          <t>开始投票</t>
         </is>
       </c>
       <c r="D98" s="0" t="inlineStr">
@@ -2825,14 +2825,14 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>53007</v>
+        <v>53005</v>
       </c>
       <c r="B99" s="0" t="n">
-        <v>53007</v>
+        <v>53005</v>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
-          <t>反对</t>
+          <t>离开议会</t>
         </is>
       </c>
       <c r="D99" s="0" t="inlineStr">
@@ -2843,14 +2843,14 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>53008</v>
+        <v>53006</v>
       </c>
       <c r="B100" s="0" t="n">
-        <v>53008</v>
+        <v>53006</v>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>赞成</t>
         </is>
       </c>
       <c r="D100" s="0" t="inlineStr">
@@ -2861,14 +2861,14 @@
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>53009</v>
+        <v>53007</v>
       </c>
       <c r="B101" s="0" t="n">
-        <v>53009</v>
+        <v>53007</v>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
-          <t>否决</t>
+          <t>反对</t>
         </is>
       </c>
       <c r="D101" s="0" t="inlineStr">
@@ -2879,14 +2879,14 @@
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>53010</v>
+        <v>53008</v>
       </c>
       <c r="B102" s="0" t="n">
-        <v>53010</v>
+        <v>53008</v>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t>暴力说服</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="D102" s="0" t="inlineStr">
@@ -2897,14 +2897,14 @@
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>53011</v>
+        <v>53009</v>
       </c>
       <c r="B103" s="0" t="n">
-        <v>53011</v>
+        <v>53009</v>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
-          <t>自由活动</t>
+          <t>否决</t>
         </is>
       </c>
       <c r="D103" s="0" t="inlineStr">
@@ -2915,14 +2915,14 @@
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>53012</v>
+        <v>53010</v>
       </c>
       <c r="B104" s="0" t="n">
-        <v>53012</v>
+        <v>53010</v>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
-          <t>是否提交议案《{0}》？</t>
+          <t>暴力说服</t>
         </is>
       </c>
       <c r="D104" s="0" t="inlineStr">
@@ -2933,14 +2933,14 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>54001</v>
+        <v>53011</v>
       </c>
       <c r="B105" s="0" t="n">
-        <v>54001</v>
+        <v>53011</v>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
-          <t>没有可孕育的生物</t>
+          <t>自由活动</t>
         </is>
       </c>
       <c r="D105" s="0" t="inlineStr">
@@ -2951,32 +2951,32 @@
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>55001</v>
+        <v>53012</v>
       </c>
       <c r="B106" s="0" t="n">
-        <v>55001</v>
+        <v>53012</v>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
-          <t>魔王讨伐者正在靠近中...</t>
+          <t>是否提交议案《{0}》？</t>
         </is>
       </c>
       <c r="D106" s="0" t="inlineStr">
         <is>
-          <t>战斗Boss展示</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>55002</v>
+        <v>54001</v>
       </c>
       <c r="B107" s="0" t="n">
-        <v>55002</v>
+        <v>54001</v>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
-          <t>一大波勇者正在靠近中…</t>
+          <t>没有可孕育的生物</t>
         </is>
       </c>
       <c r="D107" s="0" t="inlineStr">
@@ -2987,32 +2987,32 @@
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>55003</v>
+        <v>55001</v>
       </c>
       <c r="B108" s="0" t="n">
-        <v>55003</v>
+        <v>55001</v>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
-          <t>注意！英雄队伍正在涌来…</t>
+          <t>魔王讨伐者正在靠近中...</t>
         </is>
       </c>
       <c r="D108" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗Boss展示</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>55004</v>
+        <v>55002</v>
       </c>
       <c r="B109" s="0" t="n">
-        <v>55004</v>
+        <v>55002</v>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
-          <t>侦测到讨伐部队正在接近…</t>
+          <t>一大波勇者正在靠近中…</t>
         </is>
       </c>
       <c r="D109" s="0" t="inlineStr">
@@ -3023,14 +3023,14 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>55005</v>
+        <v>55003</v>
       </c>
       <c r="B110" s="0" t="n">
-        <v>55005</v>
+        <v>55003</v>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
-          <t>勇者联军正在逼近…</t>
+          <t>注意！英雄队伍正在涌来…</t>
         </is>
       </c>
       <c r="D110" s="0" t="inlineStr">
@@ -3041,14 +3041,14 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>55006</v>
+        <v>55004</v>
       </c>
       <c r="B111" s="0" t="n">
-        <v>55006</v>
+        <v>55004</v>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t>一大波自称勇者的家伙来了…</t>
+          <t>侦测到讨伐部队正在接近…</t>
         </is>
       </c>
       <c r="D111" s="0" t="inlineStr">
@@ -3059,14 +3059,14 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>55007</v>
+        <v>55005</v>
       </c>
       <c r="B112" s="0" t="n">
-        <v>55007</v>
+        <v>55005</v>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
-          <t>警报：正义的伙伴们正在靠近…</t>
+          <t>勇者联军正在逼近…</t>
         </is>
       </c>
       <c r="D112" s="0" t="inlineStr">
@@ -3077,32 +3077,32 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>60000</v>
+        <v>55006</v>
       </c>
       <c r="B113" s="0" t="n">
-        <v>60000</v>
+        <v>55006</v>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t>献祭升级</t>
+          <t>一大波自称勇者的家伙来了…</t>
         </is>
       </c>
       <c r="D113" s="0" t="inlineStr">
         <is>
-          <t>生物献祭</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>60001</v>
+        <v>55007</v>
       </c>
       <c r="B114" s="0" t="n">
-        <v>60001</v>
+        <v>55007</v>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t>开始献祭</t>
+          <t>警报：正义的伙伴们正在靠近…</t>
         </is>
       </c>
       <c r="D114" s="0" t="inlineStr">
@@ -3113,32 +3113,32 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>60002</v>
+        <v>60000</v>
       </c>
       <c r="B115" s="0" t="n">
-        <v>60002</v>
+        <v>60000</v>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>成功率</t>
+          <t>献祭升级</t>
         </is>
       </c>
       <c r="D115" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物献祭</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>61001</v>
+        <v>60001</v>
       </c>
       <c r="B116" s="0" t="n">
-        <v>61001</v>
+        <v>60001</v>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t>还未选择献祭生物！</t>
+          <t>开始献祭</t>
         </is>
       </c>
       <c r="D116" s="0" t="inlineStr">
@@ -3149,14 +3149,14 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>61002</v>
+        <v>60002</v>
       </c>
       <c r="B117" s="0" t="n">
-        <v>61002</v>
+        <v>60002</v>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
-          <t>献祭生物数量达到上限！</t>
+          <t>成功率</t>
         </is>
       </c>
       <c r="D117" s="0" t="inlineStr">
@@ -3167,14 +3167,14 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>61003</v>
+        <v>61001</v>
       </c>
       <c r="B118" s="0" t="n">
-        <v>61003</v>
+        <v>61001</v>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t>是否开始献祭？当前成功率{0}</t>
+          <t>还未选择献祭生物！</t>
         </is>
       </c>
       <c r="D118" s="0" t="inlineStr">
@@ -3185,32 +3185,32 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>62001</v>
+        <v>61002</v>
       </c>
       <c r="B119" s="0" t="n">
-        <v>62001</v>
+        <v>61002</v>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>是否开启此项研究？花费x{0}魔晶</t>
+          <t>献祭生物数量达到上限！</t>
         </is>
       </c>
       <c r="D119" s="0" t="inlineStr">
         <is>
-          <t>生物研究</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>62002</v>
+        <v>61003</v>
       </c>
       <c r="B120" s="0" t="n">
-        <v>62002</v>
+        <v>61003</v>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>设施</t>
+          <t>是否开始献祭？当前成功率{0}</t>
         </is>
       </c>
       <c r="D120" s="0" t="inlineStr">
@@ -3221,14 +3221,14 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>62003</v>
+        <v>61004</v>
       </c>
       <c r="B121" s="0" t="n">
-        <v>62003</v>
+        <v>61004</v>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>强化</t>
+          <t>请分配完所有属性点</t>
         </is>
       </c>
       <c r="D121" s="0" t="inlineStr">
@@ -3239,14 +3239,14 @@
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>62004</v>
+        <v>61005</v>
       </c>
       <c r="B122" s="0" t="n">
-        <v>62004</v>
+        <v>61005</v>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>魔物</t>
+          <t>剩余点数:{0}</t>
         </is>
       </c>
       <c r="D122" s="0" t="inlineStr">
@@ -3257,32 +3257,32 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>63001</v>
+        <v>62001</v>
       </c>
       <c r="B123" s="0" t="n">
-        <v>63001</v>
+        <v>62001</v>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>选择转生魔王外观</t>
+          <t>是否开启此项研究？花费x{0}魔晶</t>
         </is>
       </c>
       <c r="D123" s="0" t="inlineStr">
         <is>
-          <t>生物外貌修改</t>
+          <t>生物研究</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>63002</v>
+        <v>62002</v>
       </c>
       <c r="B124" s="0" t="n">
-        <v>63002</v>
+        <v>62002</v>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>设施</t>
         </is>
       </c>
       <c r="D124" s="0" t="inlineStr">
@@ -3293,14 +3293,14 @@
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>63003</v>
+        <v>62003</v>
       </c>
       <c r="B125" s="0" t="n">
-        <v>63003</v>
+        <v>62003</v>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>是否以此外观完成转生？</t>
+          <t>强化</t>
         </is>
       </c>
       <c r="D125" s="0" t="inlineStr">
@@ -3311,104 +3311,104 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>64001</v>
+        <v>62004</v>
       </c>
       <c r="B126" s="0" t="n">
-        <v>64001</v>
+        <v>62004</v>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>魔物</t>
         </is>
       </c>
       <c r="D126" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>64002</v>
+        <v>63001</v>
       </c>
       <c r="B127" s="0" t="n">
-        <v>64002</v>
+        <v>63001</v>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>统计</t>
+          <t>选择转生魔王外观</t>
         </is>
       </c>
       <c r="D127" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物外貌修改</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>70001</v>
+        <v>63002</v>
       </c>
       <c r="B128" s="0" t="n">
-        <v>70001</v>
+        <v>63002</v>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>贿赂</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D128" s="0" t="inlineStr">
         <is>
-          <t>对话</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>80001</v>
+        <v>63003</v>
       </c>
       <c r="B129" s="0" t="n">
-        <v>80001</v>
+        <v>63003</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>开始进阶</t>
+          <t>是否以此外观完成转生？</t>
         </is>
       </c>
       <c r="D129" s="0" t="inlineStr">
         <is>
-          <t>生物进阶</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>80002</v>
+        <v>64001</v>
       </c>
       <c r="B130" s="0" t="n">
-        <v>80002</v>
+        <v>64001</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>结束进阶</t>
+          <t>成就</t>
         </is>
       </c>
       <c r="D130" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>成就</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>80003</v>
+        <v>64002</v>
       </c>
       <c r="B131" s="0" t="n">
-        <v>80003</v>
+        <v>64002</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>完成进阶</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="D131" s="0" t="inlineStr">
@@ -3419,50 +3419,50 @@
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>80004</v>
+        <v>70001</v>
       </c>
       <c r="B132" s="0" t="n">
-        <v>80004</v>
+        <v>70001</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t>是否结束进阶？进阶消耗的材料不会返回</t>
+          <t>贿赂</t>
         </is>
       </c>
       <c r="D132" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>对话</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>80005</v>
+        <v>80001</v>
       </c>
       <c r="B133" s="0" t="n">
-        <v>80005</v>
+        <v>80001</v>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t>进度</t>
+          <t>开始进阶</t>
         </is>
       </c>
       <c r="D133" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物进阶</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>80006</v>
+        <v>80002</v>
       </c>
       <c r="B134" s="0" t="n">
-        <v>80006</v>
+        <v>80002</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t>选择进阶魔物</t>
+          <t>结束进阶</t>
         </is>
       </c>
       <c r="D134" s="0" t="inlineStr">
@@ -3473,14 +3473,14 @@
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>80007</v>
+        <v>80003</v>
       </c>
       <c r="B135" s="0" t="n">
-        <v>80007</v>
+        <v>80003</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t>选择辅助魔物</t>
+          <t>完成进阶</t>
         </is>
       </c>
       <c r="D135" s="0" t="inlineStr">
@@ -3491,14 +3491,14 @@
     </row>
     <row r="136" ht="12" customHeight="1" s="1">
       <c r="A136" s="0" t="n">
-        <v>80008</v>
+        <v>80004</v>
       </c>
       <c r="B136" s="0" t="n">
-        <v>80008</v>
+        <v>80004</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物</t>
+          <t>是否结束进阶？进阶消耗的材料不会返回</t>
         </is>
       </c>
       <c r="D136" s="0" t="inlineStr">
@@ -3509,14 +3509,14 @@
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>80009</v>
+        <v>80005</v>
       </c>
       <c r="B137" s="0" t="n">
-        <v>80009</v>
+        <v>80005</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t>加速进阶 x{0}</t>
+          <t>进度</t>
         </is>
       </c>
       <c r="D137" s="0" t="inlineStr">
@@ -3527,14 +3527,14 @@
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>80010</v>
+        <v>80006</v>
       </c>
       <c r="B138" s="0" t="n">
-        <v>80010</v>
+        <v>80006</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
+          <t>选择进阶魔物</t>
         </is>
       </c>
       <c r="D138" s="0" t="inlineStr">
@@ -3545,32 +3545,32 @@
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>90001</v>
+        <v>80007</v>
       </c>
       <c r="B139" s="0" t="n">
-        <v>90001</v>
+        <v>80007</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>选择辅助魔物</t>
         </is>
       </c>
       <c r="D139" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>90002</v>
+        <v>80008</v>
       </c>
       <c r="B140" s="0" t="n">
-        <v>90002</v>
+        <v>80008</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t>魔王专属</t>
+          <t>还未选择魔物</t>
         </is>
       </c>
       <c r="D140" s="0" t="inlineStr">
@@ -3581,32 +3581,32 @@
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>1000001</v>
+        <v>80009</v>
       </c>
       <c r="B141" s="0" t="n">
-        <v>1000001</v>
+        <v>80009</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>加速进阶 x{0}</t>
         </is>
       </c>
       <c r="D141" s="0" t="inlineStr">
         <is>
-          <t>弹窗</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>1000002</v>
+        <v>80010</v>
       </c>
       <c r="B142" s="0" t="n">
-        <v>1000002</v>
+        <v>80010</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
         </is>
       </c>
       <c r="D142" s="0" t="inlineStr">
@@ -3617,122 +3617,122 @@
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>1001001</v>
+        <v>90001</v>
       </c>
       <c r="B143" s="0" t="n">
-        <v>1001001</v>
+        <v>90001</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t>等级.{0}</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D143" s="0" t="inlineStr">
         <is>
-          <t>弹窗-卡片详情</t>
+          <t>通用</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>1002001</v>
+        <v>90002</v>
       </c>
       <c r="B144" s="0" t="n">
-        <v>1002001</v>
+        <v>90002</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t>赠送</t>
+          <t>魔王专属</t>
         </is>
       </c>
       <c r="D144" s="0" t="inlineStr">
         <is>
-          <t>弹窗-道具选择</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>1002002</v>
+        <v>1000001</v>
       </c>
       <c r="B145" s="0" t="n">
-        <v>1002002</v>
+        <v>1000001</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D145" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>1003001</v>
+        <v>1000002</v>
       </c>
       <c r="B146" s="0" t="n">
-        <v>1003001</v>
+        <v>1000002</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>研究等级.{0}</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="D146" s="0" t="inlineStr">
         <is>
-          <t>弹窗-研究详情</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>1003002</v>
+        <v>1001001</v>
       </c>
       <c r="B147" s="0" t="n">
-        <v>1003002</v>
+        <v>1001001</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t>研究等级.最大</t>
+          <t>等级.{0}</t>
         </is>
       </c>
       <c r="D147" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-卡片详情</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>1004001</v>
+        <v>1002001</v>
       </c>
       <c r="B148" s="0" t="n">
-        <v>1004001</v>
+        <v>1002001</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t>取个新名字</t>
+          <t>赠送</t>
         </is>
       </c>
       <c r="D148" s="0" t="inlineStr">
         <is>
-          <t>弹窗-重命名</t>
+          <t>弹窗-道具选择</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>1004002</v>
+        <v>1002002</v>
       </c>
       <c r="B149" s="0" t="n">
-        <v>1004002</v>
+        <v>1002002</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>输入名字...</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="D149" s="0" t="inlineStr">
@@ -3743,32 +3743,32 @@
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>1005001</v>
+        <v>1003001</v>
       </c>
       <c r="B150" s="0" t="n">
-        <v>1005001</v>
+        <v>1003001</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t>选择魔物</t>
+          <t>研究等级.{0}</t>
         </is>
       </c>
       <c r="D150" s="0" t="inlineStr">
         <is>
-          <t>弹窗-生物选择</t>
+          <t>弹窗-研究详情</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>1005002</v>
+        <v>1003002</v>
       </c>
       <c r="B151" s="0" t="n">
-        <v>1005002</v>
+        <v>1003002</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>当前选择数量{0}/{1}</t>
+          <t>研究等级.最大</t>
         </is>
       </c>
       <c r="D151" s="0" t="inlineStr">
@@ -3779,68 +3779,68 @@
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>1005003</v>
+        <v>1004001</v>
       </c>
       <c r="B152" s="0" t="n">
-        <v>1005003</v>
+        <v>1004001</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>超过选择数量上限</t>
+          <t>取个新名字</t>
         </is>
       </c>
       <c r="D152" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-重命名</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>2000001</v>
+        <v>1004002</v>
       </c>
       <c r="B153" s="0" t="n">
-        <v>2000001</v>
+        <v>1004002</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t>提示</t>
+          <t>输入名字...</t>
         </is>
       </c>
       <c r="D153" s="0" t="inlineStr">
         <is>
-          <t>popup</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>2000002</v>
+        <v>1005001</v>
       </c>
       <c r="B154" s="0" t="n">
-        <v>2000002</v>
+        <v>1005001</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>魔晶</t>
+          <t>选择魔物</t>
         </is>
       </c>
       <c r="D154" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-生物选择</t>
         </is>
       </c>
     </row>
     <row r="155" ht="12" customHeight="1" s="1">
       <c r="A155" s="0" t="n">
-        <v>2000003</v>
+        <v>1005002</v>
       </c>
       <c r="B155" s="0" t="n">
-        <v>2000003</v>
+        <v>1005002</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>声望</t>
+          <t>当前选择数量{0}/{1}</t>
         </is>
       </c>
       <c r="D155" s="0" t="inlineStr">
@@ -3851,14 +3851,14 @@
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>2000004</v>
+        <v>1005003</v>
       </c>
       <c r="B156" s="0" t="n">
-        <v>2000004</v>
+        <v>1005003</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t>排序：稀有度</t>
+          <t>超过选择数量上限</t>
         </is>
       </c>
       <c r="D156" s="0" t="inlineStr">
@@ -3869,32 +3869,32 @@
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>2000005</v>
+        <v>2000001</v>
       </c>
       <c r="B157" s="0" t="n">
-        <v>2000005</v>
+        <v>2000001</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>排序：等级</t>
+          <t>提示</t>
         </is>
       </c>
       <c r="D157" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>popup</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>2000006</v>
+        <v>2000002</v>
       </c>
       <c r="B158" s="0" t="n">
-        <v>2000006</v>
+        <v>2000002</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>排序：阵容</t>
+          <t>魔晶</t>
         </is>
       </c>
       <c r="D158" s="0" t="inlineStr">
@@ -3905,14 +3905,14 @@
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>2000007</v>
+        <v>2000003</v>
       </c>
       <c r="B159" s="0" t="n">
-        <v>2000007</v>
+        <v>2000003</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t>排序：名字</t>
+          <t>声望</t>
         </is>
       </c>
       <c r="D159" s="0" t="inlineStr">
@@ -3923,14 +3923,14 @@
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>2000008</v>
+        <v>2000004</v>
       </c>
       <c r="B160" s="0" t="n">
-        <v>2000008</v>
+        <v>2000004</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>稀有度:{0}</t>
+          <t>排序：稀有度</t>
         </is>
       </c>
       <c r="D160" s="0" t="inlineStr">
@@ -3941,14 +3941,14 @@
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>2000009</v>
+        <v>2000005</v>
       </c>
       <c r="B161" s="0" t="n">
-        <v>2000009</v>
+        <v>2000005</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>所属:{0}</t>
+          <t>排序：等级</t>
         </is>
       </c>
       <c r="D161" s="0" t="inlineStr">
@@ -3959,14 +3959,14 @@
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>2000010</v>
+        <v>2000006</v>
       </c>
       <c r="B162" s="0" t="n">
-        <v>2000010</v>
+        <v>2000006</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>道具名字:{0}</t>
+          <t>排序：阵容</t>
         </is>
       </c>
       <c r="D162" s="0" t="inlineStr">
@@ -3976,18 +3976,18 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="n">
-        <v>2000011</v>
-      </c>
-      <c r="B163" t="n">
-        <v>2000011</v>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>排序：同类</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
+      <c r="A163" s="0" t="n">
+        <v>2000007</v>
+      </c>
+      <c r="B163" s="0" t="n">
+        <v>2000007</v>
+      </c>
+      <c r="C163" s="0" t="inlineStr">
+        <is>
+          <t>排序：名字</t>
+        </is>
+      </c>
+      <c r="D163" s="0" t="inlineStr">
         <is>
           <t>|</t>
         </is>
@@ -3995,32 +3995,32 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>3000001</v>
+        <v>2000008</v>
       </c>
       <c r="B164" s="0" t="n">
-        <v>3000001</v>
+        <v>2000008</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>没有足够的魔晶</t>
+          <t>稀有度:{0}</t>
         </is>
       </c>
       <c r="D164" s="0" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>3000002</v>
+        <v>2000009</v>
       </c>
       <c r="B165" s="0" t="n">
-        <v>3000002</v>
+        <v>2000009</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
+          <t>所属:{0}</t>
         </is>
       </c>
       <c r="D165" s="0" t="inlineStr">
@@ -4031,14 +4031,14 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>3000003</v>
+        <v>2000010</v>
       </c>
       <c r="B166" s="0" t="n">
-        <v>3000003</v>
+        <v>2000010</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>修改名字成功！</t>
+          <t>道具名字:{0}</t>
         </is>
       </c>
       <c r="D166" s="0" t="inlineStr">
@@ -4049,14 +4049,14 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>3000004</v>
+        <v>2000011</v>
       </c>
       <c r="B167" s="0" t="n">
-        <v>3000004</v>
+        <v>2000011</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物！</t>
+          <t>排序：同类</t>
         </is>
       </c>
       <c r="D167" s="0" t="inlineStr">
@@ -4067,50 +4067,50 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>3000005</v>
+        <v>3000001</v>
       </c>
       <c r="B168" s="0" t="n">
-        <v>3000005</v>
+        <v>3000001</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>转生成功！</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="D168" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>4000006</v>
+        <v>3000002</v>
       </c>
       <c r="B169" s="0" t="n">
-        <v>4000006</v>
+        <v>3000002</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="D169" s="0" t="inlineStr">
         <is>
-          <t>Achievement-进度</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>4000008</v>
+        <v>3000003</v>
       </c>
       <c r="B170" s="0" t="n">
-        <v>4000008</v>
+        <v>3000003</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>领取成功！</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="D170" s="0" t="inlineStr">
@@ -4121,14 +4121,14 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>4000010</v>
+        <v>3000004</v>
       </c>
       <c r="B171" s="0" t="n">
-        <v>4000010</v>
+        <v>3000004</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>游玩时间</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="D171" s="0" t="inlineStr">
@@ -4139,14 +4139,14 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>4000011</v>
+        <v>3000005</v>
       </c>
       <c r="B172" s="0" t="n">
-        <v>4000011</v>
+        <v>3000005</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>总击杀数</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="D172" s="0" t="inlineStr">
@@ -4157,32 +4157,32 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>4000012</v>
+        <v>4000006</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>4000012</v>
+        <v>4000006</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>征服通关</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="D173" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Achievement-进度</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>4000013</v>
+        <v>4000008</v>
       </c>
       <c r="B174" s="0" t="n">
-        <v>4000013</v>
+        <v>4000008</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>难度{0}</t>
+          <t>领取成功！</t>
         </is>
       </c>
       <c r="D174" s="0" t="inlineStr">
@@ -4193,14 +4193,14 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>4000014</v>
+        <v>4000010</v>
       </c>
       <c r="B175" s="0" t="n">
-        <v>4000014</v>
+        <v>4000010</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>游玩时间</t>
         </is>
       </c>
       <c r="D175" s="0" t="inlineStr">
@@ -4211,17 +4211,89 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
+        <v>4000011</v>
+      </c>
+      <c r="B176" s="0" t="n">
+        <v>4000011</v>
+      </c>
+      <c r="C176" s="0" t="inlineStr">
+        <is>
+          <t>总击杀数</t>
+        </is>
+      </c>
+      <c r="D176" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="0" t="n">
+        <v>4000012</v>
+      </c>
+      <c r="B177" s="0" t="n">
+        <v>4000012</v>
+      </c>
+      <c r="C177" s="0" t="inlineStr">
+        <is>
+          <t>征服通关</t>
+        </is>
+      </c>
+      <c r="D177" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="0" t="n">
+        <v>4000013</v>
+      </c>
+      <c r="B178" s="0" t="n">
+        <v>4000013</v>
+      </c>
+      <c r="C178" s="0" t="inlineStr">
+        <is>
+          <t>难度{0}</t>
+        </is>
+      </c>
+      <c r="D178" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="B179" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="C179" s="0" t="inlineStr">
+        <is>
+          <t>{0}时{1}分</t>
+        </is>
+      </c>
+      <c r="D179" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="0" t="n">
         <v>4000015</v>
       </c>
-      <c r="B176" s="0" t="n">
+      <c r="B180" s="0" t="n">
         <v>4000015</v>
       </c>
-      <c r="C176" s="0" t="inlineStr">
+      <c r="C180" s="0" t="inlineStr">
         <is>
           <t>总通关次数</t>
         </is>
       </c>
-      <c r="D176" s="0" t="inlineStr">
+      <c r="D180" s="0" t="inlineStr">
         <is>
           <t>|</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D180"/>
+  <dimension ref="A1:D183"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.375" customWidth="1" style="1" min="1" max="1"/>
@@ -2554,18 +2554,18 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
+      <c r="A84" s="0" t="n">
         <v>50006</v>
       </c>
-      <c r="B84" t="n">
+      <c r="B84" s="0" t="n">
         <v>50006</v>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="0" t="inlineStr">
         <is>
           <t>魔力不足</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" s="0" t="inlineStr">
         <is>
           <t>|</t>
         </is>
@@ -4067,32 +4067,32 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>3000001</v>
+        <v>2000012</v>
       </c>
       <c r="B168" s="0" t="n">
-        <v>3000001</v>
+        <v>2000012</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>没有足够的魔晶</t>
+          <t>正序</t>
         </is>
       </c>
       <c r="D168" s="0" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>3000002</v>
+        <v>2000013</v>
       </c>
       <c r="B169" s="0" t="n">
-        <v>3000002</v>
+        <v>2000013</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
+          <t>倒序</t>
         </is>
       </c>
       <c r="D169" s="0" t="inlineStr">
@@ -4102,18 +4102,18 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="0" t="n">
-        <v>3000003</v>
-      </c>
-      <c r="B170" s="0" t="n">
-        <v>3000003</v>
-      </c>
-      <c r="C170" s="0" t="inlineStr">
-        <is>
-          <t>修改名字成功！</t>
-        </is>
-      </c>
-      <c r="D170" s="0" t="inlineStr">
+      <c r="A170" t="n">
+        <v>2000014</v>
+      </c>
+      <c r="B170" t="n">
+        <v>2000014</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>筛选排序</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
         <is>
           <t>|</t>
         </is>
@@ -4121,32 +4121,32 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>3000004</v>
+        <v>3000001</v>
       </c>
       <c r="B171" s="0" t="n">
-        <v>3000004</v>
+        <v>3000001</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物！</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="D171" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>3000005</v>
+        <v>3000002</v>
       </c>
       <c r="B172" s="0" t="n">
-        <v>3000005</v>
+        <v>3000002</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>转生成功！</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="D172" s="0" t="inlineStr">
@@ -4157,32 +4157,32 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>4000006</v>
+        <v>3000003</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>4000006</v>
+        <v>3000003</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="D173" s="0" t="inlineStr">
         <is>
-          <t>Achievement-进度</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>4000008</v>
+        <v>3000004</v>
       </c>
       <c r="B174" s="0" t="n">
-        <v>4000008</v>
+        <v>3000004</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>领取成功！</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="D174" s="0" t="inlineStr">
@@ -4193,14 +4193,14 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>4000010</v>
+        <v>3000005</v>
       </c>
       <c r="B175" s="0" t="n">
-        <v>4000010</v>
+        <v>3000005</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>游玩时间</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="D175" s="0" t="inlineStr">
@@ -4211,32 +4211,32 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>4000011</v>
+        <v>4000006</v>
       </c>
       <c r="B176" s="0" t="n">
-        <v>4000011</v>
+        <v>4000006</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>总击杀数</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="D176" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Achievement-进度</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>4000012</v>
+        <v>4000008</v>
       </c>
       <c r="B177" s="0" t="n">
-        <v>4000012</v>
+        <v>4000008</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>征服通关</t>
+          <t>领取成功！</t>
         </is>
       </c>
       <c r="D177" s="0" t="inlineStr">
@@ -4247,14 +4247,14 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>4000013</v>
+        <v>4000010</v>
       </c>
       <c r="B178" s="0" t="n">
-        <v>4000013</v>
+        <v>4000010</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t>难度{0}</t>
+          <t>游玩时间</t>
         </is>
       </c>
       <c r="D178" s="0" t="inlineStr">
@@ -4265,14 +4265,14 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>4000014</v>
+        <v>4000011</v>
       </c>
       <c r="B179" s="0" t="n">
-        <v>4000014</v>
+        <v>4000011</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>总击杀数</t>
         </is>
       </c>
       <c r="D179" s="0" t="inlineStr">
@@ -4283,17 +4283,71 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
+        <v>4000012</v>
+      </c>
+      <c r="B180" s="0" t="n">
+        <v>4000012</v>
+      </c>
+      <c r="C180" s="0" t="inlineStr">
+        <is>
+          <t>征服通关</t>
+        </is>
+      </c>
+      <c r="D180" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="0" t="n">
+        <v>4000013</v>
+      </c>
+      <c r="B181" s="0" t="n">
+        <v>4000013</v>
+      </c>
+      <c r="C181" s="0" t="inlineStr">
+        <is>
+          <t>难度{0}</t>
+        </is>
+      </c>
+      <c r="D181" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="B182" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="C182" s="0" t="inlineStr">
+        <is>
+          <t>{0}时{1}分</t>
+        </is>
+      </c>
+      <c r="D182" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="0" t="n">
         <v>4000015</v>
       </c>
-      <c r="B180" s="0" t="n">
+      <c r="B183" s="0" t="n">
         <v>4000015</v>
       </c>
-      <c r="C180" s="0" t="inlineStr">
+      <c r="C183" s="0" t="inlineStr">
         <is>
           <t>总通关次数</t>
         </is>
       </c>
-      <c r="D180" s="0" t="inlineStr">
+      <c r="D183" s="0" t="inlineStr">
         <is>
           <t>|</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D183"/>
+  <dimension ref="A1:D184"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.375" customWidth="1" style="1" min="1" max="1"/>
@@ -2194,51 +2194,51 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="0" t="n">
-        <v>40001</v>
-      </c>
-      <c r="B64" s="0" t="n">
-        <v>40001</v>
-      </c>
-      <c r="C64" s="0" t="inlineStr">
-        <is>
-          <t>游戏</t>
-        </is>
-      </c>
-      <c r="D64" s="0" t="inlineStr">
-        <is>
-          <t>游戏设置</t>
+      <c r="A64" t="n">
+        <v>30007</v>
+      </c>
+      <c r="B64" t="n">
+        <v>30007</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>阵容魔物数量 {0}</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>40002</v>
+        <v>40001</v>
       </c>
       <c r="B65" s="0" t="n">
-        <v>40002</v>
+        <v>40001</v>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t>画面</t>
+          <t>游戏</t>
         </is>
       </c>
       <c r="D65" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>游戏设置</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>40003</v>
+        <v>40002</v>
       </c>
       <c r="B66" s="0" t="n">
-        <v>40003</v>
+        <v>40002</v>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t>音频</t>
+          <t>画面</t>
         </is>
       </c>
       <c r="D66" s="0" t="inlineStr">
@@ -2249,14 +2249,14 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>40998</v>
+        <v>40003</v>
       </c>
       <c r="B67" s="0" t="n">
-        <v>40998</v>
+        <v>40003</v>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t>已开启</t>
+          <t>音频</t>
         </is>
       </c>
       <c r="D67" s="0" t="inlineStr">
@@ -2267,14 +2267,14 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>40999</v>
+        <v>40998</v>
       </c>
       <c r="B68" s="0" t="n">
-        <v>40999</v>
+        <v>40998</v>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>已关闭</t>
+          <t>已开启</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
@@ -2285,14 +2285,14 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>41001</v>
+        <v>40999</v>
       </c>
       <c r="B69" s="0" t="n">
-        <v>41001</v>
+        <v>40999</v>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>语言</t>
+          <t>已关闭</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
@@ -2303,14 +2303,14 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>42001</v>
+        <v>41001</v>
       </c>
       <c r="B70" s="0" t="n">
-        <v>42001</v>
+        <v>41001</v>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>屏幕分辨率</t>
+          <t>语言</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
@@ -2321,14 +2321,14 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
-        <v>42002</v>
+        <v>42001</v>
       </c>
       <c r="B71" s="0" t="n">
-        <v>42002</v>
+        <v>42001</v>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>锁定帧数</t>
+          <t>屏幕分辨率</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
@@ -2339,14 +2339,14 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>42003</v>
+        <v>42002</v>
       </c>
       <c r="B72" s="0" t="n">
-        <v>42003</v>
+        <v>42002</v>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>帧数</t>
+          <t>锁定帧数</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
@@ -2357,14 +2357,14 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>43001</v>
+        <v>42003</v>
       </c>
       <c r="B73" s="0" t="n">
-        <v>43001</v>
+        <v>42003</v>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>音乐音量</t>
+          <t>帧数</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
@@ -2375,14 +2375,14 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>43002</v>
+        <v>43001</v>
       </c>
       <c r="B74" s="0" t="n">
-        <v>43002</v>
+        <v>43001</v>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>音效音量</t>
+          <t>音乐音量</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
@@ -2393,50 +2393,50 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>49001</v>
+        <v>43002</v>
       </c>
       <c r="B75" s="0" t="n">
-        <v>49001</v>
+        <v>43002</v>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>游戏设置</t>
+          <t>音效音量</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
         <is>
-          <t>游戏系统</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>49002</v>
+        <v>49001</v>
       </c>
       <c r="B76" s="0" t="n">
-        <v>49002</v>
+        <v>49001</v>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>返回主界面</t>
+          <t>游戏设置</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>游戏系统</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>49003</v>
+        <v>49002</v>
       </c>
       <c r="B77" s="0" t="n">
-        <v>49003</v>
+        <v>49002</v>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>退出游戏</t>
+          <t>返回主界面</t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
@@ -2447,14 +2447,14 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>49004</v>
+        <v>49003</v>
       </c>
       <c r="B78" s="0" t="n">
-        <v>49004</v>
+        <v>49003</v>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>退出战斗</t>
+          <t>退出游戏</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">
@@ -2465,50 +2465,50 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>50001</v>
+        <v>49004</v>
       </c>
       <c r="B79" s="0" t="n">
-        <v>50001</v>
+        <v>49004</v>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>退出战斗</t>
         </is>
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t>战斗结算界面</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="B80" s="0" t="n">
-        <v>50002</v>
+        <v>50001</v>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>击杀</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="D80" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗结算界面</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="B81" s="0" t="n">
-        <v>50003</v>
+        <v>50002</v>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t>经验</t>
+          <t>击杀</t>
         </is>
       </c>
       <c r="D81" s="0" t="inlineStr">
@@ -2519,14 +2519,14 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="B82" s="0" t="n">
-        <v>50004</v>
+        <v>50003</v>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>承伤</t>
+          <t>经验</t>
         </is>
       </c>
       <c r="D82" s="0" t="inlineStr">
@@ -2537,50 +2537,50 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>50005</v>
+        <v>50004</v>
       </c>
       <c r="B83" s="0" t="n">
-        <v>50005</v>
+        <v>50004</v>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t>当前征程：{0}/{1}</t>
+          <t>承伤</t>
         </is>
       </c>
       <c r="D83" s="0" t="inlineStr">
         <is>
-          <t>战斗主界面</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>50006</v>
+        <v>50005</v>
       </c>
       <c r="B84" s="0" t="n">
-        <v>50006</v>
+        <v>50005</v>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>魔力不足</t>
+          <t>当前征程：{0}/{1}</t>
         </is>
       </c>
       <c r="D84" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗主界面</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>50101</v>
+        <v>50006</v>
       </c>
       <c r="B85" s="0" t="n">
-        <v>50101</v>
+        <v>50006</v>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>继续</t>
+          <t>魔力不足</t>
         </is>
       </c>
       <c r="D85" s="0" t="inlineStr">
@@ -2591,50 +2591,50 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>51001</v>
+        <v>50101</v>
       </c>
       <c r="B86" s="0" t="n">
-        <v>51001</v>
+        <v>50101</v>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>深渊馈赠</t>
+          <t>继续</t>
         </is>
       </c>
       <c r="D86" s="0" t="inlineStr">
         <is>
-          <t>战斗深渊馈赠</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="87" ht="12" customHeight="1" s="1">
       <c r="A87" s="0" t="n">
-        <v>51002</v>
+        <v>51001</v>
       </c>
       <c r="B87" s="0" t="n">
-        <v>51002</v>
+        <v>51001</v>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>选择一个深渊馈赠</t>
+          <t>深渊馈赠</t>
         </is>
       </c>
       <c r="D87" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗深渊馈赠</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>51003</v>
+        <v>51002</v>
       </c>
       <c r="B88" s="0" t="n">
-        <v>51003</v>
+        <v>51002</v>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t>跳过</t>
+          <t>选择一个深渊馈赠</t>
         </is>
       </c>
       <c r="D88" s="0" t="inlineStr">
@@ -2645,50 +2645,50 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>52001</v>
+        <v>51003</v>
       </c>
       <c r="B89" s="0" t="n">
-        <v>52001</v>
+        <v>51003</v>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>选择奖励</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="D89" s="0" t="inlineStr">
         <is>
-          <t>奖励选择</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>52002</v>
+        <v>52001</v>
       </c>
       <c r="B90" s="0" t="n">
-        <v>52002</v>
+        <v>52001</v>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>跳过</t>
+          <t>选择奖励</t>
         </is>
       </c>
       <c r="D90" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>奖励选择</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>52003</v>
+        <v>52002</v>
       </c>
       <c r="B91" s="0" t="n">
-        <v>52003</v>
+        <v>52002</v>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t>剩余可选择次数{0}/{1}</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="D91" s="0" t="inlineStr">
@@ -2699,14 +2699,14 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>52004</v>
+        <v>52003</v>
       </c>
       <c r="B92" s="0" t="n">
-        <v>52004</v>
+        <v>52003</v>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t>没有可选择次数</t>
+          <t>剩余可选择次数{0}/{1}</t>
         </is>
       </c>
       <c r="D92" s="0" t="inlineStr">
@@ -2717,14 +2717,14 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>52005</v>
+        <v>52004</v>
       </c>
       <c r="B93" s="0" t="n">
-        <v>52005</v>
+        <v>52004</v>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t>还有可选择次数，是否仍要结束选择奖励？</t>
+          <t>没有可选择次数</t>
         </is>
       </c>
       <c r="D93" s="0" t="inlineStr">
@@ -2735,50 +2735,50 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>53000</v>
+        <v>52005</v>
       </c>
       <c r="B94" s="0" t="n">
-        <v>53000</v>
+        <v>52005</v>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t>终焉议会</t>
+          <t>还有可选择次数，是否仍要结束选择奖励？</t>
         </is>
       </c>
       <c r="D94" s="0" t="inlineStr">
         <is>
-          <t>终焉议会</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>53001</v>
+        <v>53000</v>
       </c>
       <c r="B95" s="0" t="n">
-        <v>53001</v>
+        <v>53000</v>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t>选择一个议案</t>
+          <t>终焉议会</t>
         </is>
       </c>
       <c r="D95" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>终焉议会</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>53002</v>
+        <v>53001</v>
       </c>
       <c r="B96" s="0" t="n">
-        <v>53002</v>
+        <v>53001</v>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t>是否提交议案《{0}》，并且前往终焉议会？</t>
+          <t>选择一个议案</t>
         </is>
       </c>
       <c r="D96" s="0" t="inlineStr">
@@ -2789,14 +2789,14 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>53003</v>
+        <v>53002</v>
       </c>
       <c r="B97" s="0" t="n">
-        <v>53003</v>
+        <v>53002</v>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>通过率   {0}%</t>
+          <t>是否提交议案《{0}》，并且前往终焉议会？</t>
         </is>
       </c>
       <c r="D97" s="0" t="inlineStr">
@@ -2807,14 +2807,14 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>53004</v>
+        <v>53003</v>
       </c>
       <c r="B98" s="0" t="n">
-        <v>53004</v>
+        <v>53003</v>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>开始投票</t>
+          <t>通过率   {0}%</t>
         </is>
       </c>
       <c r="D98" s="0" t="inlineStr">
@@ -2825,14 +2825,14 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>53005</v>
+        <v>53004</v>
       </c>
       <c r="B99" s="0" t="n">
-        <v>53005</v>
+        <v>53004</v>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
-          <t>离开议会</t>
+          <t>开始投票</t>
         </is>
       </c>
       <c r="D99" s="0" t="inlineStr">
@@ -2843,14 +2843,14 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>53006</v>
+        <v>53005</v>
       </c>
       <c r="B100" s="0" t="n">
-        <v>53006</v>
+        <v>53005</v>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
-          <t>赞成</t>
+          <t>离开议会</t>
         </is>
       </c>
       <c r="D100" s="0" t="inlineStr">
@@ -2861,14 +2861,14 @@
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>53007</v>
+        <v>53006</v>
       </c>
       <c r="B101" s="0" t="n">
-        <v>53007</v>
+        <v>53006</v>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
-          <t>反对</t>
+          <t>赞成</t>
         </is>
       </c>
       <c r="D101" s="0" t="inlineStr">
@@ -2879,14 +2879,14 @@
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>53008</v>
+        <v>53007</v>
       </c>
       <c r="B102" s="0" t="n">
-        <v>53008</v>
+        <v>53007</v>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>反对</t>
         </is>
       </c>
       <c r="D102" s="0" t="inlineStr">
@@ -2897,14 +2897,14 @@
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>53009</v>
+        <v>53008</v>
       </c>
       <c r="B103" s="0" t="n">
-        <v>53009</v>
+        <v>53008</v>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
-          <t>否决</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="D103" s="0" t="inlineStr">
@@ -2915,14 +2915,14 @@
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>53010</v>
+        <v>53009</v>
       </c>
       <c r="B104" s="0" t="n">
-        <v>53010</v>
+        <v>53009</v>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
-          <t>暴力说服</t>
+          <t>否决</t>
         </is>
       </c>
       <c r="D104" s="0" t="inlineStr">
@@ -2933,14 +2933,14 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>53011</v>
+        <v>53010</v>
       </c>
       <c r="B105" s="0" t="n">
-        <v>53011</v>
+        <v>53010</v>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
-          <t>自由活动</t>
+          <t>暴力说服</t>
         </is>
       </c>
       <c r="D105" s="0" t="inlineStr">
@@ -2951,14 +2951,14 @@
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>53012</v>
+        <v>53011</v>
       </c>
       <c r="B106" s="0" t="n">
-        <v>53012</v>
+        <v>53011</v>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
-          <t>是否提交议案《{0}》？</t>
+          <t>自由活动</t>
         </is>
       </c>
       <c r="D106" s="0" t="inlineStr">
@@ -2969,14 +2969,14 @@
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>54001</v>
+        <v>53012</v>
       </c>
       <c r="B107" s="0" t="n">
-        <v>54001</v>
+        <v>53012</v>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
-          <t>没有可孕育的生物</t>
+          <t>是否提交议案《{0}》？</t>
         </is>
       </c>
       <c r="D107" s="0" t="inlineStr">
@@ -2987,50 +2987,50 @@
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>55001</v>
+        <v>54001</v>
       </c>
       <c r="B108" s="0" t="n">
-        <v>55001</v>
+        <v>54001</v>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
-          <t>魔王讨伐者正在靠近中...</t>
+          <t>没有可孕育的生物</t>
         </is>
       </c>
       <c r="D108" s="0" t="inlineStr">
         <is>
-          <t>战斗Boss展示</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>55002</v>
+        <v>55001</v>
       </c>
       <c r="B109" s="0" t="n">
-        <v>55002</v>
+        <v>55001</v>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
-          <t>一大波勇者正在靠近中…</t>
+          <t>魔王讨伐者正在靠近中...</t>
         </is>
       </c>
       <c r="D109" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗Boss展示</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>55003</v>
+        <v>55002</v>
       </c>
       <c r="B110" s="0" t="n">
-        <v>55003</v>
+        <v>55002</v>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
-          <t>注意！英雄队伍正在涌来…</t>
+          <t>一大波勇者正在靠近中…</t>
         </is>
       </c>
       <c r="D110" s="0" t="inlineStr">
@@ -3041,14 +3041,14 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>55004</v>
+        <v>55003</v>
       </c>
       <c r="B111" s="0" t="n">
-        <v>55004</v>
+        <v>55003</v>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t>侦测到讨伐部队正在接近…</t>
+          <t>注意！英雄队伍正在涌来…</t>
         </is>
       </c>
       <c r="D111" s="0" t="inlineStr">
@@ -3059,14 +3059,14 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>55005</v>
+        <v>55004</v>
       </c>
       <c r="B112" s="0" t="n">
-        <v>55005</v>
+        <v>55004</v>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
-          <t>勇者联军正在逼近…</t>
+          <t>侦测到讨伐部队正在接近…</t>
         </is>
       </c>
       <c r="D112" s="0" t="inlineStr">
@@ -3077,14 +3077,14 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>55006</v>
+        <v>55005</v>
       </c>
       <c r="B113" s="0" t="n">
-        <v>55006</v>
+        <v>55005</v>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t>一大波自称勇者的家伙来了…</t>
+          <t>勇者联军正在逼近…</t>
         </is>
       </c>
       <c r="D113" s="0" t="inlineStr">
@@ -3095,14 +3095,14 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>55007</v>
+        <v>55006</v>
       </c>
       <c r="B114" s="0" t="n">
-        <v>55007</v>
+        <v>55006</v>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t>警报：正义的伙伴们正在靠近…</t>
+          <t>一大波自称勇者的家伙来了…</t>
         </is>
       </c>
       <c r="D114" s="0" t="inlineStr">
@@ -3113,50 +3113,50 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>60000</v>
+        <v>55007</v>
       </c>
       <c r="B115" s="0" t="n">
-        <v>60000</v>
+        <v>55007</v>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>献祭升级</t>
+          <t>警报：正义的伙伴们正在靠近…</t>
         </is>
       </c>
       <c r="D115" s="0" t="inlineStr">
         <is>
-          <t>生物献祭</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>60001</v>
+        <v>60000</v>
       </c>
       <c r="B116" s="0" t="n">
-        <v>60001</v>
+        <v>60000</v>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t>开始献祭</t>
+          <t>献祭升级</t>
         </is>
       </c>
       <c r="D116" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物献祭</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>60002</v>
+        <v>60001</v>
       </c>
       <c r="B117" s="0" t="n">
-        <v>60002</v>
+        <v>60001</v>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
-          <t>成功率</t>
+          <t>开始献祭</t>
         </is>
       </c>
       <c r="D117" s="0" t="inlineStr">
@@ -3167,14 +3167,14 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>61001</v>
+        <v>60002</v>
       </c>
       <c r="B118" s="0" t="n">
-        <v>61001</v>
+        <v>60002</v>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t>还未选择献祭生物！</t>
+          <t>成功率</t>
         </is>
       </c>
       <c r="D118" s="0" t="inlineStr">
@@ -3185,14 +3185,14 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>61002</v>
+        <v>61001</v>
       </c>
       <c r="B119" s="0" t="n">
-        <v>61002</v>
+        <v>61001</v>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>献祭生物数量达到上限！</t>
+          <t>还未选择献祭生物！</t>
         </is>
       </c>
       <c r="D119" s="0" t="inlineStr">
@@ -3203,14 +3203,14 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>61003</v>
+        <v>61002</v>
       </c>
       <c r="B120" s="0" t="n">
-        <v>61003</v>
+        <v>61002</v>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>是否开始献祭？当前成功率{0}</t>
+          <t>献祭生物数量达到上限！</t>
         </is>
       </c>
       <c r="D120" s="0" t="inlineStr">
@@ -3221,14 +3221,14 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>61004</v>
+        <v>61003</v>
       </c>
       <c r="B121" s="0" t="n">
-        <v>61004</v>
+        <v>61003</v>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>请分配完所有属性点</t>
+          <t>是否开始献祭？当前成功率{0}</t>
         </is>
       </c>
       <c r="D121" s="0" t="inlineStr">
@@ -3239,14 +3239,14 @@
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>61005</v>
+        <v>61004</v>
       </c>
       <c r="B122" s="0" t="n">
-        <v>61005</v>
+        <v>61004</v>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>剩余点数:{0}</t>
+          <t>请分配完所有属性点</t>
         </is>
       </c>
       <c r="D122" s="0" t="inlineStr">
@@ -3257,50 +3257,50 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>62001</v>
+        <v>61005</v>
       </c>
       <c r="B123" s="0" t="n">
-        <v>62001</v>
+        <v>61005</v>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>是否开启此项研究？花费x{0}魔晶</t>
+          <t>剩余点数:{0}</t>
         </is>
       </c>
       <c r="D123" s="0" t="inlineStr">
         <is>
-          <t>生物研究</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>62002</v>
+        <v>62001</v>
       </c>
       <c r="B124" s="0" t="n">
-        <v>62002</v>
+        <v>62001</v>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>设施</t>
+          <t>是否开启此项研究？花费x{0}魔晶</t>
         </is>
       </c>
       <c r="D124" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物研究</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>62003</v>
+        <v>62002</v>
       </c>
       <c r="B125" s="0" t="n">
-        <v>62003</v>
+        <v>62002</v>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>强化</t>
+          <t>设施</t>
         </is>
       </c>
       <c r="D125" s="0" t="inlineStr">
@@ -3311,14 +3311,14 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>62004</v>
+        <v>62003</v>
       </c>
       <c r="B126" s="0" t="n">
-        <v>62004</v>
+        <v>62003</v>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>魔物</t>
+          <t>强化</t>
         </is>
       </c>
       <c r="D126" s="0" t="inlineStr">
@@ -3329,50 +3329,50 @@
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>63001</v>
+        <v>62004</v>
       </c>
       <c r="B127" s="0" t="n">
-        <v>63001</v>
+        <v>62004</v>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>选择转生魔王外观</t>
+          <t>魔物</t>
         </is>
       </c>
       <c r="D127" s="0" t="inlineStr">
         <is>
-          <t>生物外貌修改</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>63002</v>
+        <v>63001</v>
       </c>
       <c r="B128" s="0" t="n">
-        <v>63002</v>
+        <v>63001</v>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>选择转生魔王外观</t>
         </is>
       </c>
       <c r="D128" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物外貌修改</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>63003</v>
+        <v>63002</v>
       </c>
       <c r="B129" s="0" t="n">
-        <v>63003</v>
+        <v>63002</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>是否以此外观完成转生？</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D129" s="0" t="inlineStr">
@@ -3383,104 +3383,104 @@
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>64001</v>
+        <v>63003</v>
       </c>
       <c r="B130" s="0" t="n">
-        <v>64001</v>
+        <v>63003</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>是否以此外观完成转生？</t>
         </is>
       </c>
       <c r="D130" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>64002</v>
+        <v>64001</v>
       </c>
       <c r="B131" s="0" t="n">
-        <v>64002</v>
+        <v>64001</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>统计</t>
+          <t>成就</t>
         </is>
       </c>
       <c r="D131" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>成就</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>70001</v>
+        <v>64002</v>
       </c>
       <c r="B132" s="0" t="n">
-        <v>70001</v>
+        <v>64002</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t>贿赂</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="D132" s="0" t="inlineStr">
         <is>
-          <t>对话</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>80001</v>
+        <v>70001</v>
       </c>
       <c r="B133" s="0" t="n">
-        <v>80001</v>
+        <v>70001</v>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t>开始进阶</t>
+          <t>贿赂</t>
         </is>
       </c>
       <c r="D133" s="0" t="inlineStr">
         <is>
-          <t>生物进阶</t>
+          <t>对话</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>80002</v>
+        <v>80001</v>
       </c>
       <c r="B134" s="0" t="n">
-        <v>80002</v>
+        <v>80001</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t>结束进阶</t>
+          <t>开始进阶</t>
         </is>
       </c>
       <c r="D134" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物进阶</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>80003</v>
+        <v>80002</v>
       </c>
       <c r="B135" s="0" t="n">
-        <v>80003</v>
+        <v>80002</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t>完成进阶</t>
+          <t>结束进阶</t>
         </is>
       </c>
       <c r="D135" s="0" t="inlineStr">
@@ -3491,14 +3491,14 @@
     </row>
     <row r="136" ht="12" customHeight="1" s="1">
       <c r="A136" s="0" t="n">
-        <v>80004</v>
+        <v>80003</v>
       </c>
       <c r="B136" s="0" t="n">
-        <v>80004</v>
+        <v>80003</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t>是否结束进阶？进阶消耗的材料不会返回</t>
+          <t>完成进阶</t>
         </is>
       </c>
       <c r="D136" s="0" t="inlineStr">
@@ -3509,14 +3509,14 @@
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>80005</v>
+        <v>80004</v>
       </c>
       <c r="B137" s="0" t="n">
-        <v>80005</v>
+        <v>80004</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t>进度</t>
+          <t>是否结束进阶？进阶消耗的材料不会返回</t>
         </is>
       </c>
       <c r="D137" s="0" t="inlineStr">
@@ -3527,14 +3527,14 @@
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>80006</v>
+        <v>80005</v>
       </c>
       <c r="B138" s="0" t="n">
-        <v>80006</v>
+        <v>80005</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t>选择进阶魔物</t>
+          <t>进度</t>
         </is>
       </c>
       <c r="D138" s="0" t="inlineStr">
@@ -3545,14 +3545,14 @@
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>80007</v>
+        <v>80006</v>
       </c>
       <c r="B139" s="0" t="n">
-        <v>80007</v>
+        <v>80006</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t>选择辅助魔物</t>
+          <t>选择进阶魔物</t>
         </is>
       </c>
       <c r="D139" s="0" t="inlineStr">
@@ -3563,14 +3563,14 @@
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>80008</v>
+        <v>80007</v>
       </c>
       <c r="B140" s="0" t="n">
-        <v>80008</v>
+        <v>80007</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物</t>
+          <t>选择辅助魔物</t>
         </is>
       </c>
       <c r="D140" s="0" t="inlineStr">
@@ -3581,14 +3581,14 @@
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>80009</v>
+        <v>80008</v>
       </c>
       <c r="B141" s="0" t="n">
-        <v>80009</v>
+        <v>80008</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t>加速进阶 x{0}</t>
+          <t>还未选择魔物</t>
         </is>
       </c>
       <c r="D141" s="0" t="inlineStr">
@@ -3599,14 +3599,14 @@
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>80010</v>
+        <v>80009</v>
       </c>
       <c r="B142" s="0" t="n">
-        <v>80010</v>
+        <v>80009</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
+          <t>加速进阶 x{0}</t>
         </is>
       </c>
       <c r="D142" s="0" t="inlineStr">
@@ -3617,248 +3617,248 @@
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>90001</v>
+        <v>80010</v>
       </c>
       <c r="B143" s="0" t="n">
-        <v>90001</v>
+        <v>80010</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
         </is>
       </c>
       <c r="D143" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>90002</v>
+        <v>90001</v>
       </c>
       <c r="B144" s="0" t="n">
-        <v>90002</v>
+        <v>90001</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t>魔王专属</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D144" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>通用</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>1000001</v>
+        <v>90002</v>
       </c>
       <c r="B145" s="0" t="n">
-        <v>1000001</v>
+        <v>90002</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>魔王专属</t>
         </is>
       </c>
       <c r="D145" s="0" t="inlineStr">
         <is>
-          <t>弹窗</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>1000002</v>
+        <v>1000001</v>
       </c>
       <c r="B146" s="0" t="n">
-        <v>1000002</v>
+        <v>1000001</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D146" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>1001001</v>
+        <v>1000002</v>
       </c>
       <c r="B147" s="0" t="n">
-        <v>1001001</v>
+        <v>1000002</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t>等级.{0}</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="D147" s="0" t="inlineStr">
         <is>
-          <t>弹窗-卡片详情</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>1002001</v>
+        <v>1001001</v>
       </c>
       <c r="B148" s="0" t="n">
-        <v>1002001</v>
+        <v>1001001</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t>赠送</t>
+          <t>等级.{0}</t>
         </is>
       </c>
       <c r="D148" s="0" t="inlineStr">
         <is>
-          <t>弹窗-道具选择</t>
+          <t>弹窗-卡片详情</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>1002002</v>
+        <v>1002001</v>
       </c>
       <c r="B149" s="0" t="n">
-        <v>1002002</v>
+        <v>1002001</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>赠送</t>
         </is>
       </c>
       <c r="D149" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-道具选择</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>1003001</v>
+        <v>1002002</v>
       </c>
       <c r="B150" s="0" t="n">
-        <v>1003001</v>
+        <v>1002002</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t>研究等级.{0}</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="D150" s="0" t="inlineStr">
         <is>
-          <t>弹窗-研究详情</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>1003002</v>
+        <v>1003001</v>
       </c>
       <c r="B151" s="0" t="n">
-        <v>1003002</v>
+        <v>1003001</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>研究等级.最大</t>
+          <t>研究等级.{0}</t>
         </is>
       </c>
       <c r="D151" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-研究详情</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>1004001</v>
+        <v>1003002</v>
       </c>
       <c r="B152" s="0" t="n">
-        <v>1004001</v>
+        <v>1003002</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>取个新名字</t>
+          <t>研究等级.最大</t>
         </is>
       </c>
       <c r="D152" s="0" t="inlineStr">
         <is>
-          <t>弹窗-重命名</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>1004002</v>
+        <v>1004001</v>
       </c>
       <c r="B153" s="0" t="n">
-        <v>1004002</v>
+        <v>1004001</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t>输入名字...</t>
+          <t>取个新名字</t>
         </is>
       </c>
       <c r="D153" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-重命名</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>1005001</v>
+        <v>1004002</v>
       </c>
       <c r="B154" s="0" t="n">
-        <v>1005001</v>
+        <v>1004002</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>选择魔物</t>
+          <t>输入名字...</t>
         </is>
       </c>
       <c r="D154" s="0" t="inlineStr">
         <is>
-          <t>弹窗-生物选择</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="155" ht="12" customHeight="1" s="1">
       <c r="A155" s="0" t="n">
-        <v>1005002</v>
+        <v>1005001</v>
       </c>
       <c r="B155" s="0" t="n">
-        <v>1005002</v>
+        <v>1005001</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>当前选择数量{0}/{1}</t>
+          <t>选择魔物</t>
         </is>
       </c>
       <c r="D155" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-生物选择</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>1005003</v>
+        <v>1005002</v>
       </c>
       <c r="B156" s="0" t="n">
-        <v>1005003</v>
+        <v>1005002</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t>超过选择数量上限</t>
+          <t>当前选择数量{0}/{1}</t>
         </is>
       </c>
       <c r="D156" s="0" t="inlineStr">
@@ -3869,50 +3869,50 @@
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>2000001</v>
+        <v>1005003</v>
       </c>
       <c r="B157" s="0" t="n">
-        <v>2000001</v>
+        <v>1005003</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>提示</t>
+          <t>超过选择数量上限</t>
         </is>
       </c>
       <c r="D157" s="0" t="inlineStr">
         <is>
-          <t>popup</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>2000002</v>
+        <v>2000001</v>
       </c>
       <c r="B158" s="0" t="n">
-        <v>2000002</v>
+        <v>2000001</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>魔晶</t>
+          <t>提示</t>
         </is>
       </c>
       <c r="D158" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>popup</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>2000003</v>
+        <v>2000002</v>
       </c>
       <c r="B159" s="0" t="n">
-        <v>2000003</v>
+        <v>2000002</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t>声望</t>
+          <t>魔晶</t>
         </is>
       </c>
       <c r="D159" s="0" t="inlineStr">
@@ -3923,14 +3923,14 @@
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>2000004</v>
+        <v>2000003</v>
       </c>
       <c r="B160" s="0" t="n">
-        <v>2000004</v>
+        <v>2000003</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>排序：稀有度</t>
+          <t>声望</t>
         </is>
       </c>
       <c r="D160" s="0" t="inlineStr">
@@ -3941,14 +3941,14 @@
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>2000005</v>
+        <v>2000004</v>
       </c>
       <c r="B161" s="0" t="n">
-        <v>2000005</v>
+        <v>2000004</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>排序：等级</t>
+          <t>排序：稀有度</t>
         </is>
       </c>
       <c r="D161" s="0" t="inlineStr">
@@ -3959,14 +3959,14 @@
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>2000006</v>
+        <v>2000005</v>
       </c>
       <c r="B162" s="0" t="n">
-        <v>2000006</v>
+        <v>2000005</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>排序：阵容</t>
+          <t>排序：等级</t>
         </is>
       </c>
       <c r="D162" s="0" t="inlineStr">
@@ -3977,14 +3977,14 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>2000007</v>
+        <v>2000006</v>
       </c>
       <c r="B163" s="0" t="n">
-        <v>2000007</v>
+        <v>2000006</v>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>排序：名字</t>
+          <t>排序：阵容</t>
         </is>
       </c>
       <c r="D163" s="0" t="inlineStr">
@@ -3995,14 +3995,14 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>2000008</v>
+        <v>2000007</v>
       </c>
       <c r="B164" s="0" t="n">
-        <v>2000008</v>
+        <v>2000007</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>稀有度:{0}</t>
+          <t>排序：名字</t>
         </is>
       </c>
       <c r="D164" s="0" t="inlineStr">
@@ -4013,14 +4013,14 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>2000009</v>
+        <v>2000008</v>
       </c>
       <c r="B165" s="0" t="n">
-        <v>2000009</v>
+        <v>2000008</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>所属:{0}</t>
+          <t>稀有度:{0}</t>
         </is>
       </c>
       <c r="D165" s="0" t="inlineStr">
@@ -4031,14 +4031,14 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>2000010</v>
+        <v>2000009</v>
       </c>
       <c r="B166" s="0" t="n">
-        <v>2000010</v>
+        <v>2000009</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>道具名字:{0}</t>
+          <t>所属:{0}</t>
         </is>
       </c>
       <c r="D166" s="0" t="inlineStr">
@@ -4049,14 +4049,14 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>2000011</v>
+        <v>2000010</v>
       </c>
       <c r="B167" s="0" t="n">
-        <v>2000011</v>
+        <v>2000010</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>排序：同类</t>
+          <t>道具名字:{0}</t>
         </is>
       </c>
       <c r="D167" s="0" t="inlineStr">
@@ -4067,14 +4067,14 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>2000012</v>
+        <v>2000011</v>
       </c>
       <c r="B168" s="0" t="n">
-        <v>2000012</v>
+        <v>2000011</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>正序</t>
+          <t>排序：同类</t>
         </is>
       </c>
       <c r="D168" s="0" t="inlineStr">
@@ -4085,35 +4085,35 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
+        <v>2000012</v>
+      </c>
+      <c r="B169" s="0" t="n">
+        <v>2000012</v>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t>正序</t>
+        </is>
+      </c>
+      <c r="D169" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="0" t="n">
         <v>2000013</v>
       </c>
-      <c r="B169" s="0" t="n">
+      <c r="B170" s="0" t="n">
         <v>2000013</v>
       </c>
-      <c r="C169" s="0" t="inlineStr">
+      <c r="C170" s="0" t="inlineStr">
         <is>
           <t>倒序</t>
         </is>
       </c>
-      <c r="D169" s="0" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>2000014</v>
-      </c>
-      <c r="B170" t="n">
-        <v>2000014</v>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>筛选排序</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
+      <c r="D170" s="0" t="inlineStr">
         <is>
           <t>|</t>
         </is>
@@ -4121,50 +4121,50 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>3000001</v>
+        <v>2000014</v>
       </c>
       <c r="B171" s="0" t="n">
-        <v>3000001</v>
+        <v>2000014</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>没有足够的魔晶</t>
+          <t>筛选排序</t>
         </is>
       </c>
       <c r="D171" s="0" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>3000002</v>
+        <v>3000001</v>
       </c>
       <c r="B172" s="0" t="n">
-        <v>3000002</v>
+        <v>3000001</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="D172" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>3000003</v>
+        <v>3000002</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>3000003</v>
+        <v>3000002</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>修改名字成功！</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="D173" s="0" t="inlineStr">
@@ -4175,14 +4175,14 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>3000004</v>
+        <v>3000003</v>
       </c>
       <c r="B174" s="0" t="n">
-        <v>3000004</v>
+        <v>3000003</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物！</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="D174" s="0" t="inlineStr">
@@ -4193,14 +4193,14 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>3000005</v>
+        <v>3000004</v>
       </c>
       <c r="B175" s="0" t="n">
-        <v>3000005</v>
+        <v>3000004</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>转生成功！</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="D175" s="0" t="inlineStr">
@@ -4211,50 +4211,50 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>4000006</v>
+        <v>3000005</v>
       </c>
       <c r="B176" s="0" t="n">
-        <v>4000006</v>
+        <v>3000005</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="D176" s="0" t="inlineStr">
         <is>
-          <t>Achievement-进度</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>4000008</v>
+        <v>4000006</v>
       </c>
       <c r="B177" s="0" t="n">
-        <v>4000008</v>
+        <v>4000006</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>领取成功！</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="D177" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Achievement-进度</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>4000010</v>
+        <v>4000008</v>
       </c>
       <c r="B178" s="0" t="n">
-        <v>4000010</v>
+        <v>4000008</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t>游玩时间</t>
+          <t>领取成功！</t>
         </is>
       </c>
       <c r="D178" s="0" t="inlineStr">
@@ -4265,14 +4265,14 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>4000011</v>
+        <v>4000010</v>
       </c>
       <c r="B179" s="0" t="n">
-        <v>4000011</v>
+        <v>4000010</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t>总击杀数</t>
+          <t>游玩时间</t>
         </is>
       </c>
       <c r="D179" s="0" t="inlineStr">
@@ -4283,14 +4283,14 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>4000012</v>
+        <v>4000011</v>
       </c>
       <c r="B180" s="0" t="n">
-        <v>4000012</v>
+        <v>4000011</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t>征服通关</t>
+          <t>总击杀数</t>
         </is>
       </c>
       <c r="D180" s="0" t="inlineStr">
@@ -4301,14 +4301,14 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>4000013</v>
+        <v>4000012</v>
       </c>
       <c r="B181" s="0" t="n">
-        <v>4000013</v>
+        <v>4000012</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t>难度{0}</t>
+          <t>征服通关</t>
         </is>
       </c>
       <c r="D181" s="0" t="inlineStr">
@@ -4319,14 +4319,14 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>4000014</v>
+        <v>4000013</v>
       </c>
       <c r="B182" s="0" t="n">
-        <v>4000014</v>
+        <v>4000013</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>难度{0}</t>
         </is>
       </c>
       <c r="D182" s="0" t="inlineStr">
@@ -4337,17 +4337,35 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="B183" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="C183" s="0" t="inlineStr">
+        <is>
+          <t>{0}时{1}分</t>
+        </is>
+      </c>
+      <c r="D183" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="0" t="n">
         <v>4000015</v>
       </c>
-      <c r="B183" s="0" t="n">
+      <c r="B184" s="0" t="n">
         <v>4000015</v>
       </c>
-      <c r="C183" s="0" t="inlineStr">
+      <c r="C184" s="0" t="inlineStr">
         <is>
           <t>总通关次数</t>
         </is>
       </c>
-      <c r="D183" s="0" t="inlineStr">
+      <c r="D184" s="0" t="inlineStr">
         <is>
           <t>|</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="UIText" sheetId="1" r:id="rId1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D188"/>
+  <dimension ref="A1:D192"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.375" customWidth="1" style="1" min="1" max="1"/>
@@ -1528,18 +1528,18 @@
       </c>
     </row>
     <row r="27" ht="12" customHeight="1" s="1">
-      <c r="A27" t="n">
+      <c r="A27" s="0" t="n">
         <v>404</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="0" t="n">
         <v>404</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>难度未解锁</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>提示</t>
         </is>
@@ -3005,14 +3005,14 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>54001</v>
+        <v>53013</v>
       </c>
       <c r="B109" s="0" t="n">
-        <v>54001</v>
+        <v>53013</v>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
-          <t>没有数据</t>
+          <t>是否确认离开议会？离开后消耗的资源不会返还。</t>
         </is>
       </c>
       <c r="D109" s="0" t="inlineStr">
@@ -3023,32 +3023,32 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>55001</v>
+        <v>53014</v>
       </c>
       <c r="B110" s="0" t="n">
-        <v>55001</v>
+        <v>53014</v>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
-          <t>魔王讨伐者正在靠近中...</t>
+          <t>当前议案通过率:{0}%</t>
         </is>
       </c>
       <c r="D110" s="0" t="inlineStr">
         <is>
-          <t>战斗Boss展示</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>55002</v>
+        <v>54001</v>
       </c>
       <c r="B111" s="0" t="n">
-        <v>55002</v>
+        <v>54001</v>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t>一大波勇者正在靠近中…</t>
+          <t>没有数据</t>
         </is>
       </c>
       <c r="D111" s="0" t="inlineStr">
@@ -3059,32 +3059,32 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>55003</v>
+        <v>55001</v>
       </c>
       <c r="B112" s="0" t="n">
-        <v>55003</v>
+        <v>55001</v>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
-          <t>注意！英雄队伍正在涌来…</t>
+          <t>魔王讨伐者正在靠近中...</t>
         </is>
       </c>
       <c r="D112" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗Boss展示</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>55004</v>
+        <v>55002</v>
       </c>
       <c r="B113" s="0" t="n">
-        <v>55004</v>
+        <v>55002</v>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t>侦测到讨伐部队正在接近…</t>
+          <t>一大波勇者正在靠近中…</t>
         </is>
       </c>
       <c r="D113" s="0" t="inlineStr">
@@ -3095,14 +3095,14 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>55005</v>
+        <v>55003</v>
       </c>
       <c r="B114" s="0" t="n">
-        <v>55005</v>
+        <v>55003</v>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t>勇者联军正在逼近…</t>
+          <t>注意！英雄队伍正在涌来…</t>
         </is>
       </c>
       <c r="D114" s="0" t="inlineStr">
@@ -3113,14 +3113,14 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>55006</v>
+        <v>55004</v>
       </c>
       <c r="B115" s="0" t="n">
-        <v>55006</v>
+        <v>55004</v>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>一大波自称勇者的家伙来了…</t>
+          <t>侦测到讨伐部队正在接近…</t>
         </is>
       </c>
       <c r="D115" s="0" t="inlineStr">
@@ -3131,14 +3131,14 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>55007</v>
+        <v>55005</v>
       </c>
       <c r="B116" s="0" t="n">
-        <v>55007</v>
+        <v>55005</v>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t>警报：正义的伙伴们正在靠近…</t>
+          <t>勇者联军正在逼近…</t>
         </is>
       </c>
       <c r="D116" s="0" t="inlineStr">
@@ -3149,32 +3149,32 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>60000</v>
+        <v>55006</v>
       </c>
       <c r="B117" s="0" t="n">
-        <v>60000</v>
+        <v>55006</v>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
-          <t>献祭升级</t>
+          <t>一大波自称勇者的家伙来了…</t>
         </is>
       </c>
       <c r="D117" s="0" t="inlineStr">
         <is>
-          <t>生物献祭</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>60001</v>
+        <v>55007</v>
       </c>
       <c r="B118" s="0" t="n">
-        <v>60001</v>
+        <v>55007</v>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t>开始献祭</t>
+          <t>警报：正义的伙伴们正在靠近…</t>
         </is>
       </c>
       <c r="D118" s="0" t="inlineStr">
@@ -3185,32 +3185,32 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>60002</v>
+        <v>60000</v>
       </c>
       <c r="B119" s="0" t="n">
-        <v>60002</v>
+        <v>60000</v>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>成功率</t>
+          <t>献祭升级</t>
         </is>
       </c>
       <c r="D119" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物献祭</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>61001</v>
+        <v>60001</v>
       </c>
       <c r="B120" s="0" t="n">
-        <v>61001</v>
+        <v>60001</v>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>还未选择献祭生物！</t>
+          <t>开始献祭</t>
         </is>
       </c>
       <c r="D120" s="0" t="inlineStr">
@@ -3221,14 +3221,14 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>61002</v>
+        <v>60002</v>
       </c>
       <c r="B121" s="0" t="n">
-        <v>61002</v>
+        <v>60002</v>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>献祭生物数量达到上限！</t>
+          <t>成功率</t>
         </is>
       </c>
       <c r="D121" s="0" t="inlineStr">
@@ -3239,14 +3239,14 @@
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>61003</v>
+        <v>61001</v>
       </c>
       <c r="B122" s="0" t="n">
-        <v>61003</v>
+        <v>61001</v>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>是否开始献祭？当前成功率{0}</t>
+          <t>还未选择献祭生物！</t>
         </is>
       </c>
       <c r="D122" s="0" t="inlineStr">
@@ -3257,14 +3257,14 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>61004</v>
+        <v>61002</v>
       </c>
       <c r="B123" s="0" t="n">
-        <v>61004</v>
+        <v>61002</v>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>请分配完所有属性点</t>
+          <t>献祭生物数量达到上限！</t>
         </is>
       </c>
       <c r="D123" s="0" t="inlineStr">
@@ -3275,14 +3275,14 @@
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>61005</v>
+        <v>61003</v>
       </c>
       <c r="B124" s="0" t="n">
-        <v>61005</v>
+        <v>61003</v>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>剩余点数:{0}</t>
+          <t>是否开始献祭？当前成功率{0}</t>
         </is>
       </c>
       <c r="D124" s="0" t="inlineStr">
@@ -3293,32 +3293,32 @@
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>62001</v>
+        <v>61004</v>
       </c>
       <c r="B125" s="0" t="n">
-        <v>62001</v>
+        <v>61004</v>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>是否开启此项研究？花费x{0}魔晶</t>
+          <t>请分配完所有属性点</t>
         </is>
       </c>
       <c r="D125" s="0" t="inlineStr">
         <is>
-          <t>生物研究</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>62002</v>
+        <v>61005</v>
       </c>
       <c r="B126" s="0" t="n">
-        <v>62002</v>
+        <v>61005</v>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>设施</t>
+          <t>剩余点数:{0}</t>
         </is>
       </c>
       <c r="D126" s="0" t="inlineStr">
@@ -3329,32 +3329,32 @@
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>62003</v>
+        <v>62001</v>
       </c>
       <c r="B127" s="0" t="n">
-        <v>62003</v>
+        <v>62001</v>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>强化</t>
+          <t>是否开启此项研究？花费x{0}魔晶</t>
         </is>
       </c>
       <c r="D127" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物研究</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>62004</v>
+        <v>62002</v>
       </c>
       <c r="B128" s="0" t="n">
-        <v>62004</v>
+        <v>62002</v>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>魔物</t>
+          <t>设施</t>
         </is>
       </c>
       <c r="D128" s="0" t="inlineStr">
@@ -3365,32 +3365,32 @@
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>63001</v>
+        <v>62003</v>
       </c>
       <c r="B129" s="0" t="n">
-        <v>63001</v>
+        <v>62003</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>选择转生魔王外观</t>
+          <t>强化</t>
         </is>
       </c>
       <c r="D129" s="0" t="inlineStr">
         <is>
-          <t>生物外貌修改</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>63002</v>
+        <v>62004</v>
       </c>
       <c r="B130" s="0" t="n">
-        <v>63002</v>
+        <v>62004</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>魔物</t>
         </is>
       </c>
       <c r="D130" s="0" t="inlineStr">
@@ -3401,50 +3401,50 @@
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>63003</v>
+        <v>63001</v>
       </c>
       <c r="B131" s="0" t="n">
-        <v>63003</v>
+        <v>63001</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>是否以此外观完成转生？</t>
+          <t>选择转生魔王外观</t>
         </is>
       </c>
       <c r="D131" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物外貌修改</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>64001</v>
+        <v>63002</v>
       </c>
       <c r="B132" s="0" t="n">
-        <v>64001</v>
+        <v>63002</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D132" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>64002</v>
+        <v>63003</v>
       </c>
       <c r="B133" s="0" t="n">
-        <v>64002</v>
+        <v>63003</v>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t>统计</t>
+          <t>是否以此外观完成转生？</t>
         </is>
       </c>
       <c r="D133" s="0" t="inlineStr">
@@ -3455,86 +3455,86 @@
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>70001</v>
+        <v>64001</v>
       </c>
       <c r="B134" s="0" t="n">
-        <v>70001</v>
+        <v>64001</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t>贿赂</t>
+          <t>成就</t>
         </is>
       </c>
       <c r="D134" s="0" t="inlineStr">
         <is>
-          <t>对话</t>
+          <t>成就</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>80001</v>
+        <v>64002</v>
       </c>
       <c r="B135" s="0" t="n">
-        <v>80001</v>
+        <v>64002</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t>开始进阶</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="D135" s="0" t="inlineStr">
         <is>
-          <t>生物进阶</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="136" ht="12" customHeight="1" s="1">
       <c r="A136" s="0" t="n">
-        <v>80002</v>
+        <v>70001</v>
       </c>
       <c r="B136" s="0" t="n">
-        <v>80002</v>
+        <v>70001</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t>结束进阶</t>
+          <t>贿赂</t>
         </is>
       </c>
       <c r="D136" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>对话</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>80003</v>
+        <v>80001</v>
       </c>
       <c r="B137" s="0" t="n">
-        <v>80003</v>
+        <v>80001</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t>完成进阶</t>
+          <t>开始进阶</t>
         </is>
       </c>
       <c r="D137" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物进阶</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>80004</v>
+        <v>80002</v>
       </c>
       <c r="B138" s="0" t="n">
-        <v>80004</v>
+        <v>80002</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t>是否结束进阶？进阶消耗的材料不会返回</t>
+          <t>结束进阶</t>
         </is>
       </c>
       <c r="D138" s="0" t="inlineStr">
@@ -3545,14 +3545,14 @@
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>80005</v>
+        <v>80003</v>
       </c>
       <c r="B139" s="0" t="n">
-        <v>80005</v>
+        <v>80003</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t>进度</t>
+          <t>完成进阶</t>
         </is>
       </c>
       <c r="D139" s="0" t="inlineStr">
@@ -3563,14 +3563,14 @@
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>80006</v>
+        <v>80004</v>
       </c>
       <c r="B140" s="0" t="n">
-        <v>80006</v>
+        <v>80004</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t>选择进阶魔物</t>
+          <t>是否结束进阶？进阶消耗的材料不会返回</t>
         </is>
       </c>
       <c r="D140" s="0" t="inlineStr">
@@ -3581,14 +3581,14 @@
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>80007</v>
+        <v>80005</v>
       </c>
       <c r="B141" s="0" t="n">
-        <v>80007</v>
+        <v>80005</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t>选择辅助魔物</t>
+          <t>进度</t>
         </is>
       </c>
       <c r="D141" s="0" t="inlineStr">
@@ -3599,14 +3599,14 @@
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>80008</v>
+        <v>80006</v>
       </c>
       <c r="B142" s="0" t="n">
-        <v>80008</v>
+        <v>80006</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物</t>
+          <t>选择进阶魔物</t>
         </is>
       </c>
       <c r="D142" s="0" t="inlineStr">
@@ -3617,14 +3617,14 @@
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>80009</v>
+        <v>80007</v>
       </c>
       <c r="B143" s="0" t="n">
-        <v>80009</v>
+        <v>80007</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t>加速进阶 x{0}</t>
+          <t>选择辅助魔物</t>
         </is>
       </c>
       <c r="D143" s="0" t="inlineStr">
@@ -3635,14 +3635,14 @@
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>80010</v>
+        <v>80008</v>
       </c>
       <c r="B144" s="0" t="n">
-        <v>80010</v>
+        <v>80008</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
+          <t>还未选择魔物</t>
         </is>
       </c>
       <c r="D144" s="0" t="inlineStr">
@@ -3653,32 +3653,32 @@
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>90001</v>
+        <v>80009</v>
       </c>
       <c r="B145" s="0" t="n">
-        <v>90001</v>
+        <v>80009</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>加速进阶 x{0}</t>
         </is>
       </c>
       <c r="D145" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>90002</v>
+        <v>80010</v>
       </c>
       <c r="B146" s="0" t="n">
-        <v>90002</v>
+        <v>80010</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>魔王专属</t>
+          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
         </is>
       </c>
       <c r="D146" s="0" t="inlineStr">
@@ -3689,32 +3689,32 @@
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>1000001</v>
+        <v>90001</v>
       </c>
       <c r="B147" s="0" t="n">
-        <v>1000001</v>
+        <v>90001</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D147" s="0" t="inlineStr">
         <is>
-          <t>弹窗</t>
+          <t>通用</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>1000002</v>
+        <v>90002</v>
       </c>
       <c r="B148" s="0" t="n">
-        <v>1000002</v>
+        <v>90002</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>魔王专属</t>
         </is>
       </c>
       <c r="D148" s="0" t="inlineStr">
@@ -3725,86 +3725,86 @@
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>1001001</v>
+        <v>1000001</v>
       </c>
       <c r="B149" s="0" t="n">
-        <v>1001001</v>
+        <v>1000001</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>等级.{0}</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D149" s="0" t="inlineStr">
         <is>
-          <t>弹窗-卡片详情</t>
+          <t>弹窗</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>1002001</v>
+        <v>1000002</v>
       </c>
       <c r="B150" s="0" t="n">
-        <v>1002001</v>
+        <v>1000002</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t>赠送</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="D150" s="0" t="inlineStr">
         <is>
-          <t>弹窗-道具选择</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>1002002</v>
+        <v>1001001</v>
       </c>
       <c r="B151" s="0" t="n">
-        <v>1002002</v>
+        <v>1001001</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>等级.{0}</t>
         </is>
       </c>
       <c r="D151" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-卡片详情</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>1003001</v>
+        <v>1002001</v>
       </c>
       <c r="B152" s="0" t="n">
-        <v>1003001</v>
+        <v>1002001</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>研究等级.{0}</t>
+          <t>赠送</t>
         </is>
       </c>
       <c r="D152" s="0" t="inlineStr">
         <is>
-          <t>弹窗-研究详情</t>
+          <t>弹窗-道具选择</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>1003002</v>
+        <v>1002002</v>
       </c>
       <c r="B153" s="0" t="n">
-        <v>1003002</v>
+        <v>1002002</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t>研究等级.最大</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="D153" s="0" t="inlineStr">
@@ -3815,32 +3815,32 @@
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>1004001</v>
+        <v>1003001</v>
       </c>
       <c r="B154" s="0" t="n">
-        <v>1004001</v>
+        <v>1003001</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>取个新名字</t>
+          <t>研究等级.{0}</t>
         </is>
       </c>
       <c r="D154" s="0" t="inlineStr">
         <is>
-          <t>弹窗-重命名</t>
+          <t>弹窗-研究详情</t>
         </is>
       </c>
     </row>
     <row r="155" ht="12" customHeight="1" s="1">
       <c r="A155" s="0" t="n">
-        <v>1004002</v>
+        <v>1003002</v>
       </c>
       <c r="B155" s="0" t="n">
-        <v>1004002</v>
+        <v>1003002</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>输入名字...</t>
+          <t>研究等级.最大</t>
         </is>
       </c>
       <c r="D155" s="0" t="inlineStr">
@@ -3851,32 +3851,32 @@
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>1005001</v>
+        <v>1004001</v>
       </c>
       <c r="B156" s="0" t="n">
-        <v>1005001</v>
+        <v>1004001</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t>选择魔物</t>
+          <t>取个新名字</t>
         </is>
       </c>
       <c r="D156" s="0" t="inlineStr">
         <is>
-          <t>弹窗-生物选择</t>
+          <t>弹窗-重命名</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>1005002</v>
+        <v>1004002</v>
       </c>
       <c r="B157" s="0" t="n">
-        <v>1005002</v>
+        <v>1004002</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>当前选择数量{0}/{1}</t>
+          <t>输入名字...</t>
         </is>
       </c>
       <c r="D157" s="0" t="inlineStr">
@@ -3887,50 +3887,50 @@
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>1005003</v>
+        <v>1005001</v>
       </c>
       <c r="B158" s="0" t="n">
-        <v>1005003</v>
+        <v>1005001</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>超过选择数量上限</t>
+          <t>选择魔物</t>
         </is>
       </c>
       <c r="D158" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-生物选择</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>2000001</v>
+        <v>1005002</v>
       </c>
       <c r="B159" s="0" t="n">
-        <v>2000001</v>
+        <v>1005002</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t>提示</t>
+          <t>当前选择数量{0}/{1}</t>
         </is>
       </c>
       <c r="D159" s="0" t="inlineStr">
         <is>
-          <t>popup</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>2000002</v>
+        <v>1005003</v>
       </c>
       <c r="B160" s="0" t="n">
-        <v>2000002</v>
+        <v>1005003</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>魔晶</t>
+          <t>超过选择数量上限</t>
         </is>
       </c>
       <c r="D160" s="0" t="inlineStr">
@@ -3941,32 +3941,32 @@
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>2000003</v>
+        <v>2000001</v>
       </c>
       <c r="B161" s="0" t="n">
-        <v>2000003</v>
+        <v>2000001</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>声望</t>
+          <t>提示</t>
         </is>
       </c>
       <c r="D161" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>popup</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>2000004</v>
+        <v>2000002</v>
       </c>
       <c r="B162" s="0" t="n">
-        <v>2000004</v>
+        <v>2000002</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>排序：稀有度</t>
+          <t>魔晶</t>
         </is>
       </c>
       <c r="D162" s="0" t="inlineStr">
@@ -3977,14 +3977,14 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>2000005</v>
+        <v>2000003</v>
       </c>
       <c r="B163" s="0" t="n">
-        <v>2000005</v>
+        <v>2000003</v>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>排序：等级</t>
+          <t>声望</t>
         </is>
       </c>
       <c r="D163" s="0" t="inlineStr">
@@ -3995,14 +3995,14 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="B164" s="0" t="n">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>排序：阵容</t>
+          <t>排序：稀有度</t>
         </is>
       </c>
       <c r="D164" s="0" t="inlineStr">
@@ -4013,14 +4013,14 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>2000007</v>
+        <v>2000005</v>
       </c>
       <c r="B165" s="0" t="n">
-        <v>2000007</v>
+        <v>2000005</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>排序：名字</t>
+          <t>排序：等级</t>
         </is>
       </c>
       <c r="D165" s="0" t="inlineStr">
@@ -4031,14 +4031,14 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>2000008</v>
+        <v>2000006</v>
       </c>
       <c r="B166" s="0" t="n">
-        <v>2000008</v>
+        <v>2000006</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>稀有度:{0}</t>
+          <t>排序：阵容</t>
         </is>
       </c>
       <c r="D166" s="0" t="inlineStr">
@@ -4049,14 +4049,14 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>2000009</v>
+        <v>2000007</v>
       </c>
       <c r="B167" s="0" t="n">
-        <v>2000009</v>
+        <v>2000007</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>所属:{0}</t>
+          <t>排序：名字</t>
         </is>
       </c>
       <c r="D167" s="0" t="inlineStr">
@@ -4067,14 +4067,14 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>2000010</v>
+        <v>2000008</v>
       </c>
       <c r="B168" s="0" t="n">
-        <v>2000010</v>
+        <v>2000008</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>道具名字:{0}</t>
+          <t>稀有度:{0}</t>
         </is>
       </c>
       <c r="D168" s="0" t="inlineStr">
@@ -4085,14 +4085,14 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>2000011</v>
+        <v>2000009</v>
       </c>
       <c r="B169" s="0" t="n">
-        <v>2000011</v>
+        <v>2000009</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>排序：同类</t>
+          <t>所属:{0}</t>
         </is>
       </c>
       <c r="D169" s="0" t="inlineStr">
@@ -4103,14 +4103,14 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>2000012</v>
+        <v>2000010</v>
       </c>
       <c r="B170" s="0" t="n">
-        <v>2000012</v>
+        <v>2000010</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>正序</t>
+          <t>道具名字:{0}</t>
         </is>
       </c>
       <c r="D170" s="0" t="inlineStr">
@@ -4121,14 +4121,14 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>2000013</v>
+        <v>2000011</v>
       </c>
       <c r="B171" s="0" t="n">
-        <v>2000013</v>
+        <v>2000011</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>倒序</t>
+          <t>排序：同类</t>
         </is>
       </c>
       <c r="D171" s="0" t="inlineStr">
@@ -4139,14 +4139,14 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>2000014</v>
+        <v>2000012</v>
       </c>
       <c r="B172" s="0" t="n">
-        <v>2000014</v>
+        <v>2000012</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>筛选排序</t>
+          <t>正序</t>
         </is>
       </c>
       <c r="D172" s="0" t="inlineStr">
@@ -4157,14 +4157,14 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>2000015</v>
+        <v>2000013</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>2000015</v>
+        <v>2000013</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>没有相关道具</t>
+          <t>倒序</t>
         </is>
       </c>
       <c r="D173" s="0" t="inlineStr">
@@ -4175,14 +4175,14 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>2000016</v>
+        <v>2000014</v>
       </c>
       <c r="B174" s="0" t="n">
-        <v>2000016</v>
+        <v>2000014</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>没有相关魔物</t>
+          <t>筛选排序</t>
         </is>
       </c>
       <c r="D174" s="0" t="inlineStr">
@@ -4193,14 +4193,14 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>2000017</v>
+        <v>2000015</v>
       </c>
       <c r="B175" s="0" t="n">
-        <v>2000017</v>
+        <v>2000015</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>没有可孕育的生物</t>
+          <t>没有相关道具</t>
         </is>
       </c>
       <c r="D175" s="0" t="inlineStr">
@@ -4211,32 +4211,32 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>3000001</v>
+        <v>2000016</v>
       </c>
       <c r="B176" s="0" t="n">
-        <v>3000001</v>
+        <v>2000016</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>没有足够的魔晶</t>
+          <t>没有相关魔物</t>
         </is>
       </c>
       <c r="D176" s="0" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>3000002</v>
+        <v>2000017</v>
       </c>
       <c r="B177" s="0" t="n">
-        <v>3000002</v>
+        <v>2000017</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
+          <t>没有可孕育的生物</t>
         </is>
       </c>
       <c r="D177" s="0" t="inlineStr">
@@ -4247,32 +4247,32 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>3000003</v>
+        <v>3000001</v>
       </c>
       <c r="B178" s="0" t="n">
-        <v>3000003</v>
+        <v>3000001</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t>修改名字成功！</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="D178" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>3000004</v>
+        <v>3000002</v>
       </c>
       <c r="B179" s="0" t="n">
-        <v>3000004</v>
+        <v>3000002</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物！</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="D179" s="0" t="inlineStr">
@@ -4283,14 +4283,14 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>3000005</v>
+        <v>3000003</v>
       </c>
       <c r="B180" s="0" t="n">
-        <v>3000005</v>
+        <v>3000003</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t>转生成功！</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="D180" s="0" t="inlineStr">
@@ -4301,32 +4301,32 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>4000006</v>
+        <v>3000004</v>
       </c>
       <c r="B181" s="0" t="n">
-        <v>4000006</v>
+        <v>3000004</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="D181" s="0" t="inlineStr">
         <is>
-          <t>Achievement-进度</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>4000008</v>
+        <v>3000005</v>
       </c>
       <c r="B182" s="0" t="n">
-        <v>4000008</v>
+        <v>3000005</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t>领取成功！</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="D182" s="0" t="inlineStr">
@@ -4337,32 +4337,32 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
-        <v>4000010</v>
+        <v>4000006</v>
       </c>
       <c r="B183" s="0" t="n">
-        <v>4000010</v>
+        <v>4000006</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
-          <t>游玩时间</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="D183" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Achievement-进度</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="n">
-        <v>4000011</v>
+        <v>4000008</v>
       </c>
       <c r="B184" s="0" t="n">
-        <v>4000011</v>
+        <v>4000008</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t>总击杀数</t>
+          <t>领取成功！</t>
         </is>
       </c>
       <c r="D184" s="0" t="inlineStr">
@@ -4373,14 +4373,14 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="n">
-        <v>4000012</v>
+        <v>4000010</v>
       </c>
       <c r="B185" s="0" t="n">
-        <v>4000012</v>
+        <v>4000010</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t>征服通关</t>
+          <t>游玩时间</t>
         </is>
       </c>
       <c r="D185" s="0" t="inlineStr">
@@ -4391,14 +4391,14 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="n">
-        <v>4000013</v>
+        <v>4000011</v>
       </c>
       <c r="B186" s="0" t="n">
-        <v>4000013</v>
+        <v>4000011</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t>难度{0}</t>
+          <t>总击杀数</t>
         </is>
       </c>
       <c r="D186" s="0" t="inlineStr">
@@ -4409,14 +4409,14 @@
     </row>
     <row r="187">
       <c r="A187" s="0" t="n">
-        <v>4000014</v>
+        <v>4000012</v>
       </c>
       <c r="B187" s="0" t="n">
-        <v>4000014</v>
+        <v>4000012</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>征服通关</t>
         </is>
       </c>
       <c r="D187" s="0" t="inlineStr">
@@ -4427,26 +4427,94 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="n">
+        <v>4000013</v>
+      </c>
+      <c r="B188" s="0" t="n">
+        <v>4000013</v>
+      </c>
+      <c r="C188" s="0" t="inlineStr">
+        <is>
+          <t>难度{0}</t>
+        </is>
+      </c>
+      <c r="D188" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="12" customHeight="1" s="1">
+      <c r="A189" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="B189" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="C189" s="0" t="inlineStr">
+        <is>
+          <t>{0}时{1}分</t>
+        </is>
+      </c>
+      <c r="D189" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="12" customHeight="1" s="1">
+      <c r="A190" s="0" t="n">
         <v>4000015</v>
       </c>
-      <c r="B188" s="0" t="n">
+      <c r="B190" s="0" t="n">
         <v>4000015</v>
       </c>
-      <c r="C188" s="0" t="inlineStr">
+      <c r="C190" s="0" t="inlineStr">
         <is>
           <t>总通关次数</t>
         </is>
       </c>
-      <c r="D188" s="0" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="12" customHeight="1" s="1"/>
-    <row r="190" ht="12" customHeight="1" s="1"/>
-    <row r="191" ht="12" customHeight="1" s="1"/>
-    <row r="192" ht="12" customHeight="1" s="1"/>
+      <c r="D190" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="12" customHeight="1" s="1">
+      <c r="A191" s="0" t="n">
+        <v>4000016</v>
+      </c>
+      <c r="B191" s="0" t="n">
+        <v>4000016</v>
+      </c>
+      <c r="C191" s="0" t="inlineStr">
+        <is>
+          <t>Lv.{0}/{1}</t>
+        </is>
+      </c>
+      <c r="D191" s="0" t="inlineStr">
+        <is>
+          <t>Achievement-等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="12" customHeight="1" s="1">
+      <c r="A192" t="n">
+        <v>4000017</v>
+      </c>
+      <c r="B192" t="n">
+        <v>4000017</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Achievement-已完成</t>
+        </is>
+      </c>
+    </row>
     <row r="193" ht="12" customHeight="1" s="1"/>
     <row r="194" ht="12" customHeight="1" s="1"/>
     <row r="195" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D192"/>
+  <dimension ref="A1:D194"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.375" customWidth="1" style="1" min="1" max="1"/>
@@ -2608,51 +2608,51 @@
       </c>
     </row>
     <row r="87" ht="12" customHeight="1" s="1">
-      <c r="A87" s="0" t="n">
-        <v>50101</v>
-      </c>
-      <c r="B87" s="0" t="n">
-        <v>50101</v>
-      </c>
-      <c r="C87" s="0" t="inlineStr">
-        <is>
-          <t>继续</t>
-        </is>
-      </c>
-      <c r="D87" s="0" t="inlineStr">
-        <is>
-          <t>|</t>
+      <c r="A87" t="n">
+        <v>50007</v>
+      </c>
+      <c r="B87" t="n">
+        <v>50007</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>治疗</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>战斗结算界面</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="0" t="n">
-        <v>51001</v>
-      </c>
-      <c r="B88" s="0" t="n">
-        <v>51001</v>
-      </c>
-      <c r="C88" s="0" t="inlineStr">
-        <is>
-          <t>深渊馈赠</t>
-        </is>
-      </c>
-      <c r="D88" s="0" t="inlineStr">
-        <is>
-          <t>战斗深渊馈赠</t>
+      <c r="A88" t="n">
+        <v>50008</v>
+      </c>
+      <c r="B88" t="n">
+        <v>50008</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>受疗</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>战斗结算界面</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>51002</v>
+        <v>50101</v>
       </c>
       <c r="B89" s="0" t="n">
-        <v>51002</v>
+        <v>50101</v>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>选择一个深渊馈赠</t>
+          <t>继续</t>
         </is>
       </c>
       <c r="D89" s="0" t="inlineStr">
@@ -2663,46 +2663,46 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>51003</v>
+        <v>51001</v>
       </c>
       <c r="B90" s="0" t="n">
-        <v>51003</v>
+        <v>51001</v>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>跳过</t>
+          <t>深渊馈赠</t>
         </is>
       </c>
       <c r="D90" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗深渊馈赠</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>52001</v>
+        <v>51002</v>
       </c>
       <c r="B91" s="0" t="n">
-        <v>52001</v>
+        <v>51002</v>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t>选择奖励</t>
+          <t>选择一个深渊馈赠</t>
         </is>
       </c>
       <c r="D91" s="0" t="inlineStr">
         <is>
-          <t>奖励选择</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>52002</v>
+        <v>51003</v>
       </c>
       <c r="B92" s="0" t="n">
-        <v>52002</v>
+        <v>51003</v>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>52003</v>
+        <v>52001</v>
       </c>
       <c r="B93" s="0" t="n">
-        <v>52003</v>
+        <v>52001</v>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t>剩余可选择次数{0}/{1}</t>
+          <t>选择奖励</t>
         </is>
       </c>
       <c r="D93" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>奖励选择</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>52004</v>
+        <v>52002</v>
       </c>
       <c r="B94" s="0" t="n">
-        <v>52004</v>
+        <v>52002</v>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t>没有可选择次数</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="D94" s="0" t="inlineStr">
@@ -2753,14 +2753,14 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>52005</v>
+        <v>52003</v>
       </c>
       <c r="B95" s="0" t="n">
-        <v>52005</v>
+        <v>52003</v>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t>还有可选择次数，是否仍要结束选择奖励？</t>
+          <t>剩余可选择次数{0}/{1}</t>
         </is>
       </c>
       <c r="D95" s="0" t="inlineStr">
@@ -2771,32 +2771,32 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>53000</v>
+        <v>52004</v>
       </c>
       <c r="B96" s="0" t="n">
-        <v>53000</v>
+        <v>52004</v>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t>终焉议会</t>
+          <t>没有可选择次数</t>
         </is>
       </c>
       <c r="D96" s="0" t="inlineStr">
         <is>
-          <t>终焉议会</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>53001</v>
+        <v>52005</v>
       </c>
       <c r="B97" s="0" t="n">
-        <v>53001</v>
+        <v>52005</v>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>选择一个议案</t>
+          <t>还有可选择次数，是否仍要结束选择奖励？</t>
         </is>
       </c>
       <c r="D97" s="0" t="inlineStr">
@@ -2807,32 +2807,32 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>53002</v>
+        <v>53000</v>
       </c>
       <c r="B98" s="0" t="n">
-        <v>53002</v>
+        <v>53000</v>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>是否提交议案《{0}》，并且前往终焉议会？</t>
+          <t>终焉议会</t>
         </is>
       </c>
       <c r="D98" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>终焉议会</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>53003</v>
+        <v>53001</v>
       </c>
       <c r="B99" s="0" t="n">
-        <v>53003</v>
+        <v>53001</v>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
-          <t>通过率   {0}%</t>
+          <t>选择一个议案</t>
         </is>
       </c>
       <c r="D99" s="0" t="inlineStr">
@@ -2843,14 +2843,14 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>53004</v>
+        <v>53002</v>
       </c>
       <c r="B100" s="0" t="n">
-        <v>53004</v>
+        <v>53002</v>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
-          <t>开始投票</t>
+          <t>是否提交议案《{0}》，并且前往终焉议会？</t>
         </is>
       </c>
       <c r="D100" s="0" t="inlineStr">
@@ -2861,14 +2861,14 @@
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>53005</v>
+        <v>53003</v>
       </c>
       <c r="B101" s="0" t="n">
-        <v>53005</v>
+        <v>53003</v>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
-          <t>离开议会</t>
+          <t>通过率   {0}%</t>
         </is>
       </c>
       <c r="D101" s="0" t="inlineStr">
@@ -2879,14 +2879,14 @@
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>53006</v>
+        <v>53004</v>
       </c>
       <c r="B102" s="0" t="n">
-        <v>53006</v>
+        <v>53004</v>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t>赞成</t>
+          <t>开始投票</t>
         </is>
       </c>
       <c r="D102" s="0" t="inlineStr">
@@ -2897,14 +2897,14 @@
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>53007</v>
+        <v>53005</v>
       </c>
       <c r="B103" s="0" t="n">
-        <v>53007</v>
+        <v>53005</v>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
-          <t>反对</t>
+          <t>离开议会</t>
         </is>
       </c>
       <c r="D103" s="0" t="inlineStr">
@@ -2915,14 +2915,14 @@
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>53008</v>
+        <v>53006</v>
       </c>
       <c r="B104" s="0" t="n">
-        <v>53008</v>
+        <v>53006</v>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>赞成</t>
         </is>
       </c>
       <c r="D104" s="0" t="inlineStr">
@@ -2933,14 +2933,14 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>53009</v>
+        <v>53007</v>
       </c>
       <c r="B105" s="0" t="n">
-        <v>53009</v>
+        <v>53007</v>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
-          <t>否决</t>
+          <t>反对</t>
         </is>
       </c>
       <c r="D105" s="0" t="inlineStr">
@@ -2951,14 +2951,14 @@
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>53010</v>
+        <v>53008</v>
       </c>
       <c r="B106" s="0" t="n">
-        <v>53010</v>
+        <v>53008</v>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
-          <t>暴力说服</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="D106" s="0" t="inlineStr">
@@ -2969,14 +2969,14 @@
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>53011</v>
+        <v>53009</v>
       </c>
       <c r="B107" s="0" t="n">
-        <v>53011</v>
+        <v>53009</v>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
-          <t>自由活动</t>
+          <t>否决</t>
         </is>
       </c>
       <c r="D107" s="0" t="inlineStr">
@@ -2987,14 +2987,14 @@
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>53012</v>
+        <v>53010</v>
       </c>
       <c r="B108" s="0" t="n">
-        <v>53012</v>
+        <v>53010</v>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
-          <t>是否提交议案《{0}》？</t>
+          <t>暴力说服</t>
         </is>
       </c>
       <c r="D108" s="0" t="inlineStr">
@@ -3005,14 +3005,14 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>53013</v>
+        <v>53011</v>
       </c>
       <c r="B109" s="0" t="n">
-        <v>53013</v>
+        <v>53011</v>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
-          <t>是否确认离开议会？离开后消耗的资源不会返还。</t>
+          <t>自由活动</t>
         </is>
       </c>
       <c r="D109" s="0" t="inlineStr">
@@ -3023,14 +3023,14 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>53014</v>
+        <v>53012</v>
       </c>
       <c r="B110" s="0" t="n">
-        <v>53014</v>
+        <v>53012</v>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
-          <t>当前议案通过率:{0}%</t>
+          <t>是否提交议案《{0}》？</t>
         </is>
       </c>
       <c r="D110" s="0" t="inlineStr">
@@ -3041,14 +3041,14 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>54001</v>
+        <v>53013</v>
       </c>
       <c r="B111" s="0" t="n">
-        <v>54001</v>
+        <v>53013</v>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t>没有数据</t>
+          <t>是否确认离开议会？离开后消耗的资源不会返还。</t>
         </is>
       </c>
       <c r="D111" s="0" t="inlineStr">
@@ -3059,32 +3059,32 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>55001</v>
+        <v>53014</v>
       </c>
       <c r="B112" s="0" t="n">
-        <v>55001</v>
+        <v>53014</v>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
-          <t>魔王讨伐者正在靠近中...</t>
+          <t>当前议案通过率:{0}%</t>
         </is>
       </c>
       <c r="D112" s="0" t="inlineStr">
         <is>
-          <t>战斗Boss展示</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>55002</v>
+        <v>54001</v>
       </c>
       <c r="B113" s="0" t="n">
-        <v>55002</v>
+        <v>54001</v>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t>一大波勇者正在靠近中…</t>
+          <t>没有数据</t>
         </is>
       </c>
       <c r="D113" s="0" t="inlineStr">
@@ -3095,32 +3095,32 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>55003</v>
+        <v>55001</v>
       </c>
       <c r="B114" s="0" t="n">
-        <v>55003</v>
+        <v>55001</v>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t>注意！英雄队伍正在涌来…</t>
+          <t>魔王讨伐者正在靠近中...</t>
         </is>
       </c>
       <c r="D114" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗Boss展示</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>55004</v>
+        <v>55002</v>
       </c>
       <c r="B115" s="0" t="n">
-        <v>55004</v>
+        <v>55002</v>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>侦测到讨伐部队正在接近…</t>
+          <t>一大波勇者正在靠近中…</t>
         </is>
       </c>
       <c r="D115" s="0" t="inlineStr">
@@ -3131,14 +3131,14 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>55005</v>
+        <v>55003</v>
       </c>
       <c r="B116" s="0" t="n">
-        <v>55005</v>
+        <v>55003</v>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t>勇者联军正在逼近…</t>
+          <t>注意！英雄队伍正在涌来…</t>
         </is>
       </c>
       <c r="D116" s="0" t="inlineStr">
@@ -3149,14 +3149,14 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>55006</v>
+        <v>55004</v>
       </c>
       <c r="B117" s="0" t="n">
-        <v>55006</v>
+        <v>55004</v>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
-          <t>一大波自称勇者的家伙来了…</t>
+          <t>侦测到讨伐部队正在接近…</t>
         </is>
       </c>
       <c r="D117" s="0" t="inlineStr">
@@ -3167,14 +3167,14 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>55007</v>
+        <v>55005</v>
       </c>
       <c r="B118" s="0" t="n">
-        <v>55007</v>
+        <v>55005</v>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t>警报：正义的伙伴们正在靠近…</t>
+          <t>勇者联军正在逼近…</t>
         </is>
       </c>
       <c r="D118" s="0" t="inlineStr">
@@ -3185,32 +3185,32 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>60000</v>
+        <v>55006</v>
       </c>
       <c r="B119" s="0" t="n">
-        <v>60000</v>
+        <v>55006</v>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>献祭升级</t>
+          <t>一大波自称勇者的家伙来了…</t>
         </is>
       </c>
       <c r="D119" s="0" t="inlineStr">
         <is>
-          <t>生物献祭</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>60001</v>
+        <v>55007</v>
       </c>
       <c r="B120" s="0" t="n">
-        <v>60001</v>
+        <v>55007</v>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>开始献祭</t>
+          <t>警报：正义的伙伴们正在靠近…</t>
         </is>
       </c>
       <c r="D120" s="0" t="inlineStr">
@@ -3221,32 +3221,32 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>60002</v>
+        <v>60000</v>
       </c>
       <c r="B121" s="0" t="n">
-        <v>60002</v>
+        <v>60000</v>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>成功率</t>
+          <t>献祭升级</t>
         </is>
       </c>
       <c r="D121" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物献祭</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>61001</v>
+        <v>60001</v>
       </c>
       <c r="B122" s="0" t="n">
-        <v>61001</v>
+        <v>60001</v>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>还未选择献祭生物！</t>
+          <t>开始献祭</t>
         </is>
       </c>
       <c r="D122" s="0" t="inlineStr">
@@ -3257,14 +3257,14 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>61002</v>
+        <v>60002</v>
       </c>
       <c r="B123" s="0" t="n">
-        <v>61002</v>
+        <v>60002</v>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>献祭生物数量达到上限！</t>
+          <t>成功率</t>
         </is>
       </c>
       <c r="D123" s="0" t="inlineStr">
@@ -3275,14 +3275,14 @@
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>61003</v>
+        <v>61001</v>
       </c>
       <c r="B124" s="0" t="n">
-        <v>61003</v>
+        <v>61001</v>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>是否开始献祭？当前成功率{0}</t>
+          <t>还未选择献祭生物！</t>
         </is>
       </c>
       <c r="D124" s="0" t="inlineStr">
@@ -3293,14 +3293,14 @@
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>61004</v>
+        <v>61002</v>
       </c>
       <c r="B125" s="0" t="n">
-        <v>61004</v>
+        <v>61002</v>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>请分配完所有属性点</t>
+          <t>献祭生物数量达到上限！</t>
         </is>
       </c>
       <c r="D125" s="0" t="inlineStr">
@@ -3311,14 +3311,14 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>61005</v>
+        <v>61003</v>
       </c>
       <c r="B126" s="0" t="n">
-        <v>61005</v>
+        <v>61003</v>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>剩余点数:{0}</t>
+          <t>是否开始献祭？当前成功率{0}</t>
         </is>
       </c>
       <c r="D126" s="0" t="inlineStr">
@@ -3329,32 +3329,32 @@
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>62001</v>
+        <v>61004</v>
       </c>
       <c r="B127" s="0" t="n">
-        <v>62001</v>
+        <v>61004</v>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>是否开启此项研究？花费x{0}魔晶</t>
+          <t>请分配完所有属性点</t>
         </is>
       </c>
       <c r="D127" s="0" t="inlineStr">
         <is>
-          <t>生物研究</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>62002</v>
+        <v>61005</v>
       </c>
       <c r="B128" s="0" t="n">
-        <v>62002</v>
+        <v>61005</v>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>设施</t>
+          <t>剩余点数:{0}</t>
         </is>
       </c>
       <c r="D128" s="0" t="inlineStr">
@@ -3365,32 +3365,32 @@
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>62003</v>
+        <v>62001</v>
       </c>
       <c r="B129" s="0" t="n">
-        <v>62003</v>
+        <v>62001</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>强化</t>
+          <t>是否开启此项研究？花费x{0}魔晶</t>
         </is>
       </c>
       <c r="D129" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物研究</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>62004</v>
+        <v>62002</v>
       </c>
       <c r="B130" s="0" t="n">
-        <v>62004</v>
+        <v>62002</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>魔物</t>
+          <t>设施</t>
         </is>
       </c>
       <c r="D130" s="0" t="inlineStr">
@@ -3401,32 +3401,32 @@
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>63001</v>
+        <v>62003</v>
       </c>
       <c r="B131" s="0" t="n">
-        <v>63001</v>
+        <v>62003</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>选择转生魔王外观</t>
+          <t>强化</t>
         </is>
       </c>
       <c r="D131" s="0" t="inlineStr">
         <is>
-          <t>生物外貌修改</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>63002</v>
+        <v>62004</v>
       </c>
       <c r="B132" s="0" t="n">
-        <v>63002</v>
+        <v>62004</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>魔物</t>
         </is>
       </c>
       <c r="D132" s="0" t="inlineStr">
@@ -3437,50 +3437,50 @@
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>63003</v>
+        <v>63001</v>
       </c>
       <c r="B133" s="0" t="n">
-        <v>63003</v>
+        <v>63001</v>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t>是否以此外观完成转生？</t>
+          <t>选择转生魔王外观</t>
         </is>
       </c>
       <c r="D133" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物外貌修改</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>64001</v>
+        <v>63002</v>
       </c>
       <c r="B134" s="0" t="n">
-        <v>64001</v>
+        <v>63002</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D134" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>64002</v>
+        <v>63003</v>
       </c>
       <c r="B135" s="0" t="n">
-        <v>64002</v>
+        <v>63003</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t>统计</t>
+          <t>是否以此外观完成转生？</t>
         </is>
       </c>
       <c r="D135" s="0" t="inlineStr">
@@ -3491,86 +3491,86 @@
     </row>
     <row r="136" ht="12" customHeight="1" s="1">
       <c r="A136" s="0" t="n">
-        <v>70001</v>
+        <v>64001</v>
       </c>
       <c r="B136" s="0" t="n">
-        <v>70001</v>
+        <v>64001</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t>贿赂</t>
+          <t>成就</t>
         </is>
       </c>
       <c r="D136" s="0" t="inlineStr">
         <is>
-          <t>对话</t>
+          <t>成就</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>80001</v>
+        <v>64002</v>
       </c>
       <c r="B137" s="0" t="n">
-        <v>80001</v>
+        <v>64002</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t>开始进阶</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="D137" s="0" t="inlineStr">
         <is>
-          <t>生物进阶</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>80002</v>
+        <v>70001</v>
       </c>
       <c r="B138" s="0" t="n">
-        <v>80002</v>
+        <v>70001</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t>结束进阶</t>
+          <t>贿赂</t>
         </is>
       </c>
       <c r="D138" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>对话</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>80003</v>
+        <v>80001</v>
       </c>
       <c r="B139" s="0" t="n">
-        <v>80003</v>
+        <v>80001</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t>完成进阶</t>
+          <t>开始进阶</t>
         </is>
       </c>
       <c r="D139" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物进阶</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>80004</v>
+        <v>80002</v>
       </c>
       <c r="B140" s="0" t="n">
-        <v>80004</v>
+        <v>80002</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t>是否结束进阶？进阶消耗的材料不会返回</t>
+          <t>结束进阶</t>
         </is>
       </c>
       <c r="D140" s="0" t="inlineStr">
@@ -3581,14 +3581,14 @@
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>80005</v>
+        <v>80003</v>
       </c>
       <c r="B141" s="0" t="n">
-        <v>80005</v>
+        <v>80003</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t>进度</t>
+          <t>完成进阶</t>
         </is>
       </c>
       <c r="D141" s="0" t="inlineStr">
@@ -3599,14 +3599,14 @@
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>80006</v>
+        <v>80004</v>
       </c>
       <c r="B142" s="0" t="n">
-        <v>80006</v>
+        <v>80004</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t>选择进阶魔物</t>
+          <t>是否结束进阶？进阶消耗的材料不会返回</t>
         </is>
       </c>
       <c r="D142" s="0" t="inlineStr">
@@ -3617,14 +3617,14 @@
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>80007</v>
+        <v>80005</v>
       </c>
       <c r="B143" s="0" t="n">
-        <v>80007</v>
+        <v>80005</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t>选择辅助魔物</t>
+          <t>进度</t>
         </is>
       </c>
       <c r="D143" s="0" t="inlineStr">
@@ -3635,14 +3635,14 @@
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>80008</v>
+        <v>80006</v>
       </c>
       <c r="B144" s="0" t="n">
-        <v>80008</v>
+        <v>80006</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物</t>
+          <t>选择进阶魔物</t>
         </is>
       </c>
       <c r="D144" s="0" t="inlineStr">
@@ -3653,14 +3653,14 @@
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>80009</v>
+        <v>80007</v>
       </c>
       <c r="B145" s="0" t="n">
-        <v>80009</v>
+        <v>80007</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t>加速进阶 x{0}</t>
+          <t>选择辅助魔物</t>
         </is>
       </c>
       <c r="D145" s="0" t="inlineStr">
@@ -3671,14 +3671,14 @@
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>80010</v>
+        <v>80008</v>
       </c>
       <c r="B146" s="0" t="n">
-        <v>80010</v>
+        <v>80008</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
+          <t>还未选择魔物</t>
         </is>
       </c>
       <c r="D146" s="0" t="inlineStr">
@@ -3689,32 +3689,32 @@
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>90001</v>
+        <v>80009</v>
       </c>
       <c r="B147" s="0" t="n">
-        <v>90001</v>
+        <v>80009</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>加速进阶 x{0}</t>
         </is>
       </c>
       <c r="D147" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>90002</v>
+        <v>80010</v>
       </c>
       <c r="B148" s="0" t="n">
-        <v>90002</v>
+        <v>80010</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t>魔王专属</t>
+          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
         </is>
       </c>
       <c r="D148" s="0" t="inlineStr">
@@ -3725,32 +3725,32 @@
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>1000001</v>
+        <v>90001</v>
       </c>
       <c r="B149" s="0" t="n">
-        <v>1000001</v>
+        <v>90001</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D149" s="0" t="inlineStr">
         <is>
-          <t>弹窗</t>
+          <t>通用</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>1000002</v>
+        <v>90002</v>
       </c>
       <c r="B150" s="0" t="n">
-        <v>1000002</v>
+        <v>90002</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>魔王专属</t>
         </is>
       </c>
       <c r="D150" s="0" t="inlineStr">
@@ -3761,86 +3761,86 @@
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>1001001</v>
+        <v>1000001</v>
       </c>
       <c r="B151" s="0" t="n">
-        <v>1001001</v>
+        <v>1000001</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>等级.{0}</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D151" s="0" t="inlineStr">
         <is>
-          <t>弹窗-卡片详情</t>
+          <t>弹窗</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>1002001</v>
+        <v>1000002</v>
       </c>
       <c r="B152" s="0" t="n">
-        <v>1002001</v>
+        <v>1000002</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>赠送</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="D152" s="0" t="inlineStr">
         <is>
-          <t>弹窗-道具选择</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>1002002</v>
+        <v>1001001</v>
       </c>
       <c r="B153" s="0" t="n">
-        <v>1002002</v>
+        <v>1001001</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>等级.{0}</t>
         </is>
       </c>
       <c r="D153" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-卡片详情</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>1003001</v>
+        <v>1002001</v>
       </c>
       <c r="B154" s="0" t="n">
-        <v>1003001</v>
+        <v>1002001</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>研究等级.{0}</t>
+          <t>赠送</t>
         </is>
       </c>
       <c r="D154" s="0" t="inlineStr">
         <is>
-          <t>弹窗-研究详情</t>
+          <t>弹窗-道具选择</t>
         </is>
       </c>
     </row>
     <row r="155" ht="12" customHeight="1" s="1">
       <c r="A155" s="0" t="n">
-        <v>1003002</v>
+        <v>1002002</v>
       </c>
       <c r="B155" s="0" t="n">
-        <v>1003002</v>
+        <v>1002002</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>研究等级.最大</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="D155" s="0" t="inlineStr">
@@ -3851,32 +3851,32 @@
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>1004001</v>
+        <v>1003001</v>
       </c>
       <c r="B156" s="0" t="n">
-        <v>1004001</v>
+        <v>1003001</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t>取个新名字</t>
+          <t>研究等级.{0}</t>
         </is>
       </c>
       <c r="D156" s="0" t="inlineStr">
         <is>
-          <t>弹窗-重命名</t>
+          <t>弹窗-研究详情</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>1004002</v>
+        <v>1003002</v>
       </c>
       <c r="B157" s="0" t="n">
-        <v>1004002</v>
+        <v>1003002</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>输入名字...</t>
+          <t>研究等级.最大</t>
         </is>
       </c>
       <c r="D157" s="0" t="inlineStr">
@@ -3887,32 +3887,32 @@
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>1005001</v>
+        <v>1004001</v>
       </c>
       <c r="B158" s="0" t="n">
-        <v>1005001</v>
+        <v>1004001</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>选择魔物</t>
+          <t>取个新名字</t>
         </is>
       </c>
       <c r="D158" s="0" t="inlineStr">
         <is>
-          <t>弹窗-生物选择</t>
+          <t>弹窗-重命名</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>1005002</v>
+        <v>1004002</v>
       </c>
       <c r="B159" s="0" t="n">
-        <v>1005002</v>
+        <v>1004002</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t>当前选择数量{0}/{1}</t>
+          <t>输入名字...</t>
         </is>
       </c>
       <c r="D159" s="0" t="inlineStr">
@@ -3923,50 +3923,50 @@
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>1005003</v>
+        <v>1005001</v>
       </c>
       <c r="B160" s="0" t="n">
-        <v>1005003</v>
+        <v>1005001</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>超过选择数量上限</t>
+          <t>选择魔物</t>
         </is>
       </c>
       <c r="D160" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-生物选择</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>2000001</v>
+        <v>1005002</v>
       </c>
       <c r="B161" s="0" t="n">
-        <v>2000001</v>
+        <v>1005002</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>提示</t>
+          <t>当前选择数量{0}/{1}</t>
         </is>
       </c>
       <c r="D161" s="0" t="inlineStr">
         <is>
-          <t>popup</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>2000002</v>
+        <v>1005003</v>
       </c>
       <c r="B162" s="0" t="n">
-        <v>2000002</v>
+        <v>1005003</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>魔晶</t>
+          <t>超过选择数量上限</t>
         </is>
       </c>
       <c r="D162" s="0" t="inlineStr">
@@ -3977,32 +3977,32 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>2000003</v>
+        <v>2000001</v>
       </c>
       <c r="B163" s="0" t="n">
-        <v>2000003</v>
+        <v>2000001</v>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>声望</t>
+          <t>提示</t>
         </is>
       </c>
       <c r="D163" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>popup</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>2000004</v>
+        <v>2000002</v>
       </c>
       <c r="B164" s="0" t="n">
-        <v>2000004</v>
+        <v>2000002</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>排序：稀有度</t>
+          <t>魔晶</t>
         </is>
       </c>
       <c r="D164" s="0" t="inlineStr">
@@ -4013,14 +4013,14 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>2000005</v>
+        <v>2000003</v>
       </c>
       <c r="B165" s="0" t="n">
-        <v>2000005</v>
+        <v>2000003</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>排序：等级</t>
+          <t>声望</t>
         </is>
       </c>
       <c r="D165" s="0" t="inlineStr">
@@ -4031,14 +4031,14 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="B166" s="0" t="n">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>排序：阵容</t>
+          <t>排序：稀有度</t>
         </is>
       </c>
       <c r="D166" s="0" t="inlineStr">
@@ -4049,14 +4049,14 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>2000007</v>
+        <v>2000005</v>
       </c>
       <c r="B167" s="0" t="n">
-        <v>2000007</v>
+        <v>2000005</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>排序：名字</t>
+          <t>排序：等级</t>
         </is>
       </c>
       <c r="D167" s="0" t="inlineStr">
@@ -4067,14 +4067,14 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>2000008</v>
+        <v>2000006</v>
       </c>
       <c r="B168" s="0" t="n">
-        <v>2000008</v>
+        <v>2000006</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>稀有度:{0}</t>
+          <t>排序：阵容</t>
         </is>
       </c>
       <c r="D168" s="0" t="inlineStr">
@@ -4085,14 +4085,14 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>2000009</v>
+        <v>2000007</v>
       </c>
       <c r="B169" s="0" t="n">
-        <v>2000009</v>
+        <v>2000007</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>所属:{0}</t>
+          <t>排序：名字</t>
         </is>
       </c>
       <c r="D169" s="0" t="inlineStr">
@@ -4103,14 +4103,14 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>2000010</v>
+        <v>2000008</v>
       </c>
       <c r="B170" s="0" t="n">
-        <v>2000010</v>
+        <v>2000008</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>道具名字:{0}</t>
+          <t>稀有度:{0}</t>
         </is>
       </c>
       <c r="D170" s="0" t="inlineStr">
@@ -4121,14 +4121,14 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>2000011</v>
+        <v>2000009</v>
       </c>
       <c r="B171" s="0" t="n">
-        <v>2000011</v>
+        <v>2000009</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>排序：同类</t>
+          <t>所属:{0}</t>
         </is>
       </c>
       <c r="D171" s="0" t="inlineStr">
@@ -4139,14 +4139,14 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>2000012</v>
+        <v>2000010</v>
       </c>
       <c r="B172" s="0" t="n">
-        <v>2000012</v>
+        <v>2000010</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>正序</t>
+          <t>道具名字:{0}</t>
         </is>
       </c>
       <c r="D172" s="0" t="inlineStr">
@@ -4157,14 +4157,14 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>2000013</v>
+        <v>2000011</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>2000013</v>
+        <v>2000011</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>倒序</t>
+          <t>排序：同类</t>
         </is>
       </c>
       <c r="D173" s="0" t="inlineStr">
@@ -4175,14 +4175,14 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>2000014</v>
+        <v>2000012</v>
       </c>
       <c r="B174" s="0" t="n">
-        <v>2000014</v>
+        <v>2000012</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>筛选排序</t>
+          <t>正序</t>
         </is>
       </c>
       <c r="D174" s="0" t="inlineStr">
@@ -4193,14 +4193,14 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>2000015</v>
+        <v>2000013</v>
       </c>
       <c r="B175" s="0" t="n">
-        <v>2000015</v>
+        <v>2000013</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>没有相关道具</t>
+          <t>倒序</t>
         </is>
       </c>
       <c r="D175" s="0" t="inlineStr">
@@ -4211,14 +4211,14 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>2000016</v>
+        <v>2000014</v>
       </c>
       <c r="B176" s="0" t="n">
-        <v>2000016</v>
+        <v>2000014</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>没有相关魔物</t>
+          <t>筛选排序</t>
         </is>
       </c>
       <c r="D176" s="0" t="inlineStr">
@@ -4229,14 +4229,14 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>2000017</v>
+        <v>2000015</v>
       </c>
       <c r="B177" s="0" t="n">
-        <v>2000017</v>
+        <v>2000015</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>没有可孕育的生物</t>
+          <t>没有相关道具</t>
         </is>
       </c>
       <c r="D177" s="0" t="inlineStr">
@@ -4247,32 +4247,32 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>3000001</v>
+        <v>2000016</v>
       </c>
       <c r="B178" s="0" t="n">
-        <v>3000001</v>
+        <v>2000016</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t>没有足够的魔晶</t>
+          <t>没有相关魔物</t>
         </is>
       </c>
       <c r="D178" s="0" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>3000002</v>
+        <v>2000017</v>
       </c>
       <c r="B179" s="0" t="n">
-        <v>3000002</v>
+        <v>2000017</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
+          <t>没有可孕育的生物</t>
         </is>
       </c>
       <c r="D179" s="0" t="inlineStr">
@@ -4283,32 +4283,32 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>3000003</v>
+        <v>3000001</v>
       </c>
       <c r="B180" s="0" t="n">
-        <v>3000003</v>
+        <v>3000001</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t>修改名字成功！</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="D180" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>3000004</v>
+        <v>3000002</v>
       </c>
       <c r="B181" s="0" t="n">
-        <v>3000004</v>
+        <v>3000002</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物！</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="D181" s="0" t="inlineStr">
@@ -4319,14 +4319,14 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>3000005</v>
+        <v>3000003</v>
       </c>
       <c r="B182" s="0" t="n">
-        <v>3000005</v>
+        <v>3000003</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t>转生成功！</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="D182" s="0" t="inlineStr">
@@ -4337,32 +4337,32 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
-        <v>4000006</v>
+        <v>3000004</v>
       </c>
       <c r="B183" s="0" t="n">
-        <v>4000006</v>
+        <v>3000004</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="D183" s="0" t="inlineStr">
         <is>
-          <t>Achievement-进度</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="n">
-        <v>4000008</v>
+        <v>3000005</v>
       </c>
       <c r="B184" s="0" t="n">
-        <v>4000008</v>
+        <v>3000005</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t>领取成功！</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="D184" s="0" t="inlineStr">
@@ -4373,32 +4373,32 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="n">
-        <v>4000010</v>
+        <v>4000006</v>
       </c>
       <c r="B185" s="0" t="n">
-        <v>4000010</v>
+        <v>4000006</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t>游玩时间</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="D185" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Achievement-进度</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="n">
-        <v>4000011</v>
+        <v>4000008</v>
       </c>
       <c r="B186" s="0" t="n">
-        <v>4000011</v>
+        <v>4000008</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t>总击杀数</t>
+          <t>领取成功！</t>
         </is>
       </c>
       <c r="D186" s="0" t="inlineStr">
@@ -4409,14 +4409,14 @@
     </row>
     <row r="187">
       <c r="A187" s="0" t="n">
-        <v>4000012</v>
+        <v>4000010</v>
       </c>
       <c r="B187" s="0" t="n">
-        <v>4000012</v>
+        <v>4000010</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
-          <t>征服通关</t>
+          <t>游玩时间</t>
         </is>
       </c>
       <c r="D187" s="0" t="inlineStr">
@@ -4427,14 +4427,14 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="n">
-        <v>4000013</v>
+        <v>4000011</v>
       </c>
       <c r="B188" s="0" t="n">
-        <v>4000013</v>
+        <v>4000011</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t>难度{0}</t>
+          <t>总击杀数</t>
         </is>
       </c>
       <c r="D188" s="0" t="inlineStr">
@@ -4445,14 +4445,14 @@
     </row>
     <row r="189" ht="12" customHeight="1" s="1">
       <c r="A189" s="0" t="n">
-        <v>4000014</v>
+        <v>4000012</v>
       </c>
       <c r="B189" s="0" t="n">
-        <v>4000014</v>
+        <v>4000012</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>征服通关</t>
         </is>
       </c>
       <c r="D189" s="0" t="inlineStr">
@@ -4463,14 +4463,14 @@
     </row>
     <row r="190" ht="12" customHeight="1" s="1">
       <c r="A190" s="0" t="n">
-        <v>4000015</v>
+        <v>4000013</v>
       </c>
       <c r="B190" s="0" t="n">
-        <v>4000015</v>
+        <v>4000013</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
-          <t>总通关次数</t>
+          <t>难度{0}</t>
         </is>
       </c>
       <c r="D190" s="0" t="inlineStr">
@@ -4481,42 +4481,76 @@
     </row>
     <row r="191" ht="12" customHeight="1" s="1">
       <c r="A191" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="B191" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="C191" s="0" t="inlineStr">
+        <is>
+          <t>{0}时{1}分</t>
+        </is>
+      </c>
+      <c r="D191" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="12" customHeight="1" s="1">
+      <c r="A192" s="0" t="n">
+        <v>4000015</v>
+      </c>
+      <c r="B192" s="0" t="n">
+        <v>4000015</v>
+      </c>
+      <c r="C192" s="0" t="inlineStr">
+        <is>
+          <t>总通关次数</t>
+        </is>
+      </c>
+      <c r="D192" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="12" customHeight="1" s="1">
+      <c r="A193" s="0" t="n">
         <v>4000016</v>
       </c>
-      <c r="B191" s="0" t="n">
+      <c r="B193" s="0" t="n">
         <v>4000016</v>
       </c>
-      <c r="C191" s="0" t="inlineStr">
+      <c r="C193" s="0" t="inlineStr">
         <is>
           <t>Lv.{0}/{1}</t>
         </is>
       </c>
-      <c r="D191" s="0" t="inlineStr">
+      <c r="D193" s="0" t="inlineStr">
         <is>
           <t>Achievement-等级</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="12" customHeight="1" s="1">
-      <c r="A192" t="n">
+    <row r="194" ht="12" customHeight="1" s="1">
+      <c r="A194" s="0" t="n">
         <v>4000017</v>
       </c>
-      <c r="B192" t="n">
+      <c r="B194" s="0" t="n">
         <v>4000017</v>
       </c>
-      <c r="C192" t="inlineStr">
+      <c r="C194" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="D194" s="0" t="inlineStr">
         <is>
           <t>Achievement-已完成</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="12" customHeight="1" s="1"/>
-    <row r="194" ht="12" customHeight="1" s="1"/>
     <row r="195" ht="12" customHeight="1" s="1"/>
     <row r="196" ht="12" customHeight="1" s="1"/>
     <row r="197" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D198"/>
+  <dimension ref="A1:D203"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.375" customWidth="1" style="1" min="1" max="1"/>
@@ -3395,13 +3395,13 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="n">
+      <c r="A131" s="0" t="n">
         <v>61008</v>
       </c>
-      <c r="B131" t="n">
+      <c r="B131" s="0" t="n">
         <v>61008</v>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C131" s="0" t="inlineStr">
         <is>
           <t>献祭失败，祭品已消耗</t>
         </is>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>排序：阵容</t>
+          <t>阵容</t>
         </is>
       </c>
       <c r="D172" s="0" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>排序：同类</t>
+          <t>同类</t>
         </is>
       </c>
       <c r="D177" s="0" t="inlineStr">
@@ -4237,14 +4237,14 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>2000012</v>
+        <v>2000014</v>
       </c>
       <c r="B178" s="0" t="n">
-        <v>2000012</v>
+        <v>2000014</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t>正序</t>
+          <t>筛选排序</t>
         </is>
       </c>
       <c r="D178" s="0" t="inlineStr">
@@ -4255,14 +4255,14 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>2000013</v>
+        <v>2000015</v>
       </c>
       <c r="B179" s="0" t="n">
-        <v>2000013</v>
+        <v>2000015</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t>倒序</t>
+          <t>没有相关道具</t>
         </is>
       </c>
       <c r="D179" s="0" t="inlineStr">
@@ -4273,14 +4273,14 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>2000014</v>
+        <v>2000016</v>
       </c>
       <c r="B180" s="0" t="n">
-        <v>2000014</v>
+        <v>2000016</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t>筛选排序</t>
+          <t>没有相关魔物</t>
         </is>
       </c>
       <c r="D180" s="0" t="inlineStr">
@@ -4291,14 +4291,14 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>2000015</v>
+        <v>2000017</v>
       </c>
       <c r="B181" s="0" t="n">
-        <v>2000015</v>
+        <v>2000017</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t>没有相关道具</t>
+          <t>没有可孕育的生物</t>
         </is>
       </c>
       <c r="D181" s="0" t="inlineStr">
@@ -4309,14 +4309,14 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>2000016</v>
+        <v>2000018</v>
       </c>
       <c r="B182" s="0" t="n">
-        <v>2000016</v>
+        <v>2000018</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t>没有相关魔物</t>
+          <t>稀有度</t>
         </is>
       </c>
       <c r="D182" s="0" t="inlineStr">
@@ -4327,14 +4327,14 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
-        <v>2000017</v>
+        <v>2000019</v>
       </c>
       <c r="B183" s="0" t="n">
-        <v>2000017</v>
+        <v>2000019</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
-          <t>没有可孕育的生物</t>
+          <t>名字</t>
         </is>
       </c>
       <c r="D183" s="0" t="inlineStr">
@@ -4345,32 +4345,32 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="n">
-        <v>3000001</v>
+        <v>2000020</v>
       </c>
       <c r="B184" s="0" t="n">
-        <v>3000001</v>
+        <v>2000020</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t>没有足够的魔晶</t>
+          <t>等级</t>
         </is>
       </c>
       <c r="D184" s="0" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="n">
-        <v>3000002</v>
+        <v>2000021</v>
       </c>
       <c r="B185" s="0" t="n">
-        <v>3000002</v>
+        <v>2000021</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
+          <t>战斗</t>
         </is>
       </c>
       <c r="D185" s="0" t="inlineStr">
@@ -4381,14 +4381,14 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="n">
-        <v>3000003</v>
+        <v>2000022</v>
       </c>
       <c r="B186" s="0" t="n">
-        <v>3000003</v>
+        <v>2000022</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t>修改名字成功！</t>
+          <t>其它</t>
         </is>
       </c>
       <c r="D186" s="0" t="inlineStr">
@@ -4398,36 +4398,36 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="0" t="n">
-        <v>3000004</v>
-      </c>
-      <c r="B187" s="0" t="n">
-        <v>3000004</v>
-      </c>
-      <c r="C187" s="0" t="inlineStr">
-        <is>
-          <t>还未选择魔物！</t>
-        </is>
-      </c>
-      <c r="D187" s="0" t="inlineStr">
+      <c r="A187" t="n">
+        <v>2000023</v>
+      </c>
+      <c r="B187" t="n">
+        <v>2000023</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>低等级...</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
         <is>
           <t>|</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="0" t="n">
-        <v>3000005</v>
-      </c>
-      <c r="B188" s="0" t="n">
-        <v>3000005</v>
-      </c>
-      <c r="C188" s="0" t="inlineStr">
-        <is>
-          <t>转生成功！</t>
-        </is>
-      </c>
-      <c r="D188" s="0" t="inlineStr">
+      <c r="A188" t="n">
+        <v>2000024</v>
+      </c>
+      <c r="B188" t="n">
+        <v>2000024</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>高等级...</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
         <is>
           <t>|</t>
         </is>
@@ -4435,32 +4435,32 @@
     </row>
     <row r="189">
       <c r="A189" s="0" t="n">
-        <v>4000006</v>
+        <v>3000001</v>
       </c>
       <c r="B189" s="0" t="n">
-        <v>4000006</v>
+        <v>3000001</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="D189" s="0" t="inlineStr">
         <is>
-          <t>Achievement-进度</t>
+          <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="190" ht="12" customHeight="1" s="1">
       <c r="A190" s="0" t="n">
-        <v>4000008</v>
+        <v>3000002</v>
       </c>
       <c r="B190" s="0" t="n">
-        <v>4000008</v>
+        <v>3000002</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
-          <t>领取成功！</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="D190" s="0" t="inlineStr">
@@ -4471,14 +4471,14 @@
     </row>
     <row r="191" ht="12" customHeight="1" s="1">
       <c r="A191" s="0" t="n">
-        <v>4000010</v>
+        <v>3000003</v>
       </c>
       <c r="B191" s="0" t="n">
-        <v>4000010</v>
+        <v>3000003</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
-          <t>游玩时间</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="D191" s="0" t="inlineStr">
@@ -4489,14 +4489,14 @@
     </row>
     <row r="192" ht="12" customHeight="1" s="1">
       <c r="A192" s="0" t="n">
-        <v>4000011</v>
+        <v>3000004</v>
       </c>
       <c r="B192" s="0" t="n">
-        <v>4000011</v>
+        <v>3000004</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
-          <t>总击杀数</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="D192" s="0" t="inlineStr">
@@ -4507,14 +4507,14 @@
     </row>
     <row r="193" ht="12" customHeight="1" s="1">
       <c r="A193" s="0" t="n">
-        <v>4000012</v>
+        <v>3000005</v>
       </c>
       <c r="B193" s="0" t="n">
-        <v>4000012</v>
+        <v>3000005</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t>征服通关</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="D193" s="0" t="inlineStr">
@@ -4525,32 +4525,32 @@
     </row>
     <row r="194" ht="12" customHeight="1" s="1">
       <c r="A194" s="0" t="n">
-        <v>4000013</v>
+        <v>4000006</v>
       </c>
       <c r="B194" s="0" t="n">
-        <v>4000013</v>
+        <v>4000006</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
-          <t>难度{0}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="D194" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Achievement-进度</t>
         </is>
       </c>
     </row>
     <row r="195" ht="12" customHeight="1" s="1">
       <c r="A195" s="0" t="n">
-        <v>4000014</v>
+        <v>4000008</v>
       </c>
       <c r="B195" s="0" t="n">
-        <v>4000014</v>
+        <v>4000008</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>领取成功！</t>
         </is>
       </c>
       <c r="D195" s="0" t="inlineStr">
@@ -4561,14 +4561,14 @@
     </row>
     <row r="196" ht="12" customHeight="1" s="1">
       <c r="A196" s="0" t="n">
-        <v>4000015</v>
+        <v>4000010</v>
       </c>
       <c r="B196" s="0" t="n">
-        <v>4000015</v>
+        <v>4000010</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t>总通关次数</t>
+          <t>游玩时间</t>
         </is>
       </c>
       <c r="D196" s="0" t="inlineStr">
@@ -4579,45 +4579,130 @@
     </row>
     <row r="197" ht="12" customHeight="1" s="1">
       <c r="A197" s="0" t="n">
-        <v>4000016</v>
+        <v>4000011</v>
       </c>
       <c r="B197" s="0" t="n">
-        <v>4000016</v>
+        <v>4000011</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}/{1}</t>
+          <t>总击杀数</t>
         </is>
       </c>
       <c r="D197" s="0" t="inlineStr">
         <is>
-          <t>Achievement-等级</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="198" ht="12" customHeight="1" s="1">
       <c r="A198" s="0" t="n">
+        <v>4000012</v>
+      </c>
+      <c r="B198" s="0" t="n">
+        <v>4000012</v>
+      </c>
+      <c r="C198" s="0" t="inlineStr">
+        <is>
+          <t>征服通关</t>
+        </is>
+      </c>
+      <c r="D198" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="12" customHeight="1" s="1">
+      <c r="A199" s="0" t="n">
+        <v>4000013</v>
+      </c>
+      <c r="B199" s="0" t="n">
+        <v>4000013</v>
+      </c>
+      <c r="C199" s="0" t="inlineStr">
+        <is>
+          <t>难度{0}</t>
+        </is>
+      </c>
+      <c r="D199" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="12" customHeight="1" s="1">
+      <c r="A200" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="B200" s="0" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="C200" s="0" t="inlineStr">
+        <is>
+          <t>{0}时{1}分</t>
+        </is>
+      </c>
+      <c r="D200" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="12" customHeight="1" s="1">
+      <c r="A201" s="0" t="n">
+        <v>4000015</v>
+      </c>
+      <c r="B201" s="0" t="n">
+        <v>4000015</v>
+      </c>
+      <c r="C201" s="0" t="inlineStr">
+        <is>
+          <t>总通关次数</t>
+        </is>
+      </c>
+      <c r="D201" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="12" customHeight="1" s="1">
+      <c r="A202" s="0" t="n">
+        <v>4000016</v>
+      </c>
+      <c r="B202" s="0" t="n">
+        <v>4000016</v>
+      </c>
+      <c r="C202" s="0" t="inlineStr">
+        <is>
+          <t>Lv.{0}/{1}</t>
+        </is>
+      </c>
+      <c r="D202" s="0" t="inlineStr">
+        <is>
+          <t>Achievement-等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="12" customHeight="1" s="1">
+      <c r="A203" s="0" t="n">
         <v>4000017</v>
       </c>
-      <c r="B198" s="0" t="n">
+      <c r="B203" s="0" t="n">
         <v>4000017</v>
       </c>
-      <c r="C198" s="0" t="inlineStr">
+      <c r="C203" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="D198" s="0" t="inlineStr">
+      <c r="D203" s="0" t="inlineStr">
         <is>
           <t>Achievement-已完成</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="12" customHeight="1" s="1"/>
-    <row r="200" ht="12" customHeight="1" s="1"/>
-    <row r="201" ht="12" customHeight="1" s="1"/>
-    <row r="202" ht="12" customHeight="1" s="1"/>
-    <row r="203" ht="12" customHeight="1" s="1"/>
     <row r="204" ht="12" customHeight="1" s="1"/>
     <row r="205" ht="12" customHeight="1" s="1"/>
     <row r="206" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D203"/>
+  <dimension ref="A1:D205"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.375" customWidth="1" style="1" min="1" max="1"/>
@@ -1601,50 +1601,50 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="n">
-        <v>501</v>
+        <v>414</v>
       </c>
       <c r="B31" s="0" t="n">
-        <v>501</v>
+        <v>414</v>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>是否退出当前征服之旅，并回到基地？（退出之后会损失所有进度）</t>
+          <t>路径长度</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>游戏地图</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="n">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B32" s="0" t="n">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>是否前往？</t>
+          <t>是否退出当前征服之旅，并回到基地？（退出之后会损失所有进度）</t>
         </is>
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>游戏地图</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B33" s="0" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>是否结束当前战斗？退出后当前战斗进度将不会保留。</t>
+          <t>是否前往？</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
@@ -1655,50 +1655,50 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="n">
-        <v>1001</v>
+        <v>503</v>
       </c>
       <c r="B34" s="0" t="n">
-        <v>1001</v>
+        <v>503</v>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>头</t>
+          <t>是否结束当前战斗？退出后当前战斗进度将不会保留。</t>
         </is>
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
-          <t>枚举皮肤</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B35" s="0" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>帽子</t>
+          <t>头</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>枚举皮肤</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B36" s="0" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>发型</t>
+          <t>帽子</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
@@ -1709,14 +1709,14 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B37" s="0" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>身体</t>
+          <t>发型</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
@@ -1727,14 +1727,14 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B38" s="0" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>眼睛</t>
+          <t>身体</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
@@ -1745,14 +1745,14 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="n">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B39" s="0" t="n">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>嘴巴</t>
+          <t>眼睛</t>
         </is>
       </c>
       <c r="D39" s="0" t="inlineStr">
@@ -1763,50 +1763,50 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>2001</v>
+        <v>1006</v>
       </c>
       <c r="B40" s="0" t="n">
-        <v>2001</v>
+        <v>1006</v>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t>监视之塔</t>
+          <t>嘴巴</t>
         </is>
       </c>
       <c r="D40" s="0" t="inlineStr">
         <is>
-          <t>枚举交互类型</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B41" s="0" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>传送门</t>
+          <t>监视之塔</t>
         </is>
       </c>
       <c r="D41" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>枚举交互类型</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B42" s="0" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>终焉议会</t>
+          <t>传送门</t>
         </is>
       </c>
       <c r="D42" s="0" t="inlineStr">
@@ -1817,14 +1817,14 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B43" s="0" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>发言席</t>
+          <t>终焉议会</t>
         </is>
       </c>
       <c r="D43" s="0" t="inlineStr">
@@ -1835,14 +1835,14 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B44" s="0" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>议员</t>
+          <t>发言席</t>
         </is>
       </c>
       <c r="D44" s="0" t="inlineStr">
@@ -1853,14 +1853,14 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B45" s="0" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>议员</t>
         </is>
       </c>
       <c r="D45" s="0" t="inlineStr">
@@ -1871,35 +1871,35 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>10001</v>
+        <v>2006</v>
       </c>
       <c r="B46" s="0" t="n">
-        <v>10001</v>
+        <v>2006</v>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>购买</t>
+          <t>成就</t>
         </is>
       </c>
       <c r="D46" s="0" t="inlineStr">
         <is>
-          <t>抽卡</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="0" t="n">
-        <v>10003</v>
-      </c>
-      <c r="B47" s="0" t="n">
-        <v>10003</v>
-      </c>
-      <c r="C47" s="0" t="inlineStr">
-        <is>
-          <t>下一个</t>
-        </is>
-      </c>
-      <c r="D47" s="0" t="inlineStr">
+      <c r="A47" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>刷新次数已用完</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>|</t>
         </is>
@@ -1907,32 +1907,32 @@
     </row>
     <row r="48">
       <c r="A48" s="0" t="n">
-        <v>10004</v>
+        <v>10001</v>
       </c>
       <c r="B48" s="0" t="n">
-        <v>10004</v>
+        <v>10001</v>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t>结束</t>
+          <t>购买</t>
         </is>
       </c>
       <c r="D48" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>抽卡</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="n">
-        <v>10005</v>
+        <v>10003</v>
       </c>
       <c r="B49" s="0" t="n">
-        <v>10005</v>
+        <v>10003</v>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t>再来一次</t>
+          <t>下一个</t>
         </is>
       </c>
       <c r="D49" s="0" t="inlineStr">
@@ -1943,14 +1943,14 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="n">
-        <v>10006</v>
+        <v>10004</v>
       </c>
       <c r="B50" s="0" t="n">
-        <v>10006</v>
+        <v>10004</v>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>跳过所有</t>
+          <t>结束</t>
         </is>
       </c>
       <c r="D50" s="0" t="inlineStr">
@@ -1961,14 +1961,14 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="n">
-        <v>10007</v>
+        <v>10005</v>
       </c>
       <c r="B51" s="0" t="n">
-        <v>10007</v>
+        <v>10005</v>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>展示</t>
+          <t>再来一次</t>
         </is>
       </c>
       <c r="D51" s="0" t="inlineStr">
@@ -1979,14 +1979,14 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="n">
-        <v>10008</v>
+        <v>10006</v>
       </c>
       <c r="B52" s="0" t="n">
-        <v>10008</v>
+        <v>10006</v>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>重命名</t>
+          <t>跳过所有</t>
         </is>
       </c>
       <c r="D52" s="0" t="inlineStr">
@@ -1997,32 +1997,32 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>20001</v>
+        <v>10007</v>
       </c>
       <c r="B53" s="0" t="n">
-        <v>20001</v>
+        <v>10007</v>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>阵容</t>
+          <t>展示</t>
         </is>
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>核心界面</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>20002</v>
+        <v>10008</v>
       </c>
       <c r="B54" s="0" t="n">
-        <v>20002</v>
+        <v>10008</v>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t>孕育</t>
+          <t>重命名</t>
         </is>
       </c>
       <c r="D54" s="0" t="inlineStr">
@@ -2033,32 +2033,32 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>20003</v>
+        <v>20001</v>
       </c>
       <c r="B55" s="0" t="n">
-        <v>20003</v>
+        <v>20001</v>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t>魔物</t>
+          <t>阵容</t>
         </is>
       </c>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>核心界面</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>20004</v>
+        <v>20002</v>
       </c>
       <c r="B56" s="0" t="n">
-        <v>20004</v>
+        <v>20002</v>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>研究</t>
+          <t>孕育</t>
         </is>
       </c>
       <c r="D56" s="0" t="inlineStr">
@@ -2069,14 +2069,14 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>20006</v>
+        <v>20003</v>
       </c>
       <c r="B57" s="0" t="n">
-        <v>20006</v>
+        <v>20003</v>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>魔物</t>
         </is>
       </c>
       <c r="D57" s="0" t="inlineStr">
@@ -2087,14 +2087,14 @@
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>20005</v>
+        <v>20004</v>
       </c>
       <c r="B58" s="0" t="n">
-        <v>20005</v>
+        <v>20004</v>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>进阶</t>
+          <t>研究</t>
         </is>
       </c>
       <c r="D58" s="0" t="inlineStr">
@@ -2105,32 +2105,32 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>30001</v>
+        <v>20006</v>
       </c>
       <c r="B59" s="0" t="n">
-        <v>30001</v>
+        <v>20006</v>
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t>稀</t>
+          <t>成就</t>
         </is>
       </c>
       <c r="D59" s="0" t="inlineStr">
         <is>
-          <t>阵容管理</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>30002</v>
+        <v>20005</v>
       </c>
       <c r="B60" s="0" t="n">
-        <v>30002</v>
+        <v>20005</v>
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
-          <t>级</t>
+          <t>进阶</t>
         </is>
       </c>
       <c r="D60" s="0" t="inlineStr">
@@ -2141,32 +2141,32 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>30003</v>
+        <v>30001</v>
       </c>
       <c r="B61" s="0" t="n">
-        <v>30003</v>
+        <v>30001</v>
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t>阵</t>
+          <t>稀</t>
         </is>
       </c>
       <c r="D61" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>阵容管理</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>30004</v>
+        <v>30002</v>
       </c>
       <c r="B62" s="0" t="n">
-        <v>30004</v>
+        <v>30002</v>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t>名</t>
+          <t>级</t>
         </is>
       </c>
       <c r="D62" s="0" t="inlineStr">
@@ -2177,14 +2177,14 @@
     </row>
     <row r="63" ht="14" customHeight="1" s="1">
       <c r="A63" s="0" t="n">
-        <v>30005</v>
+        <v>30003</v>
       </c>
       <c r="B63" s="0" t="n">
-        <v>30005</v>
+        <v>30003</v>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t>阵容{0}</t>
+          <t>阵</t>
         </is>
       </c>
       <c r="D63" s="0" t="inlineStr">
@@ -2195,14 +2195,14 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>30006</v>
+        <v>30004</v>
       </c>
       <c r="B64" s="0" t="n">
-        <v>30006</v>
+        <v>30004</v>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t>超过阵容魔物上限！</t>
+          <t>名</t>
         </is>
       </c>
       <c r="D64" s="0" t="inlineStr">
@@ -2213,14 +2213,14 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>30007</v>
+        <v>30005</v>
       </c>
       <c r="B65" s="0" t="n">
-        <v>30007</v>
+        <v>30005</v>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t>阵容魔物数量 {0}</t>
+          <t>阵容{0}</t>
         </is>
       </c>
       <c r="D65" s="0" t="inlineStr">
@@ -2231,32 +2231,32 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>40001</v>
+        <v>30006</v>
       </c>
       <c r="B66" s="0" t="n">
-        <v>40001</v>
+        <v>30006</v>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t>游戏</t>
+          <t>超过阵容魔物上限！</t>
         </is>
       </c>
       <c r="D66" s="0" t="inlineStr">
         <is>
-          <t>游戏设置</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>40002</v>
+        <v>30007</v>
       </c>
       <c r="B67" s="0" t="n">
-        <v>40002</v>
+        <v>30007</v>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t>画面</t>
+          <t>阵容魔物数量 {0}</t>
         </is>
       </c>
       <c r="D67" s="0" t="inlineStr">
@@ -2267,32 +2267,32 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>40003</v>
+        <v>40001</v>
       </c>
       <c r="B68" s="0" t="n">
-        <v>40003</v>
+        <v>40001</v>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>音频</t>
+          <t>游戏</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>游戏设置</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>40998</v>
+        <v>40002</v>
       </c>
       <c r="B69" s="0" t="n">
-        <v>40998</v>
+        <v>40002</v>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>已开启</t>
+          <t>画面</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">
@@ -2303,14 +2303,14 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>40999</v>
+        <v>40003</v>
       </c>
       <c r="B70" s="0" t="n">
-        <v>40999</v>
+        <v>40003</v>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>已关闭</t>
+          <t>音频</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">
@@ -2321,14 +2321,14 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
-        <v>41001</v>
+        <v>40998</v>
       </c>
       <c r="B71" s="0" t="n">
-        <v>41001</v>
+        <v>40998</v>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>语言</t>
+          <t>已开启</t>
         </is>
       </c>
       <c r="D71" s="0" t="inlineStr">
@@ -2339,14 +2339,14 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>42001</v>
+        <v>40999</v>
       </c>
       <c r="B72" s="0" t="n">
-        <v>42001</v>
+        <v>40999</v>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>屏幕分辨率</t>
+          <t>已关闭</t>
         </is>
       </c>
       <c r="D72" s="0" t="inlineStr">
@@ -2357,14 +2357,14 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>42002</v>
+        <v>41001</v>
       </c>
       <c r="B73" s="0" t="n">
-        <v>42002</v>
+        <v>41001</v>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>锁定帧数</t>
+          <t>语言</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
@@ -2375,14 +2375,14 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>42003</v>
+        <v>42001</v>
       </c>
       <c r="B74" s="0" t="n">
-        <v>42003</v>
+        <v>42001</v>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>帧数</t>
+          <t>屏幕分辨率</t>
         </is>
       </c>
       <c r="D74" s="0" t="inlineStr">
@@ -2393,14 +2393,14 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>43001</v>
+        <v>42002</v>
       </c>
       <c r="B75" s="0" t="n">
-        <v>43001</v>
+        <v>42002</v>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>音乐音量</t>
+          <t>锁定帧数</t>
         </is>
       </c>
       <c r="D75" s="0" t="inlineStr">
@@ -2411,14 +2411,14 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>43002</v>
+        <v>42003</v>
       </c>
       <c r="B76" s="0" t="n">
-        <v>43002</v>
+        <v>42003</v>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>音效音量</t>
+          <t>帧数</t>
         </is>
       </c>
       <c r="D76" s="0" t="inlineStr">
@@ -2429,32 +2429,32 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>49001</v>
+        <v>43001</v>
       </c>
       <c r="B77" s="0" t="n">
-        <v>49001</v>
+        <v>43001</v>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>游戏设置</t>
+          <t>音乐音量</t>
         </is>
       </c>
       <c r="D77" s="0" t="inlineStr">
         <is>
-          <t>游戏系统</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>49002</v>
+        <v>43002</v>
       </c>
       <c r="B78" s="0" t="n">
-        <v>49002</v>
+        <v>43002</v>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>返回主界面</t>
+          <t>音效音量</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">
@@ -2465,32 +2465,32 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>49003</v>
+        <v>49001</v>
       </c>
       <c r="B79" s="0" t="n">
-        <v>49003</v>
+        <v>49001</v>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>退出游戏</t>
+          <t>游戏设置</t>
         </is>
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>游戏系统</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>49004</v>
+        <v>49002</v>
       </c>
       <c r="B80" s="0" t="n">
-        <v>49004</v>
+        <v>49002</v>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>退出战斗</t>
+          <t>返回主界面</t>
         </is>
       </c>
       <c r="D80" s="0" t="inlineStr">
@@ -2501,32 +2501,32 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>50001</v>
+        <v>49003</v>
       </c>
       <c r="B81" s="0" t="n">
-        <v>50001</v>
+        <v>49003</v>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>退出游戏</t>
         </is>
       </c>
       <c r="D81" s="0" t="inlineStr">
         <is>
-          <t>战斗结算界面</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>50002</v>
+        <v>49004</v>
       </c>
       <c r="B82" s="0" t="n">
-        <v>50002</v>
+        <v>49004</v>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>击杀</t>
+          <t>退出战斗</t>
         </is>
       </c>
       <c r="D82" s="0" t="inlineStr">
@@ -2537,32 +2537,32 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>50003</v>
+        <v>50001</v>
       </c>
       <c r="B83" s="0" t="n">
-        <v>50003</v>
+        <v>50001</v>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t>经验</t>
+          <t>伤害</t>
         </is>
       </c>
       <c r="D83" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗结算界面</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>50004</v>
+        <v>50002</v>
       </c>
       <c r="B84" s="0" t="n">
-        <v>50004</v>
+        <v>50002</v>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>承伤</t>
+          <t>击杀</t>
         </is>
       </c>
       <c r="D84" s="0" t="inlineStr">
@@ -2573,32 +2573,32 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>50005</v>
+        <v>50003</v>
       </c>
       <c r="B85" s="0" t="n">
-        <v>50005</v>
+        <v>50003</v>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>当前征程：{0}/{1}</t>
+          <t>经验</t>
         </is>
       </c>
       <c r="D85" s="0" t="inlineStr">
         <is>
-          <t>战斗主界面</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>50006</v>
+        <v>50004</v>
       </c>
       <c r="B86" s="0" t="n">
-        <v>50006</v>
+        <v>50004</v>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>魔力不足</t>
+          <t>承伤</t>
         </is>
       </c>
       <c r="D86" s="0" t="inlineStr">
@@ -2609,86 +2609,86 @@
     </row>
     <row r="87" ht="12" customHeight="1" s="1">
       <c r="A87" s="0" t="n">
-        <v>50007</v>
+        <v>50005</v>
       </c>
       <c r="B87" s="0" t="n">
-        <v>50007</v>
+        <v>50005</v>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>治疗</t>
+          <t>当前征程：{0}/{1}</t>
         </is>
       </c>
       <c r="D87" s="0" t="inlineStr">
         <is>
-          <t>战斗结算界面</t>
+          <t>战斗主界面</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>50008</v>
+        <v>50006</v>
       </c>
       <c r="B88" s="0" t="n">
-        <v>50008</v>
+        <v>50006</v>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t>受疗</t>
+          <t>魔力不足</t>
         </is>
       </c>
       <c r="D88" s="0" t="inlineStr">
         <is>
-          <t>战斗结算界面</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>50101</v>
+        <v>50007</v>
       </c>
       <c r="B89" s="0" t="n">
-        <v>50101</v>
+        <v>50007</v>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>继续</t>
+          <t>治疗</t>
         </is>
       </c>
       <c r="D89" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗结算界面</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>51001</v>
+        <v>50008</v>
       </c>
       <c r="B90" s="0" t="n">
-        <v>51001</v>
+        <v>50008</v>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>深渊馈赠</t>
+          <t>受疗</t>
         </is>
       </c>
       <c r="D90" s="0" t="inlineStr">
         <is>
-          <t>战斗深渊馈赠</t>
+          <t>战斗结算界面</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>51002</v>
+        <v>50101</v>
       </c>
       <c r="B91" s="0" t="n">
-        <v>51002</v>
+        <v>50101</v>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t>选择一个深渊馈赠</t>
+          <t>继续</t>
         </is>
       </c>
       <c r="D91" s="0" t="inlineStr">
@@ -2699,46 +2699,46 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>51003</v>
+        <v>51001</v>
       </c>
       <c r="B92" s="0" t="n">
-        <v>51003</v>
+        <v>51001</v>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t>跳过</t>
+          <t>深渊馈赠</t>
         </is>
       </c>
       <c r="D92" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗深渊馈赠</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>52001</v>
+        <v>51002</v>
       </c>
       <c r="B93" s="0" t="n">
-        <v>52001</v>
+        <v>51002</v>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t>选择奖励</t>
+          <t>选择一个深渊馈赠</t>
         </is>
       </c>
       <c r="D93" s="0" t="inlineStr">
         <is>
-          <t>奖励选择</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>52002</v>
+        <v>51003</v>
       </c>
       <c r="B94" s="0" t="n">
-        <v>52002</v>
+        <v>51003</v>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
@@ -2753,32 +2753,32 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>52003</v>
+        <v>52001</v>
       </c>
       <c r="B95" s="0" t="n">
-        <v>52003</v>
+        <v>52001</v>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t>剩余可选择次数{0}/{1}</t>
+          <t>选择奖励</t>
         </is>
       </c>
       <c r="D95" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>奖励选择</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>52004</v>
+        <v>52002</v>
       </c>
       <c r="B96" s="0" t="n">
-        <v>52004</v>
+        <v>52002</v>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t>没有可选择次数</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="D96" s="0" t="inlineStr">
@@ -2789,14 +2789,14 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>52005</v>
+        <v>52003</v>
       </c>
       <c r="B97" s="0" t="n">
-        <v>52005</v>
+        <v>52003</v>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>还有可选择次数，是否仍要结束选择奖励？</t>
+          <t>剩余可选择次数{0}/{1}</t>
         </is>
       </c>
       <c r="D97" s="0" t="inlineStr">
@@ -2807,32 +2807,32 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>53000</v>
+        <v>52004</v>
       </c>
       <c r="B98" s="0" t="n">
-        <v>53000</v>
+        <v>52004</v>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>终焉议会</t>
+          <t>没有可选择次数</t>
         </is>
       </c>
       <c r="D98" s="0" t="inlineStr">
         <is>
-          <t>终焉议会</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>53001</v>
+        <v>52005</v>
       </c>
       <c r="B99" s="0" t="n">
-        <v>53001</v>
+        <v>52005</v>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
-          <t>选择一个议案</t>
+          <t>还有可选择次数，是否仍要结束选择奖励？</t>
         </is>
       </c>
       <c r="D99" s="0" t="inlineStr">
@@ -2843,32 +2843,32 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>53002</v>
+        <v>53000</v>
       </c>
       <c r="B100" s="0" t="n">
-        <v>53002</v>
+        <v>53000</v>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
-          <t>是否提交议案《{0}》，并且前往终焉议会？</t>
+          <t>终焉议会</t>
         </is>
       </c>
       <c r="D100" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>终焉议会</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>53003</v>
+        <v>53001</v>
       </c>
       <c r="B101" s="0" t="n">
-        <v>53003</v>
+        <v>53001</v>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
-          <t>通过率   {0}%</t>
+          <t>选择一个议案</t>
         </is>
       </c>
       <c r="D101" s="0" t="inlineStr">
@@ -2879,14 +2879,14 @@
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>53004</v>
+        <v>53002</v>
       </c>
       <c r="B102" s="0" t="n">
-        <v>53004</v>
+        <v>53002</v>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t>开始投票</t>
+          <t>是否提交议案《{0}》，并且前往终焉议会？</t>
         </is>
       </c>
       <c r="D102" s="0" t="inlineStr">
@@ -2897,14 +2897,14 @@
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>53005</v>
+        <v>53003</v>
       </c>
       <c r="B103" s="0" t="n">
-        <v>53005</v>
+        <v>53003</v>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
-          <t>离开议会</t>
+          <t>通过率   {0}%</t>
         </is>
       </c>
       <c r="D103" s="0" t="inlineStr">
@@ -2915,14 +2915,14 @@
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>53006</v>
+        <v>53004</v>
       </c>
       <c r="B104" s="0" t="n">
-        <v>53006</v>
+        <v>53004</v>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
-          <t>赞成</t>
+          <t>开始投票</t>
         </is>
       </c>
       <c r="D104" s="0" t="inlineStr">
@@ -2933,14 +2933,14 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>53007</v>
+        <v>53005</v>
       </c>
       <c r="B105" s="0" t="n">
-        <v>53007</v>
+        <v>53005</v>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
-          <t>反对</t>
+          <t>离开议会</t>
         </is>
       </c>
       <c r="D105" s="0" t="inlineStr">
@@ -2951,14 +2951,14 @@
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>53008</v>
+        <v>53006</v>
       </c>
       <c r="B106" s="0" t="n">
-        <v>53008</v>
+        <v>53006</v>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>赞成</t>
         </is>
       </c>
       <c r="D106" s="0" t="inlineStr">
@@ -2969,14 +2969,14 @@
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>53009</v>
+        <v>53007</v>
       </c>
       <c r="B107" s="0" t="n">
-        <v>53009</v>
+        <v>53007</v>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
-          <t>否决</t>
+          <t>反对</t>
         </is>
       </c>
       <c r="D107" s="0" t="inlineStr">
@@ -2987,14 +2987,14 @@
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>53010</v>
+        <v>53008</v>
       </c>
       <c r="B108" s="0" t="n">
-        <v>53010</v>
+        <v>53008</v>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
-          <t>暴力说服</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="D108" s="0" t="inlineStr">
@@ -3005,14 +3005,14 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>53011</v>
+        <v>53009</v>
       </c>
       <c r="B109" s="0" t="n">
-        <v>53011</v>
+        <v>53009</v>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
-          <t>自由活动</t>
+          <t>否决</t>
         </is>
       </c>
       <c r="D109" s="0" t="inlineStr">
@@ -3023,14 +3023,14 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>53012</v>
+        <v>53010</v>
       </c>
       <c r="B110" s="0" t="n">
-        <v>53012</v>
+        <v>53010</v>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
-          <t>是否提交议案《{0}》？</t>
+          <t>暴力说服</t>
         </is>
       </c>
       <c r="D110" s="0" t="inlineStr">
@@ -3041,14 +3041,14 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>53013</v>
+        <v>53011</v>
       </c>
       <c r="B111" s="0" t="n">
-        <v>53013</v>
+        <v>53011</v>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t>是否确认离开议会？离开后消耗的资源不会返还。</t>
+          <t>自由活动</t>
         </is>
       </c>
       <c r="D111" s="0" t="inlineStr">
@@ -3059,14 +3059,14 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>53014</v>
+        <v>53012</v>
       </c>
       <c r="B112" s="0" t="n">
-        <v>53014</v>
+        <v>53012</v>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
-          <t>当前议案通过率:{0}%</t>
+          <t>是否提交议案《{0}》？</t>
         </is>
       </c>
       <c r="D112" s="0" t="inlineStr">
@@ -3077,14 +3077,14 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>54001</v>
+        <v>53013</v>
       </c>
       <c r="B113" s="0" t="n">
-        <v>54001</v>
+        <v>53013</v>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t>没有数据</t>
+          <t>是否确认离开议会？离开后消耗的资源不会返还。</t>
         </is>
       </c>
       <c r="D113" s="0" t="inlineStr">
@@ -3095,32 +3095,32 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>55001</v>
+        <v>53014</v>
       </c>
       <c r="B114" s="0" t="n">
-        <v>55001</v>
+        <v>53014</v>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t>魔王讨伐者正在靠近中...</t>
+          <t>当前议案通过率:{0}%</t>
         </is>
       </c>
       <c r="D114" s="0" t="inlineStr">
         <is>
-          <t>战斗Boss展示</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>55002</v>
+        <v>54001</v>
       </c>
       <c r="B115" s="0" t="n">
-        <v>55002</v>
+        <v>54001</v>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>一大波勇者正在靠近中…</t>
+          <t>没有数据</t>
         </is>
       </c>
       <c r="D115" s="0" t="inlineStr">
@@ -3131,32 +3131,32 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>55003</v>
+        <v>55001</v>
       </c>
       <c r="B116" s="0" t="n">
-        <v>55003</v>
+        <v>55001</v>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t>注意！英雄队伍正在涌来…</t>
+          <t>魔王讨伐者正在靠近中...</t>
         </is>
       </c>
       <c r="D116" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗Boss展示</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>55004</v>
+        <v>55002</v>
       </c>
       <c r="B117" s="0" t="n">
-        <v>55004</v>
+        <v>55002</v>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
-          <t>侦测到讨伐部队正在接近…</t>
+          <t>一大波勇者正在靠近中…</t>
         </is>
       </c>
       <c r="D117" s="0" t="inlineStr">
@@ -3167,14 +3167,14 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>55005</v>
+        <v>55003</v>
       </c>
       <c r="B118" s="0" t="n">
-        <v>55005</v>
+        <v>55003</v>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t>勇者联军正在逼近…</t>
+          <t>注意！英雄队伍正在涌来…</t>
         </is>
       </c>
       <c r="D118" s="0" t="inlineStr">
@@ -3185,14 +3185,14 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>55006</v>
+        <v>55004</v>
       </c>
       <c r="B119" s="0" t="n">
-        <v>55006</v>
+        <v>55004</v>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>一大波自称勇者的家伙来了…</t>
+          <t>侦测到讨伐部队正在接近…</t>
         </is>
       </c>
       <c r="D119" s="0" t="inlineStr">
@@ -3203,14 +3203,14 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>55007</v>
+        <v>55005</v>
       </c>
       <c r="B120" s="0" t="n">
-        <v>55007</v>
+        <v>55005</v>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>警报：正义的伙伴们正在靠近…</t>
+          <t>勇者联军正在逼近…</t>
         </is>
       </c>
       <c r="D120" s="0" t="inlineStr">
@@ -3221,32 +3221,32 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>60000</v>
+        <v>55006</v>
       </c>
       <c r="B121" s="0" t="n">
-        <v>60000</v>
+        <v>55006</v>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>献祭升级</t>
+          <t>一大波自称勇者的家伙来了…</t>
         </is>
       </c>
       <c r="D121" s="0" t="inlineStr">
         <is>
-          <t>生物献祭</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>60001</v>
+        <v>55007</v>
       </c>
       <c r="B122" s="0" t="n">
-        <v>60001</v>
+        <v>55007</v>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>开始献祭</t>
+          <t>警报：正义的伙伴们正在靠近…</t>
         </is>
       </c>
       <c r="D122" s="0" t="inlineStr">
@@ -3257,32 +3257,32 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>60002</v>
+        <v>60000</v>
       </c>
       <c r="B123" s="0" t="n">
-        <v>60002</v>
+        <v>60000</v>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>成功率</t>
+          <t>献祭升级</t>
         </is>
       </c>
       <c r="D123" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物献祭</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>61001</v>
+        <v>60001</v>
       </c>
       <c r="B124" s="0" t="n">
-        <v>61001</v>
+        <v>60001</v>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>还未选择献祭生物！</t>
+          <t>开始献祭</t>
         </is>
       </c>
       <c r="D124" s="0" t="inlineStr">
@@ -3293,14 +3293,14 @@
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>61002</v>
+        <v>60002</v>
       </c>
       <c r="B125" s="0" t="n">
-        <v>61002</v>
+        <v>60002</v>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>献祭生物数量达到上限！</t>
+          <t>成功率</t>
         </is>
       </c>
       <c r="D125" s="0" t="inlineStr">
@@ -3311,14 +3311,14 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>61003</v>
+        <v>61001</v>
       </c>
       <c r="B126" s="0" t="n">
-        <v>61003</v>
+        <v>61001</v>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>是否开始献祭？当前成功率{0}</t>
+          <t>还未选择献祭生物！</t>
         </is>
       </c>
       <c r="D126" s="0" t="inlineStr">
@@ -3329,14 +3329,14 @@
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>61004</v>
+        <v>61002</v>
       </c>
       <c r="B127" s="0" t="n">
-        <v>61004</v>
+        <v>61002</v>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>请分配完所有属性点</t>
+          <t>献祭生物数量达到上限！</t>
         </is>
       </c>
       <c r="D127" s="0" t="inlineStr">
@@ -3347,14 +3347,14 @@
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>61005</v>
+        <v>61003</v>
       </c>
       <c r="B128" s="0" t="n">
-        <v>61005</v>
+        <v>61003</v>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>剩余点数:{0}</t>
+          <t>是否开始献祭？当前成功率{0}</t>
         </is>
       </c>
       <c r="D128" s="0" t="inlineStr">
@@ -3365,14 +3365,14 @@
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>61006</v>
+        <v>61004</v>
       </c>
       <c r="B129" s="0" t="n">
-        <v>61006</v>
+        <v>61004</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>确认按当前方案分配属性点吗？确认后将无法更改。</t>
+          <t>请分配完所有属性点</t>
         </is>
       </c>
       <c r="D129" s="0" t="inlineStr">
@@ -3383,94 +3383,94 @@
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>61007</v>
+        <v>61005</v>
       </c>
       <c r="B130" s="0" t="n">
-        <v>61007</v>
+        <v>61005</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>献祭成功，等级提升！</t>
+          <t>剩余点数:{0}</t>
+        </is>
+      </c>
+      <c r="D130" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>61008</v>
+        <v>61006</v>
       </c>
       <c r="B131" s="0" t="n">
-        <v>61008</v>
+        <v>61006</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>献祭失败，祭品已消耗</t>
+          <t>确认按当前方案分配属性点吗？确认后将无法更改。</t>
+        </is>
+      </c>
+      <c r="D131" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>62001</v>
+        <v>61007</v>
       </c>
       <c r="B132" s="0" t="n">
-        <v>62001</v>
+        <v>61007</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t>是否开启此项研究？花费x{0}魔晶</t>
-        </is>
-      </c>
-      <c r="D132" s="0" t="inlineStr">
-        <is>
-          <t>生物研究</t>
+          <t>献祭成功，等级提升！</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>62002</v>
+        <v>61008</v>
       </c>
       <c r="B133" s="0" t="n">
-        <v>62002</v>
+        <v>61008</v>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t>设施</t>
-        </is>
-      </c>
-      <c r="D133" s="0" t="inlineStr">
-        <is>
-          <t>|</t>
+          <t>献祭失败，祭品已消耗</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>62003</v>
+        <v>62001</v>
       </c>
       <c r="B134" s="0" t="n">
-        <v>62003</v>
+        <v>62001</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t>强化</t>
+          <t>是否开启此项研究？花费x{0}魔晶</t>
         </is>
       </c>
       <c r="D134" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物研究</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>62004</v>
+        <v>62002</v>
       </c>
       <c r="B135" s="0" t="n">
-        <v>62004</v>
+        <v>62002</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t>魔物</t>
+          <t>设施</t>
         </is>
       </c>
       <c r="D135" s="0" t="inlineStr">
@@ -3481,32 +3481,32 @@
     </row>
     <row r="136" ht="12" customHeight="1" s="1">
       <c r="A136" s="0" t="n">
-        <v>63001</v>
+        <v>62003</v>
       </c>
       <c r="B136" s="0" t="n">
-        <v>63001</v>
+        <v>62003</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t>选择转生魔王外观</t>
+          <t>强化</t>
         </is>
       </c>
       <c r="D136" s="0" t="inlineStr">
         <is>
-          <t>生物外貌修改</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>63002</v>
+        <v>62004</v>
       </c>
       <c r="B137" s="0" t="n">
-        <v>63002</v>
+        <v>62004</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>魔物</t>
         </is>
       </c>
       <c r="D137" s="0" t="inlineStr">
@@ -3517,50 +3517,50 @@
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>63003</v>
+        <v>63001</v>
       </c>
       <c r="B138" s="0" t="n">
-        <v>63003</v>
+        <v>63001</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t>是否以此外观完成转生？</t>
+          <t>选择转生魔王外观</t>
         </is>
       </c>
       <c r="D138" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物外貌修改</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>64001</v>
+        <v>63002</v>
       </c>
       <c r="B139" s="0" t="n">
-        <v>64001</v>
+        <v>63002</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D139" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>64002</v>
+        <v>63003</v>
       </c>
       <c r="B140" s="0" t="n">
-        <v>64002</v>
+        <v>63003</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t>统计</t>
+          <t>是否以此外观完成转生？</t>
         </is>
       </c>
       <c r="D140" s="0" t="inlineStr">
@@ -3571,104 +3571,104 @@
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>65001</v>
+        <v>64001</v>
       </c>
       <c r="B141" s="0" t="n">
-        <v>65001</v>
+        <v>64001</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>成就</t>
         </is>
       </c>
       <c r="D141" s="0" t="inlineStr">
         <is>
-          <t>生物属性添加</t>
+          <t>成就</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>70001</v>
+        <v>64002</v>
       </c>
       <c r="B142" s="0" t="n">
-        <v>70001</v>
+        <v>64002</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t>贿赂</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="D142" s="0" t="inlineStr">
         <is>
-          <t>对话</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>80001</v>
+        <v>65001</v>
       </c>
       <c r="B143" s="0" t="n">
-        <v>80001</v>
+        <v>65001</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t>开始进阶</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D143" s="0" t="inlineStr">
         <is>
-          <t>生物进阶</t>
+          <t>生物属性添加</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>80002</v>
+        <v>70001</v>
       </c>
       <c r="B144" s="0" t="n">
-        <v>80002</v>
+        <v>70001</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t>结束进阶</t>
+          <t>贿赂</t>
         </is>
       </c>
       <c r="D144" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>对话</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>80003</v>
+        <v>80001</v>
       </c>
       <c r="B145" s="0" t="n">
-        <v>80003</v>
+        <v>80001</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t>完成进阶</t>
+          <t>开始进阶</t>
         </is>
       </c>
       <c r="D145" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物进阶</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>80004</v>
+        <v>80002</v>
       </c>
       <c r="B146" s="0" t="n">
-        <v>80004</v>
+        <v>80002</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>是否结束进阶？进阶消耗的材料不会返回</t>
+          <t>结束进阶</t>
         </is>
       </c>
       <c r="D146" s="0" t="inlineStr">
@@ -3679,14 +3679,14 @@
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>80005</v>
+        <v>80003</v>
       </c>
       <c r="B147" s="0" t="n">
-        <v>80005</v>
+        <v>80003</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t>进度</t>
+          <t>完成进阶</t>
         </is>
       </c>
       <c r="D147" s="0" t="inlineStr">
@@ -3697,14 +3697,14 @@
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>80006</v>
+        <v>80004</v>
       </c>
       <c r="B148" s="0" t="n">
-        <v>80006</v>
+        <v>80004</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t>选择进阶魔物</t>
+          <t>是否结束进阶？进阶消耗的材料不会返回</t>
         </is>
       </c>
       <c r="D148" s="0" t="inlineStr">
@@ -3715,14 +3715,14 @@
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>80007</v>
+        <v>80005</v>
       </c>
       <c r="B149" s="0" t="n">
-        <v>80007</v>
+        <v>80005</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>选择辅助魔物</t>
+          <t>进度</t>
         </is>
       </c>
       <c r="D149" s="0" t="inlineStr">
@@ -3733,14 +3733,14 @@
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>80008</v>
+        <v>80006</v>
       </c>
       <c r="B150" s="0" t="n">
-        <v>80008</v>
+        <v>80006</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物</t>
+          <t>选择进阶魔物</t>
         </is>
       </c>
       <c r="D150" s="0" t="inlineStr">
@@ -3751,14 +3751,14 @@
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>80009</v>
+        <v>80007</v>
       </c>
       <c r="B151" s="0" t="n">
-        <v>80009</v>
+        <v>80007</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>加速进阶 x{0}</t>
+          <t>选择辅助魔物</t>
         </is>
       </c>
       <c r="D151" s="0" t="inlineStr">
@@ -3769,14 +3769,14 @@
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>80010</v>
+        <v>80008</v>
       </c>
       <c r="B152" s="0" t="n">
-        <v>80010</v>
+        <v>80008</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
+          <t>还未选择魔物</t>
         </is>
       </c>
       <c r="D152" s="0" t="inlineStr">
@@ -3787,32 +3787,32 @@
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>90001</v>
+        <v>80009</v>
       </c>
       <c r="B153" s="0" t="n">
-        <v>90001</v>
+        <v>80009</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>加速进阶 x{0}</t>
         </is>
       </c>
       <c r="D153" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>90002</v>
+        <v>80010</v>
       </c>
       <c r="B154" s="0" t="n">
-        <v>90002</v>
+        <v>80010</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>魔王专属</t>
+          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
         </is>
       </c>
       <c r="D154" s="0" t="inlineStr">
@@ -3823,32 +3823,32 @@
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>1000001</v>
+        <v>90001</v>
       </c>
       <c r="B155" s="0" t="n">
-        <v>1000001</v>
+        <v>90001</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D155" s="0" t="inlineStr">
         <is>
-          <t>弹窗</t>
+          <t>通用</t>
         </is>
       </c>
     </row>
     <row r="156" ht="12" customHeight="1" s="1">
       <c r="A156" s="0" t="n">
-        <v>1000002</v>
+        <v>90002</v>
       </c>
       <c r="B156" s="0" t="n">
-        <v>1000002</v>
+        <v>90002</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>魔王专属</t>
         </is>
       </c>
       <c r="D156" s="0" t="inlineStr">
@@ -3859,86 +3859,86 @@
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>1001001</v>
+        <v>1000001</v>
       </c>
       <c r="B157" s="0" t="n">
-        <v>1001001</v>
+        <v>1000001</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>等级.{0}</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D157" s="0" t="inlineStr">
         <is>
-          <t>弹窗-卡片详情</t>
+          <t>弹窗</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>1002001</v>
+        <v>1000002</v>
       </c>
       <c r="B158" s="0" t="n">
-        <v>1002001</v>
+        <v>1000002</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>赠送</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="D158" s="0" t="inlineStr">
         <is>
-          <t>弹窗-道具选择</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>1002002</v>
+        <v>1001001</v>
       </c>
       <c r="B159" s="0" t="n">
-        <v>1002002</v>
+        <v>1001001</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>等级.{0}</t>
         </is>
       </c>
       <c r="D159" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-卡片详情</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>1003001</v>
+        <v>1002001</v>
       </c>
       <c r="B160" s="0" t="n">
-        <v>1003001</v>
+        <v>1002001</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>研究等级.{0}</t>
+          <t>赠送</t>
         </is>
       </c>
       <c r="D160" s="0" t="inlineStr">
         <is>
-          <t>弹窗-研究详情</t>
+          <t>弹窗-道具选择</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>1003002</v>
+        <v>1002002</v>
       </c>
       <c r="B161" s="0" t="n">
-        <v>1003002</v>
+        <v>1002002</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>研究等级.最大</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="D161" s="0" t="inlineStr">
@@ -3949,32 +3949,32 @@
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>1004001</v>
+        <v>1003001</v>
       </c>
       <c r="B162" s="0" t="n">
-        <v>1004001</v>
+        <v>1003001</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>取个新名字</t>
+          <t>研究等级.{0}</t>
         </is>
       </c>
       <c r="D162" s="0" t="inlineStr">
         <is>
-          <t>弹窗-重命名</t>
+          <t>弹窗-研究详情</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>1004002</v>
+        <v>1003002</v>
       </c>
       <c r="B163" s="0" t="n">
-        <v>1004002</v>
+        <v>1003002</v>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>输入名字...</t>
+          <t>研究等级.最大</t>
         </is>
       </c>
       <c r="D163" s="0" t="inlineStr">
@@ -3985,32 +3985,32 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>1005001</v>
+        <v>1004001</v>
       </c>
       <c r="B164" s="0" t="n">
-        <v>1005001</v>
+        <v>1004001</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>选择魔物</t>
+          <t>取个新名字</t>
         </is>
       </c>
       <c r="D164" s="0" t="inlineStr">
         <is>
-          <t>弹窗-生物选择</t>
+          <t>弹窗-重命名</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>1005002</v>
+        <v>1004002</v>
       </c>
       <c r="B165" s="0" t="n">
-        <v>1005002</v>
+        <v>1004002</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>当前选择数量{0}/{1}</t>
+          <t>输入名字...</t>
         </is>
       </c>
       <c r="D165" s="0" t="inlineStr">
@@ -4021,50 +4021,50 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>1005003</v>
+        <v>1005001</v>
       </c>
       <c r="B166" s="0" t="n">
-        <v>1005003</v>
+        <v>1005001</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>超过选择数量上限</t>
+          <t>选择魔物</t>
         </is>
       </c>
       <c r="D166" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-生物选择</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>2000001</v>
+        <v>1005002</v>
       </c>
       <c r="B167" s="0" t="n">
-        <v>2000001</v>
+        <v>1005002</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>提示</t>
+          <t>当前选择数量{0}/{1}</t>
         </is>
       </c>
       <c r="D167" s="0" t="inlineStr">
         <is>
-          <t>popup</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>2000002</v>
+        <v>1005003</v>
       </c>
       <c r="B168" s="0" t="n">
-        <v>2000002</v>
+        <v>1005003</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>魔晶</t>
+          <t>超过选择数量上限</t>
         </is>
       </c>
       <c r="D168" s="0" t="inlineStr">
@@ -4075,32 +4075,32 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>2000003</v>
+        <v>2000001</v>
       </c>
       <c r="B169" s="0" t="n">
-        <v>2000003</v>
+        <v>2000001</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>声望</t>
+          <t>提示</t>
         </is>
       </c>
       <c r="D169" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>popup</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>2000004</v>
+        <v>2000002</v>
       </c>
       <c r="B170" s="0" t="n">
-        <v>2000004</v>
+        <v>2000002</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>排序：稀有度</t>
+          <t>魔晶</t>
         </is>
       </c>
       <c r="D170" s="0" t="inlineStr">
@@ -4111,14 +4111,14 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>2000005</v>
+        <v>2000003</v>
       </c>
       <c r="B171" s="0" t="n">
-        <v>2000005</v>
+        <v>2000003</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>排序：等级</t>
+          <t>声望</t>
         </is>
       </c>
       <c r="D171" s="0" t="inlineStr">
@@ -4129,14 +4129,14 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="B172" s="0" t="n">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>阵容</t>
+          <t>排序：稀有度</t>
         </is>
       </c>
       <c r="D172" s="0" t="inlineStr">
@@ -4147,14 +4147,14 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>2000007</v>
+        <v>2000005</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>2000007</v>
+        <v>2000005</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>排序：名字</t>
+          <t>排序：等级</t>
         </is>
       </c>
       <c r="D173" s="0" t="inlineStr">
@@ -4165,14 +4165,14 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>2000008</v>
+        <v>2000006</v>
       </c>
       <c r="B174" s="0" t="n">
-        <v>2000008</v>
+        <v>2000006</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>稀有度:{0}</t>
+          <t>阵容</t>
         </is>
       </c>
       <c r="D174" s="0" t="inlineStr">
@@ -4183,14 +4183,14 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>2000009</v>
+        <v>2000007</v>
       </c>
       <c r="B175" s="0" t="n">
-        <v>2000009</v>
+        <v>2000007</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>所属:{0}</t>
+          <t>排序：名字</t>
         </is>
       </c>
       <c r="D175" s="0" t="inlineStr">
@@ -4201,14 +4201,14 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>2000010</v>
+        <v>2000008</v>
       </c>
       <c r="B176" s="0" t="n">
-        <v>2000010</v>
+        <v>2000008</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>道具名字:{0}</t>
+          <t>稀有度:{0}</t>
         </is>
       </c>
       <c r="D176" s="0" t="inlineStr">
@@ -4219,14 +4219,14 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>2000011</v>
+        <v>2000009</v>
       </c>
       <c r="B177" s="0" t="n">
-        <v>2000011</v>
+        <v>2000009</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>同类</t>
+          <t>所属:{0}</t>
         </is>
       </c>
       <c r="D177" s="0" t="inlineStr">
@@ -4237,14 +4237,14 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>2000014</v>
+        <v>2000010</v>
       </c>
       <c r="B178" s="0" t="n">
-        <v>2000014</v>
+        <v>2000010</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t>筛选排序</t>
+          <t>道具名字:{0}</t>
         </is>
       </c>
       <c r="D178" s="0" t="inlineStr">
@@ -4255,14 +4255,14 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>2000015</v>
+        <v>2000011</v>
       </c>
       <c r="B179" s="0" t="n">
-        <v>2000015</v>
+        <v>2000011</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t>没有相关道具</t>
+          <t>同类</t>
         </is>
       </c>
       <c r="D179" s="0" t="inlineStr">
@@ -4273,14 +4273,14 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>2000016</v>
+        <v>2000014</v>
       </c>
       <c r="B180" s="0" t="n">
-        <v>2000016</v>
+        <v>2000014</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t>没有相关魔物</t>
+          <t>筛选排序</t>
         </is>
       </c>
       <c r="D180" s="0" t="inlineStr">
@@ -4291,14 +4291,14 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>2000017</v>
+        <v>2000015</v>
       </c>
       <c r="B181" s="0" t="n">
-        <v>2000017</v>
+        <v>2000015</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t>没有可孕育的生物</t>
+          <t>没有相关道具</t>
         </is>
       </c>
       <c r="D181" s="0" t="inlineStr">
@@ -4309,14 +4309,14 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>2000018</v>
+        <v>2000016</v>
       </c>
       <c r="B182" s="0" t="n">
-        <v>2000018</v>
+        <v>2000016</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t>稀有度</t>
+          <t>没有相关魔物</t>
         </is>
       </c>
       <c r="D182" s="0" t="inlineStr">
@@ -4327,14 +4327,14 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
-        <v>2000019</v>
+        <v>2000017</v>
       </c>
       <c r="B183" s="0" t="n">
-        <v>2000019</v>
+        <v>2000017</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
-          <t>名字</t>
+          <t>没有可孕育的生物</t>
         </is>
       </c>
       <c r="D183" s="0" t="inlineStr">
@@ -4345,14 +4345,14 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="n">
-        <v>2000020</v>
+        <v>2000018</v>
       </c>
       <c r="B184" s="0" t="n">
-        <v>2000020</v>
+        <v>2000018</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t>等级</t>
+          <t>稀有度</t>
         </is>
       </c>
       <c r="D184" s="0" t="inlineStr">
@@ -4363,14 +4363,14 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="n">
-        <v>2000021</v>
+        <v>2000019</v>
       </c>
       <c r="B185" s="0" t="n">
-        <v>2000021</v>
+        <v>2000019</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t>战斗</t>
+          <t>名字</t>
         </is>
       </c>
       <c r="D185" s="0" t="inlineStr">
@@ -4381,53 +4381,53 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="n">
+        <v>2000020</v>
+      </c>
+      <c r="B186" s="0" t="n">
+        <v>2000020</v>
+      </c>
+      <c r="C186" s="0" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="D186" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="0" t="n">
+        <v>2000021</v>
+      </c>
+      <c r="B187" s="0" t="n">
+        <v>2000021</v>
+      </c>
+      <c r="C187" s="0" t="inlineStr">
+        <is>
+          <t>战斗</t>
+        </is>
+      </c>
+      <c r="D187" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="0" t="n">
         <v>2000022</v>
       </c>
-      <c r="B186" s="0" t="n">
+      <c r="B188" s="0" t="n">
         <v>2000022</v>
       </c>
-      <c r="C186" s="0" t="inlineStr">
+      <c r="C188" s="0" t="inlineStr">
         <is>
           <t>其它</t>
         </is>
       </c>
-      <c r="D186" s="0" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>2000023</v>
-      </c>
-      <c r="B187" t="n">
-        <v>2000023</v>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>低等级...</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>2000024</v>
-      </c>
-      <c r="B188" t="n">
-        <v>2000024</v>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>高等级...</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
+      <c r="D188" s="0" t="inlineStr">
         <is>
           <t>|</t>
         </is>
@@ -4435,32 +4435,32 @@
     </row>
     <row r="189">
       <c r="A189" s="0" t="n">
-        <v>3000001</v>
+        <v>2000023</v>
       </c>
       <c r="B189" s="0" t="n">
-        <v>3000001</v>
+        <v>2000023</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
-          <t>没有足够的魔晶</t>
+          <t>低等级...</t>
         </is>
       </c>
       <c r="D189" s="0" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="190" ht="12" customHeight="1" s="1">
       <c r="A190" s="0" t="n">
-        <v>3000002</v>
+        <v>2000024</v>
       </c>
       <c r="B190" s="0" t="n">
-        <v>3000002</v>
+        <v>2000024</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
+          <t>高等级...</t>
         </is>
       </c>
       <c r="D190" s="0" t="inlineStr">
@@ -4471,32 +4471,32 @@
     </row>
     <row r="191" ht="12" customHeight="1" s="1">
       <c r="A191" s="0" t="n">
-        <v>3000003</v>
+        <v>3000001</v>
       </c>
       <c r="B191" s="0" t="n">
-        <v>3000003</v>
+        <v>3000001</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
-          <t>修改名字成功！</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="D191" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="192" ht="12" customHeight="1" s="1">
       <c r="A192" s="0" t="n">
-        <v>3000004</v>
+        <v>3000002</v>
       </c>
       <c r="B192" s="0" t="n">
-        <v>3000004</v>
+        <v>3000002</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物！</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="D192" s="0" t="inlineStr">
@@ -4507,14 +4507,14 @@
     </row>
     <row r="193" ht="12" customHeight="1" s="1">
       <c r="A193" s="0" t="n">
-        <v>3000005</v>
+        <v>3000003</v>
       </c>
       <c r="B193" s="0" t="n">
-        <v>3000005</v>
+        <v>3000003</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t>转生成功！</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="D193" s="0" t="inlineStr">
@@ -4525,32 +4525,32 @@
     </row>
     <row r="194" ht="12" customHeight="1" s="1">
       <c r="A194" s="0" t="n">
-        <v>4000006</v>
+        <v>3000004</v>
       </c>
       <c r="B194" s="0" t="n">
-        <v>4000006</v>
+        <v>3000004</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="D194" s="0" t="inlineStr">
         <is>
-          <t>Achievement-进度</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="195" ht="12" customHeight="1" s="1">
       <c r="A195" s="0" t="n">
-        <v>4000008</v>
+        <v>3000005</v>
       </c>
       <c r="B195" s="0" t="n">
-        <v>4000008</v>
+        <v>3000005</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
-          <t>领取成功！</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="D195" s="0" t="inlineStr">
@@ -4561,32 +4561,32 @@
     </row>
     <row r="196" ht="12" customHeight="1" s="1">
       <c r="A196" s="0" t="n">
-        <v>4000010</v>
+        <v>4000006</v>
       </c>
       <c r="B196" s="0" t="n">
-        <v>4000010</v>
+        <v>4000006</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t>游玩时间</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="D196" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Achievement-进度</t>
         </is>
       </c>
     </row>
     <row r="197" ht="12" customHeight="1" s="1">
       <c r="A197" s="0" t="n">
-        <v>4000011</v>
+        <v>4000008</v>
       </c>
       <c r="B197" s="0" t="n">
-        <v>4000011</v>
+        <v>4000008</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t>总击杀数</t>
+          <t>领取成功！</t>
         </is>
       </c>
       <c r="D197" s="0" t="inlineStr">
@@ -4597,14 +4597,14 @@
     </row>
     <row r="198" ht="12" customHeight="1" s="1">
       <c r="A198" s="0" t="n">
-        <v>4000012</v>
+        <v>4000010</v>
       </c>
       <c r="B198" s="0" t="n">
-        <v>4000012</v>
+        <v>4000010</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t>征服通关</t>
+          <t>游玩时间</t>
         </is>
       </c>
       <c r="D198" s="0" t="inlineStr">
@@ -4615,14 +4615,14 @@
     </row>
     <row r="199" ht="12" customHeight="1" s="1">
       <c r="A199" s="0" t="n">
-        <v>4000013</v>
+        <v>4000011</v>
       </c>
       <c r="B199" s="0" t="n">
-        <v>4000013</v>
+        <v>4000011</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
-          <t>难度{0}</t>
+          <t>总击杀数</t>
         </is>
       </c>
       <c r="D199" s="0" t="inlineStr">
@@ -4633,14 +4633,14 @@
     </row>
     <row r="200" ht="12" customHeight="1" s="1">
       <c r="A200" s="0" t="n">
-        <v>4000014</v>
+        <v>4000012</v>
       </c>
       <c r="B200" s="0" t="n">
-        <v>4000014</v>
+        <v>4000012</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>征服通关</t>
         </is>
       </c>
       <c r="D200" s="0" t="inlineStr">
@@ -4651,14 +4651,14 @@
     </row>
     <row r="201" ht="12" customHeight="1" s="1">
       <c r="A201" s="0" t="n">
-        <v>4000015</v>
+        <v>4000013</v>
       </c>
       <c r="B201" s="0" t="n">
-        <v>4000015</v>
+        <v>4000013</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
-          <t>总通关次数</t>
+          <t>难度{0}</t>
         </is>
       </c>
       <c r="D201" s="0" t="inlineStr">
@@ -4669,42 +4669,76 @@
     </row>
     <row r="202" ht="12" customHeight="1" s="1">
       <c r="A202" s="0" t="n">
-        <v>4000016</v>
+        <v>4000014</v>
       </c>
       <c r="B202" s="0" t="n">
-        <v>4000016</v>
+        <v>4000014</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}/{1}</t>
+          <t>{0}时{1}分</t>
         </is>
       </c>
       <c r="D202" s="0" t="inlineStr">
         <is>
-          <t>Achievement-等级</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="203" ht="12" customHeight="1" s="1">
       <c r="A203" s="0" t="n">
+        <v>4000015</v>
+      </c>
+      <c r="B203" s="0" t="n">
+        <v>4000015</v>
+      </c>
+      <c r="C203" s="0" t="inlineStr">
+        <is>
+          <t>总通关次数</t>
+        </is>
+      </c>
+      <c r="D203" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="12" customHeight="1" s="1">
+      <c r="A204" s="0" t="n">
+        <v>4000016</v>
+      </c>
+      <c r="B204" s="0" t="n">
+        <v>4000016</v>
+      </c>
+      <c r="C204" s="0" t="inlineStr">
+        <is>
+          <t>Lv.{0}/{1}</t>
+        </is>
+      </c>
+      <c r="D204" s="0" t="inlineStr">
+        <is>
+          <t>Achievement-等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="12" customHeight="1" s="1">
+      <c r="A205" s="0" t="n">
         <v>4000017</v>
       </c>
-      <c r="B203" s="0" t="n">
+      <c r="B205" s="0" t="n">
         <v>4000017</v>
       </c>
-      <c r="C203" s="0" t="inlineStr">
+      <c r="C205" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="D203" s="0" t="inlineStr">
+      <c r="D205" s="0" t="inlineStr">
         <is>
           <t>Achievement-已完成</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="12" customHeight="1" s="1"/>
-    <row r="205" ht="12" customHeight="1" s="1"/>
     <row r="206" ht="12" customHeight="1" s="1"/>
     <row r="207" ht="12" customHeight="1" s="1"/>
     <row r="208" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="UIText" sheetId="1" state="visible" r:id="rId1"/>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D205"/>
+  <dimension ref="A1:D207"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.375" customWidth="1" style="1" min="1" max="1"/>
@@ -1888,18 +1888,18 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" s="0" t="n">
         <v>2007</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" s="0" t="n">
         <v>2007</v>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>刷新次数已用完</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="0" t="inlineStr">
         <is>
           <t>|</t>
         </is>
@@ -3429,6 +3429,11 @@
           <t>献祭成功，等级提升！</t>
         </is>
       </c>
+      <c r="D132" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
@@ -3442,6 +3447,11 @@
           <t>献祭失败，祭品已消耗</t>
         </is>
       </c>
+      <c r="D133" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
@@ -4739,7 +4749,24 @@
         </is>
       </c>
     </row>
-    <row r="206" ht="12" customHeight="1" s="1"/>
+    <row r="206" ht="12" customHeight="1" s="1">
+      <c r="A206" t="n">
+        <v>4000018</v>
+      </c>
+      <c r="B206" t="n">
+        <v>4000018</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>刷新x{0}</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>深渊馈赠-刷新</t>
+        </is>
+      </c>
+    </row>
     <row r="207" ht="12" customHeight="1" s="1"/>
     <row r="208" ht="12" customHeight="1" s="1"/>
     <row r="209" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D207"/>
+  <dimension ref="A1:D208"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.375" customWidth="1" style="1" min="1" max="1"/>
@@ -3113,68 +3113,68 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>54001</v>
+        <v>53015</v>
       </c>
       <c r="B115" s="0" t="n">
-        <v>54001</v>
+        <v>53015</v>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>没有数据</t>
+          <t>议案:</t>
         </is>
       </c>
       <c r="D115" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>标题</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>55001</v>
+        <v>54001</v>
       </c>
       <c r="B116" s="0" t="n">
-        <v>55001</v>
+        <v>54001</v>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t>魔王讨伐者正在靠近中...</t>
+          <t>没有数据</t>
         </is>
       </c>
       <c r="D116" s="0" t="inlineStr">
         <is>
-          <t>战斗Boss展示</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>55002</v>
+        <v>55001</v>
       </c>
       <c r="B117" s="0" t="n">
-        <v>55002</v>
+        <v>55001</v>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
-          <t>一大波勇者正在靠近中…</t>
+          <t>魔王讨伐者正在靠近中...</t>
         </is>
       </c>
       <c r="D117" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>战斗Boss展示</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>55003</v>
+        <v>55002</v>
       </c>
       <c r="B118" s="0" t="n">
-        <v>55003</v>
+        <v>55002</v>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t>注意！英雄队伍正在涌来…</t>
+          <t>一大波勇者正在靠近中…</t>
         </is>
       </c>
       <c r="D118" s="0" t="inlineStr">
@@ -3185,14 +3185,14 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>55004</v>
+        <v>55003</v>
       </c>
       <c r="B119" s="0" t="n">
-        <v>55004</v>
+        <v>55003</v>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>侦测到讨伐部队正在接近…</t>
+          <t>注意！英雄队伍正在涌来…</t>
         </is>
       </c>
       <c r="D119" s="0" t="inlineStr">
@@ -3203,14 +3203,14 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>55005</v>
+        <v>55004</v>
       </c>
       <c r="B120" s="0" t="n">
-        <v>55005</v>
+        <v>55004</v>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>勇者联军正在逼近…</t>
+          <t>侦测到讨伐部队正在接近…</t>
         </is>
       </c>
       <c r="D120" s="0" t="inlineStr">
@@ -3221,14 +3221,14 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>55006</v>
+        <v>55005</v>
       </c>
       <c r="B121" s="0" t="n">
-        <v>55006</v>
+        <v>55005</v>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>一大波自称勇者的家伙来了…</t>
+          <t>勇者联军正在逼近…</t>
         </is>
       </c>
       <c r="D121" s="0" t="inlineStr">
@@ -3239,14 +3239,14 @@
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>55007</v>
+        <v>55006</v>
       </c>
       <c r="B122" s="0" t="n">
-        <v>55007</v>
+        <v>55006</v>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>警报：正义的伙伴们正在靠近…</t>
+          <t>一大波自称勇者的家伙来了…</t>
         </is>
       </c>
       <c r="D122" s="0" t="inlineStr">
@@ -3257,50 +3257,50 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>60000</v>
+        <v>55007</v>
       </c>
       <c r="B123" s="0" t="n">
-        <v>60000</v>
+        <v>55007</v>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>献祭升级</t>
+          <t>警报：正义的伙伴们正在靠近…</t>
         </is>
       </c>
       <c r="D123" s="0" t="inlineStr">
         <is>
-          <t>生物献祭</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>60001</v>
+        <v>60000</v>
       </c>
       <c r="B124" s="0" t="n">
-        <v>60001</v>
+        <v>60000</v>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>开始献祭</t>
+          <t>献祭升级</t>
         </is>
       </c>
       <c r="D124" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物献祭</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>60002</v>
+        <v>60001</v>
       </c>
       <c r="B125" s="0" t="n">
-        <v>60002</v>
+        <v>60001</v>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>成功率</t>
+          <t>开始献祭</t>
         </is>
       </c>
       <c r="D125" s="0" t="inlineStr">
@@ -3311,14 +3311,14 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>61001</v>
+        <v>60002</v>
       </c>
       <c r="B126" s="0" t="n">
-        <v>61001</v>
+        <v>60002</v>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>还未选择献祭生物！</t>
+          <t>成功率</t>
         </is>
       </c>
       <c r="D126" s="0" t="inlineStr">
@@ -3329,14 +3329,14 @@
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>61002</v>
+        <v>61001</v>
       </c>
       <c r="B127" s="0" t="n">
-        <v>61002</v>
+        <v>61001</v>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>献祭生物数量达到上限！</t>
+          <t>还未选择献祭生物！</t>
         </is>
       </c>
       <c r="D127" s="0" t="inlineStr">
@@ -3347,14 +3347,14 @@
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>61003</v>
+        <v>61002</v>
       </c>
       <c r="B128" s="0" t="n">
-        <v>61003</v>
+        <v>61002</v>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>是否开始献祭？当前成功率{0}</t>
+          <t>献祭生物数量达到上限！</t>
         </is>
       </c>
       <c r="D128" s="0" t="inlineStr">
@@ -3365,14 +3365,14 @@
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>61004</v>
+        <v>61003</v>
       </c>
       <c r="B129" s="0" t="n">
-        <v>61004</v>
+        <v>61003</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>请分配完所有属性点</t>
+          <t>是否开始献祭？当前成功率{0}</t>
         </is>
       </c>
       <c r="D129" s="0" t="inlineStr">
@@ -3383,14 +3383,14 @@
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>61005</v>
+        <v>61004</v>
       </c>
       <c r="B130" s="0" t="n">
-        <v>61005</v>
+        <v>61004</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>剩余点数:{0}</t>
+          <t>请分配完所有属性点</t>
         </is>
       </c>
       <c r="D130" s="0" t="inlineStr">
@@ -3401,14 +3401,14 @@
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>61006</v>
+        <v>61005</v>
       </c>
       <c r="B131" s="0" t="n">
-        <v>61006</v>
+        <v>61005</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>确认按当前方案分配属性点吗？确认后将无法更改。</t>
+          <t>剩余点数:{0}</t>
         </is>
       </c>
       <c r="D131" s="0" t="inlineStr">
@@ -3419,14 +3419,14 @@
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>61007</v>
+        <v>61006</v>
       </c>
       <c r="B132" s="0" t="n">
-        <v>61007</v>
+        <v>61006</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t>献祭成功，等级提升！</t>
+          <t>确认按当前方案分配属性点吗？确认后将无法更改。</t>
         </is>
       </c>
       <c r="D132" s="0" t="inlineStr">
@@ -3437,14 +3437,14 @@
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>61008</v>
+        <v>61007</v>
       </c>
       <c r="B133" s="0" t="n">
-        <v>61008</v>
+        <v>61007</v>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t>献祭失败，祭品已消耗</t>
+          <t>献祭成功，等级提升！</t>
         </is>
       </c>
       <c r="D133" s="0" t="inlineStr">
@@ -3455,50 +3455,50 @@
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>62001</v>
+        <v>61008</v>
       </c>
       <c r="B134" s="0" t="n">
-        <v>62001</v>
+        <v>61008</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t>是否开启此项研究？花费x{0}魔晶</t>
+          <t>献祭失败，祭品已消耗</t>
         </is>
       </c>
       <c r="D134" s="0" t="inlineStr">
         <is>
-          <t>生物研究</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>62002</v>
+        <v>62001</v>
       </c>
       <c r="B135" s="0" t="n">
-        <v>62002</v>
+        <v>62001</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t>设施</t>
+          <t>是否开启此项研究？花费x{0}魔晶</t>
         </is>
       </c>
       <c r="D135" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物研究</t>
         </is>
       </c>
     </row>
     <row r="136" ht="12" customHeight="1" s="1">
       <c r="A136" s="0" t="n">
-        <v>62003</v>
+        <v>62002</v>
       </c>
       <c r="B136" s="0" t="n">
-        <v>62003</v>
+        <v>62002</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t>强化</t>
+          <t>设施</t>
         </is>
       </c>
       <c r="D136" s="0" t="inlineStr">
@@ -3509,14 +3509,14 @@
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>62004</v>
+        <v>62003</v>
       </c>
       <c r="B137" s="0" t="n">
-        <v>62004</v>
+        <v>62003</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t>魔物</t>
+          <t>强化</t>
         </is>
       </c>
       <c r="D137" s="0" t="inlineStr">
@@ -3527,50 +3527,50 @@
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>63001</v>
+        <v>62004</v>
       </c>
       <c r="B138" s="0" t="n">
-        <v>63001</v>
+        <v>62004</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t>选择转生魔王外观</t>
+          <t>魔物</t>
         </is>
       </c>
       <c r="D138" s="0" t="inlineStr">
         <is>
-          <t>生物外貌修改</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>63002</v>
+        <v>63001</v>
       </c>
       <c r="B139" s="0" t="n">
-        <v>63002</v>
+        <v>63001</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>选择转生魔王外观</t>
         </is>
       </c>
       <c r="D139" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物外貌修改</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>63003</v>
+        <v>63002</v>
       </c>
       <c r="B140" s="0" t="n">
-        <v>63003</v>
+        <v>63002</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t>是否以此外观完成转生？</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D140" s="0" t="inlineStr">
@@ -3581,122 +3581,122 @@
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>64001</v>
+        <v>63003</v>
       </c>
       <c r="B141" s="0" t="n">
-        <v>64001</v>
+        <v>63003</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>是否以此外观完成转生？</t>
         </is>
       </c>
       <c r="D141" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>64002</v>
+        <v>64001</v>
       </c>
       <c r="B142" s="0" t="n">
-        <v>64002</v>
+        <v>64001</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t>统计</t>
+          <t>成就</t>
         </is>
       </c>
       <c r="D142" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>成就</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>65001</v>
+        <v>64002</v>
       </c>
       <c r="B143" s="0" t="n">
-        <v>65001</v>
+        <v>64002</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="D143" s="0" t="inlineStr">
         <is>
-          <t>生物属性添加</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>70001</v>
+        <v>65001</v>
       </c>
       <c r="B144" s="0" t="n">
-        <v>70001</v>
+        <v>65001</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t>贿赂</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D144" s="0" t="inlineStr">
         <is>
-          <t>对话</t>
+          <t>生物属性添加</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>80001</v>
+        <v>70001</v>
       </c>
       <c r="B145" s="0" t="n">
-        <v>80001</v>
+        <v>70001</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t>开始进阶</t>
+          <t>贿赂</t>
         </is>
       </c>
       <c r="D145" s="0" t="inlineStr">
         <is>
-          <t>生物进阶</t>
+          <t>对话</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>80002</v>
+        <v>80001</v>
       </c>
       <c r="B146" s="0" t="n">
-        <v>80002</v>
+        <v>80001</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>结束进阶</t>
+          <t>开始进阶</t>
         </is>
       </c>
       <c r="D146" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物进阶</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>80003</v>
+        <v>80002</v>
       </c>
       <c r="B147" s="0" t="n">
-        <v>80003</v>
+        <v>80002</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t>完成进阶</t>
+          <t>结束进阶</t>
         </is>
       </c>
       <c r="D147" s="0" t="inlineStr">
@@ -3707,14 +3707,14 @@
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>80004</v>
+        <v>80003</v>
       </c>
       <c r="B148" s="0" t="n">
-        <v>80004</v>
+        <v>80003</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t>是否结束进阶？进阶消耗的材料不会返回</t>
+          <t>完成进阶</t>
         </is>
       </c>
       <c r="D148" s="0" t="inlineStr">
@@ -3725,14 +3725,14 @@
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>80005</v>
+        <v>80004</v>
       </c>
       <c r="B149" s="0" t="n">
-        <v>80005</v>
+        <v>80004</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>进度</t>
+          <t>是否结束进阶？进阶消耗的材料不会返回</t>
         </is>
       </c>
       <c r="D149" s="0" t="inlineStr">
@@ -3743,14 +3743,14 @@
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>80006</v>
+        <v>80005</v>
       </c>
       <c r="B150" s="0" t="n">
-        <v>80006</v>
+        <v>80005</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t>选择进阶魔物</t>
+          <t>进度</t>
         </is>
       </c>
       <c r="D150" s="0" t="inlineStr">
@@ -3761,14 +3761,14 @@
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>80007</v>
+        <v>80006</v>
       </c>
       <c r="B151" s="0" t="n">
-        <v>80007</v>
+        <v>80006</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>选择辅助魔物</t>
+          <t>选择进阶魔物</t>
         </is>
       </c>
       <c r="D151" s="0" t="inlineStr">
@@ -3779,14 +3779,14 @@
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>80008</v>
+        <v>80007</v>
       </c>
       <c r="B152" s="0" t="n">
-        <v>80008</v>
+        <v>80007</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物</t>
+          <t>选择辅助魔物</t>
         </is>
       </c>
       <c r="D152" s="0" t="inlineStr">
@@ -3797,14 +3797,14 @@
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>80009</v>
+        <v>80008</v>
       </c>
       <c r="B153" s="0" t="n">
-        <v>80009</v>
+        <v>80008</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t>加速进阶 x{0}</t>
+          <t>还未选择魔物</t>
         </is>
       </c>
       <c r="D153" s="0" t="inlineStr">
@@ -3815,14 +3815,14 @@
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>80010</v>
+        <v>80009</v>
       </c>
       <c r="B154" s="0" t="n">
-        <v>80010</v>
+        <v>80009</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
+          <t>加速进阶 x{0}</t>
         </is>
       </c>
       <c r="D154" s="0" t="inlineStr">
@@ -3833,35 +3833,35 @@
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>90001</v>
+        <v>80010</v>
       </c>
       <c r="B155" s="0" t="n">
-        <v>90001</v>
+        <v>80010</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
         </is>
       </c>
       <c r="D155" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="156" ht="12" customHeight="1" s="1">
-      <c r="A156" s="0" t="n">
-        <v>90002</v>
-      </c>
-      <c r="B156" s="0" t="n">
-        <v>90002</v>
-      </c>
-      <c r="C156" s="0" t="inlineStr">
-        <is>
-          <t>魔王专属</t>
-        </is>
-      </c>
-      <c r="D156" s="0" t="inlineStr">
+      <c r="A156" t="n">
+        <v>80013</v>
+      </c>
+      <c r="B156" t="n">
+        <v>80013</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>进阶成功，稀有度提升！</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
         <is>
           <t>|</t>
         </is>
@@ -3869,32 +3869,32 @@
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>1000001</v>
+        <v>90001</v>
       </c>
       <c r="B157" s="0" t="n">
-        <v>1000001</v>
+        <v>90001</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D157" s="0" t="inlineStr">
         <is>
-          <t>弹窗</t>
+          <t>通用</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>1000002</v>
+        <v>90002</v>
       </c>
       <c r="B158" s="0" t="n">
-        <v>1000002</v>
+        <v>90002</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>魔王专属</t>
         </is>
       </c>
       <c r="D158" s="0" t="inlineStr">
@@ -3905,86 +3905,86 @@
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>1001001</v>
+        <v>1000001</v>
       </c>
       <c r="B159" s="0" t="n">
-        <v>1001001</v>
+        <v>1000001</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t>等级.{0}</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D159" s="0" t="inlineStr">
         <is>
-          <t>弹窗-卡片详情</t>
+          <t>弹窗</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>1002001</v>
+        <v>1000002</v>
       </c>
       <c r="B160" s="0" t="n">
-        <v>1002001</v>
+        <v>1000002</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>赠送</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="D160" s="0" t="inlineStr">
         <is>
-          <t>弹窗-道具选择</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>1002002</v>
+        <v>1001001</v>
       </c>
       <c r="B161" s="0" t="n">
-        <v>1002002</v>
+        <v>1001001</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>等级.{0}</t>
         </is>
       </c>
       <c r="D161" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-卡片详情</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>1003001</v>
+        <v>1002001</v>
       </c>
       <c r="B162" s="0" t="n">
-        <v>1003001</v>
+        <v>1002001</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>研究等级.{0}</t>
+          <t>赠送</t>
         </is>
       </c>
       <c r="D162" s="0" t="inlineStr">
         <is>
-          <t>弹窗-研究详情</t>
+          <t>弹窗-道具选择</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>1003002</v>
+        <v>1002002</v>
       </c>
       <c r="B163" s="0" t="n">
-        <v>1003002</v>
+        <v>1002002</v>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>研究等级.最大</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="D163" s="0" t="inlineStr">
@@ -3995,32 +3995,32 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>1004001</v>
+        <v>1003001</v>
       </c>
       <c r="B164" s="0" t="n">
-        <v>1004001</v>
+        <v>1003001</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>取个新名字</t>
+          <t>研究等级.{0}</t>
         </is>
       </c>
       <c r="D164" s="0" t="inlineStr">
         <is>
-          <t>弹窗-重命名</t>
+          <t>弹窗-研究详情</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>1004002</v>
+        <v>1003002</v>
       </c>
       <c r="B165" s="0" t="n">
-        <v>1004002</v>
+        <v>1003002</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>输入名字...</t>
+          <t>研究等级.最大</t>
         </is>
       </c>
       <c r="D165" s="0" t="inlineStr">
@@ -4031,32 +4031,32 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>1005001</v>
+        <v>1004001</v>
       </c>
       <c r="B166" s="0" t="n">
-        <v>1005001</v>
+        <v>1004001</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>选择魔物</t>
+          <t>取个新名字</t>
         </is>
       </c>
       <c r="D166" s="0" t="inlineStr">
         <is>
-          <t>弹窗-生物选择</t>
+          <t>弹窗-重命名</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>1005002</v>
+        <v>1004002</v>
       </c>
       <c r="B167" s="0" t="n">
-        <v>1005002</v>
+        <v>1004002</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>当前选择数量{0}/{1}</t>
+          <t>输入名字...</t>
         </is>
       </c>
       <c r="D167" s="0" t="inlineStr">
@@ -4067,50 +4067,50 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>1005003</v>
+        <v>1005001</v>
       </c>
       <c r="B168" s="0" t="n">
-        <v>1005003</v>
+        <v>1005001</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>超过选择数量上限</t>
+          <t>选择魔物</t>
         </is>
       </c>
       <c r="D168" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-生物选择</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>2000001</v>
+        <v>1005002</v>
       </c>
       <c r="B169" s="0" t="n">
-        <v>2000001</v>
+        <v>1005002</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>提示</t>
+          <t>当前选择数量{0}/{1}</t>
         </is>
       </c>
       <c r="D169" s="0" t="inlineStr">
         <is>
-          <t>popup</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>2000002</v>
+        <v>1005003</v>
       </c>
       <c r="B170" s="0" t="n">
-        <v>2000002</v>
+        <v>1005003</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>魔晶</t>
+          <t>超过选择数量上限</t>
         </is>
       </c>
       <c r="D170" s="0" t="inlineStr">
@@ -4121,32 +4121,32 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>2000003</v>
+        <v>2000001</v>
       </c>
       <c r="B171" s="0" t="n">
-        <v>2000003</v>
+        <v>2000001</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>声望</t>
+          <t>提示</t>
         </is>
       </c>
       <c r="D171" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>popup</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>2000004</v>
+        <v>2000002</v>
       </c>
       <c r="B172" s="0" t="n">
-        <v>2000004</v>
+        <v>2000002</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>排序：稀有度</t>
+          <t>魔晶</t>
         </is>
       </c>
       <c r="D172" s="0" t="inlineStr">
@@ -4157,14 +4157,14 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>2000005</v>
+        <v>2000003</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>2000005</v>
+        <v>2000003</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>排序：等级</t>
+          <t>声望</t>
         </is>
       </c>
       <c r="D173" s="0" t="inlineStr">
@@ -4175,14 +4175,14 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="B174" s="0" t="n">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>阵容</t>
+          <t>排序：稀有度</t>
         </is>
       </c>
       <c r="D174" s="0" t="inlineStr">
@@ -4193,14 +4193,14 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>2000007</v>
+        <v>2000005</v>
       </c>
       <c r="B175" s="0" t="n">
-        <v>2000007</v>
+        <v>2000005</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>排序：名字</t>
+          <t>排序：等级</t>
         </is>
       </c>
       <c r="D175" s="0" t="inlineStr">
@@ -4211,14 +4211,14 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>2000008</v>
+        <v>2000006</v>
       </c>
       <c r="B176" s="0" t="n">
-        <v>2000008</v>
+        <v>2000006</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>稀有度:{0}</t>
+          <t>阵容</t>
         </is>
       </c>
       <c r="D176" s="0" t="inlineStr">
@@ -4229,14 +4229,14 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>2000009</v>
+        <v>2000007</v>
       </c>
       <c r="B177" s="0" t="n">
-        <v>2000009</v>
+        <v>2000007</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>所属:{0}</t>
+          <t>排序：名字</t>
         </is>
       </c>
       <c r="D177" s="0" t="inlineStr">
@@ -4247,14 +4247,14 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>2000010</v>
+        <v>2000008</v>
       </c>
       <c r="B178" s="0" t="n">
-        <v>2000010</v>
+        <v>2000008</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t>道具名字:{0}</t>
+          <t>稀有度:{0}</t>
         </is>
       </c>
       <c r="D178" s="0" t="inlineStr">
@@ -4265,14 +4265,14 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>2000011</v>
+        <v>2000009</v>
       </c>
       <c r="B179" s="0" t="n">
-        <v>2000011</v>
+        <v>2000009</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t>同类</t>
+          <t>所属:{0}</t>
         </is>
       </c>
       <c r="D179" s="0" t="inlineStr">
@@ -4283,14 +4283,14 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>2000014</v>
+        <v>2000010</v>
       </c>
       <c r="B180" s="0" t="n">
-        <v>2000014</v>
+        <v>2000010</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t>筛选排序</t>
+          <t>道具名字:{0}</t>
         </is>
       </c>
       <c r="D180" s="0" t="inlineStr">
@@ -4301,14 +4301,14 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>2000015</v>
+        <v>2000011</v>
       </c>
       <c r="B181" s="0" t="n">
-        <v>2000015</v>
+        <v>2000011</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t>没有相关道具</t>
+          <t>同类</t>
         </is>
       </c>
       <c r="D181" s="0" t="inlineStr">
@@ -4319,14 +4319,14 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>2000016</v>
+        <v>2000014</v>
       </c>
       <c r="B182" s="0" t="n">
-        <v>2000016</v>
+        <v>2000014</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t>没有相关魔物</t>
+          <t>筛选排序</t>
         </is>
       </c>
       <c r="D182" s="0" t="inlineStr">
@@ -4337,14 +4337,14 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
-        <v>2000017</v>
+        <v>2000015</v>
       </c>
       <c r="B183" s="0" t="n">
-        <v>2000017</v>
+        <v>2000015</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
-          <t>没有可孕育的生物</t>
+          <t>没有相关道具</t>
         </is>
       </c>
       <c r="D183" s="0" t="inlineStr">
@@ -4355,14 +4355,14 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="n">
-        <v>2000018</v>
+        <v>2000016</v>
       </c>
       <c r="B184" s="0" t="n">
-        <v>2000018</v>
+        <v>2000016</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t>稀有度</t>
+          <t>没有相关魔物</t>
         </is>
       </c>
       <c r="D184" s="0" t="inlineStr">
@@ -4373,14 +4373,14 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="n">
-        <v>2000019</v>
+        <v>2000017</v>
       </c>
       <c r="B185" s="0" t="n">
-        <v>2000019</v>
+        <v>2000017</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t>名字</t>
+          <t>没有可孕育的生物</t>
         </is>
       </c>
       <c r="D185" s="0" t="inlineStr">
@@ -4391,14 +4391,14 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="n">
-        <v>2000020</v>
+        <v>2000018</v>
       </c>
       <c r="B186" s="0" t="n">
-        <v>2000020</v>
+        <v>2000018</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t>等级</t>
+          <t>稀有度</t>
         </is>
       </c>
       <c r="D186" s="0" t="inlineStr">
@@ -4409,14 +4409,14 @@
     </row>
     <row r="187">
       <c r="A187" s="0" t="n">
-        <v>2000021</v>
+        <v>2000019</v>
       </c>
       <c r="B187" s="0" t="n">
-        <v>2000021</v>
+        <v>2000019</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
-          <t>战斗</t>
+          <t>名字</t>
         </is>
       </c>
       <c r="D187" s="0" t="inlineStr">
@@ -4427,14 +4427,14 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="n">
-        <v>2000022</v>
+        <v>2000020</v>
       </c>
       <c r="B188" s="0" t="n">
-        <v>2000022</v>
+        <v>2000020</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t>其它</t>
+          <t>等级</t>
         </is>
       </c>
       <c r="D188" s="0" t="inlineStr">
@@ -4445,14 +4445,14 @@
     </row>
     <row r="189">
       <c r="A189" s="0" t="n">
-        <v>2000023</v>
+        <v>2000021</v>
       </c>
       <c r="B189" s="0" t="n">
-        <v>2000023</v>
+        <v>2000021</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
-          <t>低等级...</t>
+          <t>战斗</t>
         </is>
       </c>
       <c r="D189" s="0" t="inlineStr">
@@ -4463,14 +4463,14 @@
     </row>
     <row r="190" ht="12" customHeight="1" s="1">
       <c r="A190" s="0" t="n">
-        <v>2000024</v>
+        <v>2000022</v>
       </c>
       <c r="B190" s="0" t="n">
-        <v>2000024</v>
+        <v>2000022</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
-          <t>高等级...</t>
+          <t>其它</t>
         </is>
       </c>
       <c r="D190" s="0" t="inlineStr">
@@ -4481,32 +4481,32 @@
     </row>
     <row r="191" ht="12" customHeight="1" s="1">
       <c r="A191" s="0" t="n">
-        <v>3000001</v>
+        <v>2000023</v>
       </c>
       <c r="B191" s="0" t="n">
-        <v>3000001</v>
+        <v>2000023</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
-          <t>没有足够的魔晶</t>
+          <t>低等级...</t>
         </is>
       </c>
       <c r="D191" s="0" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="192" ht="12" customHeight="1" s="1">
       <c r="A192" s="0" t="n">
-        <v>3000002</v>
+        <v>2000024</v>
       </c>
       <c r="B192" s="0" t="n">
-        <v>3000002</v>
+        <v>2000024</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
+          <t>高等级...</t>
         </is>
       </c>
       <c r="D192" s="0" t="inlineStr">
@@ -4517,32 +4517,32 @@
     </row>
     <row r="193" ht="12" customHeight="1" s="1">
       <c r="A193" s="0" t="n">
-        <v>3000003</v>
+        <v>3000001</v>
       </c>
       <c r="B193" s="0" t="n">
-        <v>3000003</v>
+        <v>3000001</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t>修改名字成功！</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="D193" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="194" ht="12" customHeight="1" s="1">
       <c r="A194" s="0" t="n">
-        <v>3000004</v>
+        <v>3000002</v>
       </c>
       <c r="B194" s="0" t="n">
-        <v>3000004</v>
+        <v>3000002</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物！</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="D194" s="0" t="inlineStr">
@@ -4553,14 +4553,14 @@
     </row>
     <row r="195" ht="12" customHeight="1" s="1">
       <c r="A195" s="0" t="n">
-        <v>3000005</v>
+        <v>3000003</v>
       </c>
       <c r="B195" s="0" t="n">
-        <v>3000005</v>
+        <v>3000003</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
-          <t>转生成功！</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="D195" s="0" t="inlineStr">
@@ -4571,32 +4571,32 @@
     </row>
     <row r="196" ht="12" customHeight="1" s="1">
       <c r="A196" s="0" t="n">
-        <v>4000006</v>
+        <v>3000004</v>
       </c>
       <c r="B196" s="0" t="n">
-        <v>4000006</v>
+        <v>3000004</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="D196" s="0" t="inlineStr">
         <is>
-          <t>Achievement-进度</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="197" ht="12" customHeight="1" s="1">
       <c r="A197" s="0" t="n">
-        <v>4000008</v>
+        <v>3000005</v>
       </c>
       <c r="B197" s="0" t="n">
-        <v>4000008</v>
+        <v>3000005</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t>领取成功！</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="D197" s="0" t="inlineStr">
@@ -4607,32 +4607,32 @@
     </row>
     <row r="198" ht="12" customHeight="1" s="1">
       <c r="A198" s="0" t="n">
-        <v>4000010</v>
+        <v>4000006</v>
       </c>
       <c r="B198" s="0" t="n">
-        <v>4000010</v>
+        <v>4000006</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t>游玩时间</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="D198" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Achievement-进度</t>
         </is>
       </c>
     </row>
     <row r="199" ht="12" customHeight="1" s="1">
       <c r="A199" s="0" t="n">
-        <v>4000011</v>
+        <v>4000008</v>
       </c>
       <c r="B199" s="0" t="n">
-        <v>4000011</v>
+        <v>4000008</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
-          <t>总击杀数</t>
+          <t>领取成功！</t>
         </is>
       </c>
       <c r="D199" s="0" t="inlineStr">
@@ -4643,14 +4643,14 @@
     </row>
     <row r="200" ht="12" customHeight="1" s="1">
       <c r="A200" s="0" t="n">
-        <v>4000012</v>
+        <v>4000010</v>
       </c>
       <c r="B200" s="0" t="n">
-        <v>4000012</v>
+        <v>4000010</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t>征服通关</t>
+          <t>游玩时间</t>
         </is>
       </c>
       <c r="D200" s="0" t="inlineStr">
@@ -4661,14 +4661,14 @@
     </row>
     <row r="201" ht="12" customHeight="1" s="1">
       <c r="A201" s="0" t="n">
-        <v>4000013</v>
+        <v>4000011</v>
       </c>
       <c r="B201" s="0" t="n">
-        <v>4000013</v>
+        <v>4000011</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
-          <t>难度{0}</t>
+          <t>总击杀数</t>
         </is>
       </c>
       <c r="D201" s="0" t="inlineStr">
@@ -4679,14 +4679,14 @@
     </row>
     <row r="202" ht="12" customHeight="1" s="1">
       <c r="A202" s="0" t="n">
-        <v>4000014</v>
+        <v>4000012</v>
       </c>
       <c r="B202" s="0" t="n">
-        <v>4000014</v>
+        <v>4000012</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>征服通关</t>
         </is>
       </c>
       <c r="D202" s="0" t="inlineStr">
@@ -4697,14 +4697,14 @@
     </row>
     <row r="203" ht="12" customHeight="1" s="1">
       <c r="A203" s="0" t="n">
-        <v>4000015</v>
+        <v>4000013</v>
       </c>
       <c r="B203" s="0" t="n">
-        <v>4000015</v>
+        <v>4000013</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
-          <t>总通关次数</t>
+          <t>难度{0}</t>
         </is>
       </c>
       <c r="D203" s="0" t="inlineStr">
@@ -4715,60 +4715,94 @@
     </row>
     <row r="204" ht="12" customHeight="1" s="1">
       <c r="A204" s="0" t="n">
-        <v>4000016</v>
+        <v>4000014</v>
       </c>
       <c r="B204" s="0" t="n">
-        <v>4000016</v>
+        <v>4000014</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}/{1}</t>
+          <t>{0}时{1}分</t>
         </is>
       </c>
       <c r="D204" s="0" t="inlineStr">
         <is>
-          <t>Achievement-等级</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="205" ht="12" customHeight="1" s="1">
       <c r="A205" s="0" t="n">
+        <v>4000015</v>
+      </c>
+      <c r="B205" s="0" t="n">
+        <v>4000015</v>
+      </c>
+      <c r="C205" s="0" t="inlineStr">
+        <is>
+          <t>总通关次数</t>
+        </is>
+      </c>
+      <c r="D205" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="12" customHeight="1" s="1">
+      <c r="A206" s="0" t="n">
+        <v>4000016</v>
+      </c>
+      <c r="B206" s="0" t="n">
+        <v>4000016</v>
+      </c>
+      <c r="C206" s="0" t="inlineStr">
+        <is>
+          <t>Lv.{0}/{1}</t>
+        </is>
+      </c>
+      <c r="D206" s="0" t="inlineStr">
+        <is>
+          <t>Achievement-等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="12" customHeight="1" s="1">
+      <c r="A207" s="0" t="n">
         <v>4000017</v>
       </c>
-      <c r="B205" s="0" t="n">
+      <c r="B207" s="0" t="n">
         <v>4000017</v>
       </c>
-      <c r="C205" s="0" t="inlineStr">
+      <c r="C207" s="0" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="D205" s="0" t="inlineStr">
+      <c r="D207" s="0" t="inlineStr">
         <is>
           <t>Achievement-已完成</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="12" customHeight="1" s="1">
-      <c r="A206" t="n">
+    <row r="208" ht="12" customHeight="1" s="1">
+      <c r="A208" s="0" t="n">
         <v>4000018</v>
       </c>
-      <c r="B206" t="n">
+      <c r="B208" s="0" t="n">
         <v>4000018</v>
       </c>
-      <c r="C206" t="inlineStr">
+      <c r="C208" s="0" t="inlineStr">
         <is>
           <t>刷新x{0}</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="D208" s="0" t="inlineStr">
         <is>
           <t>深渊馈赠-刷新</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="12" customHeight="1" s="1"/>
-    <row r="208" ht="12" customHeight="1" s="1"/>
     <row r="209" ht="12" customHeight="1" s="1"/>
     <row r="210" ht="12" customHeight="1" s="1"/>
     <row r="211" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D208"/>
+  <dimension ref="A1:D209"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.375" customWidth="1" style="1" min="1" max="1"/>
@@ -3472,51 +3472,51 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="0" t="n">
-        <v>62001</v>
-      </c>
-      <c r="B135" s="0" t="n">
-        <v>62001</v>
-      </c>
-      <c r="C135" s="0" t="inlineStr">
-        <is>
-          <t>是否开启此项研究？花费x{0}魔晶</t>
-        </is>
-      </c>
-      <c r="D135" s="0" t="inlineStr">
-        <is>
-          <t>生物研究</t>
+      <c r="A135" t="n">
+        <v>61009</v>
+      </c>
+      <c r="B135" t="n">
+        <v>61009</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>经验值未达到100%</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="136" ht="12" customHeight="1" s="1">
       <c r="A136" s="0" t="n">
-        <v>62002</v>
+        <v>62001</v>
       </c>
       <c r="B136" s="0" t="n">
-        <v>62002</v>
+        <v>62001</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t>设施</t>
+          <t>是否开启此项研究？花费x{0}魔晶</t>
         </is>
       </c>
       <c r="D136" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物研究</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>62003</v>
+        <v>62002</v>
       </c>
       <c r="B137" s="0" t="n">
-        <v>62003</v>
+        <v>62002</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t>强化</t>
+          <t>设施</t>
         </is>
       </c>
       <c r="D137" s="0" t="inlineStr">
@@ -3527,14 +3527,14 @@
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>62004</v>
+        <v>62003</v>
       </c>
       <c r="B138" s="0" t="n">
-        <v>62004</v>
+        <v>62003</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t>魔物</t>
+          <t>强化</t>
         </is>
       </c>
       <c r="D138" s="0" t="inlineStr">
@@ -3545,50 +3545,50 @@
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>63001</v>
+        <v>62004</v>
       </c>
       <c r="B139" s="0" t="n">
-        <v>63001</v>
+        <v>62004</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t>选择转生魔王外观</t>
+          <t>魔物</t>
         </is>
       </c>
       <c r="D139" s="0" t="inlineStr">
         <is>
-          <t>生物外貌修改</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>63002</v>
+        <v>63001</v>
       </c>
       <c r="B140" s="0" t="n">
-        <v>63002</v>
+        <v>63001</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>选择转生魔王外观</t>
         </is>
       </c>
       <c r="D140" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物外貌修改</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>63003</v>
+        <v>63002</v>
       </c>
       <c r="B141" s="0" t="n">
-        <v>63003</v>
+        <v>63002</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t>是否以此外观完成转生？</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D141" s="0" t="inlineStr">
@@ -3599,122 +3599,122 @@
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>64001</v>
+        <v>63003</v>
       </c>
       <c r="B142" s="0" t="n">
-        <v>64001</v>
+        <v>63003</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>是否以此外观完成转生？</t>
         </is>
       </c>
       <c r="D142" s="0" t="inlineStr">
         <is>
-          <t>成就</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>64002</v>
+        <v>64001</v>
       </c>
       <c r="B143" s="0" t="n">
-        <v>64002</v>
+        <v>64001</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t>统计</t>
+          <t>成就</t>
         </is>
       </c>
       <c r="D143" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>成就</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>65001</v>
+        <v>64002</v>
       </c>
       <c r="B144" s="0" t="n">
-        <v>65001</v>
+        <v>64002</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="D144" s="0" t="inlineStr">
         <is>
-          <t>生物属性添加</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>70001</v>
+        <v>65001</v>
       </c>
       <c r="B145" s="0" t="n">
-        <v>70001</v>
+        <v>65001</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t>贿赂</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D145" s="0" t="inlineStr">
         <is>
-          <t>对话</t>
+          <t>生物属性添加</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>80001</v>
+        <v>70001</v>
       </c>
       <c r="B146" s="0" t="n">
-        <v>80001</v>
+        <v>70001</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>开始进阶</t>
+          <t>贿赂</t>
         </is>
       </c>
       <c r="D146" s="0" t="inlineStr">
         <is>
-          <t>生物进阶</t>
+          <t>对话</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>80002</v>
+        <v>80001</v>
       </c>
       <c r="B147" s="0" t="n">
-        <v>80002</v>
+        <v>80001</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t>结束进阶</t>
+          <t>开始进阶</t>
         </is>
       </c>
       <c r="D147" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>生物进阶</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>80003</v>
+        <v>80002</v>
       </c>
       <c r="B148" s="0" t="n">
-        <v>80003</v>
+        <v>80002</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t>完成进阶</t>
+          <t>结束进阶</t>
         </is>
       </c>
       <c r="D148" s="0" t="inlineStr">
@@ -3725,14 +3725,14 @@
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>80004</v>
+        <v>80003</v>
       </c>
       <c r="B149" s="0" t="n">
-        <v>80004</v>
+        <v>80003</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>是否结束进阶？进阶消耗的材料不会返回</t>
+          <t>完成进阶</t>
         </is>
       </c>
       <c r="D149" s="0" t="inlineStr">
@@ -3743,14 +3743,14 @@
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>80005</v>
+        <v>80004</v>
       </c>
       <c r="B150" s="0" t="n">
-        <v>80005</v>
+        <v>80004</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t>进度</t>
+          <t>是否结束进阶？进阶消耗的材料不会返回</t>
         </is>
       </c>
       <c r="D150" s="0" t="inlineStr">
@@ -3761,14 +3761,14 @@
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>80006</v>
+        <v>80005</v>
       </c>
       <c r="B151" s="0" t="n">
-        <v>80006</v>
+        <v>80005</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>选择进阶魔物</t>
+          <t>进度</t>
         </is>
       </c>
       <c r="D151" s="0" t="inlineStr">
@@ -3779,14 +3779,14 @@
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>80007</v>
+        <v>80006</v>
       </c>
       <c r="B152" s="0" t="n">
-        <v>80007</v>
+        <v>80006</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>选择辅助魔物</t>
+          <t>选择进阶魔物</t>
         </is>
       </c>
       <c r="D152" s="0" t="inlineStr">
@@ -3797,14 +3797,14 @@
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>80008</v>
+        <v>80007</v>
       </c>
       <c r="B153" s="0" t="n">
-        <v>80008</v>
+        <v>80007</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物</t>
+          <t>选择辅助魔物</t>
         </is>
       </c>
       <c r="D153" s="0" t="inlineStr">
@@ -3815,14 +3815,14 @@
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>80009</v>
+        <v>80008</v>
       </c>
       <c r="B154" s="0" t="n">
-        <v>80009</v>
+        <v>80008</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>加速进阶 x{0}</t>
+          <t>还未选择魔物</t>
         </is>
       </c>
       <c r="D154" s="0" t="inlineStr">
@@ -3833,35 +3833,35 @@
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
+        <v>80009</v>
+      </c>
+      <c r="B155" s="0" t="n">
+        <v>80009</v>
+      </c>
+      <c r="C155" s="0" t="inlineStr">
+        <is>
+          <t>加速进阶 x{0}</t>
+        </is>
+      </c>
+      <c r="D155" s="0" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="12" customHeight="1" s="1">
+      <c r="A156" s="0" t="n">
         <v>80010</v>
       </c>
-      <c r="B155" s="0" t="n">
+      <c r="B156" s="0" t="n">
         <v>80010</v>
       </c>
-      <c r="C155" s="0" t="inlineStr">
+      <c r="C156" s="0" t="inlineStr">
         <is>
           <t>是否溶解&lt;color=#FF6B6B&gt;{0}&lt;/color&gt;对&lt;color=#4ECDC4&gt;{1}&lt;/color&gt;进行进阶？溶解后的魔物将会消失</t>
         </is>
       </c>
-      <c r="D155" s="0" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="12" customHeight="1" s="1">
-      <c r="A156" t="n">
-        <v>80013</v>
-      </c>
-      <c r="B156" t="n">
-        <v>80013</v>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>进阶成功，稀有度提升！</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
+      <c r="D156" s="0" t="inlineStr">
         <is>
           <t>|</t>
         </is>
@@ -3869,248 +3869,248 @@
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>90001</v>
+        <v>80013</v>
       </c>
       <c r="B157" s="0" t="n">
-        <v>90001</v>
+        <v>80013</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>进阶成功，稀有度提升！</t>
         </is>
       </c>
       <c r="D157" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>90002</v>
+        <v>90001</v>
       </c>
       <c r="B158" s="0" t="n">
-        <v>90002</v>
+        <v>90001</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>魔王专属</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="D158" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>通用</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>1000001</v>
+        <v>90002</v>
       </c>
       <c r="B159" s="0" t="n">
-        <v>1000001</v>
+        <v>90002</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>魔王专属</t>
         </is>
       </c>
       <c r="D159" s="0" t="inlineStr">
         <is>
-          <t>弹窗</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>1000002</v>
+        <v>1000001</v>
       </c>
       <c r="B160" s="0" t="n">
-        <v>1000002</v>
+        <v>1000001</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>确认</t>
         </is>
       </c>
       <c r="D160" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>1001001</v>
+        <v>1000002</v>
       </c>
       <c r="B161" s="0" t="n">
-        <v>1001001</v>
+        <v>1000002</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>等级.{0}</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="D161" s="0" t="inlineStr">
         <is>
-          <t>弹窗-卡片详情</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>1002001</v>
+        <v>1001001</v>
       </c>
       <c r="B162" s="0" t="n">
-        <v>1002001</v>
+        <v>1001001</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>赠送</t>
+          <t>等级.{0}</t>
         </is>
       </c>
       <c r="D162" s="0" t="inlineStr">
         <is>
-          <t>弹窗-道具选择</t>
+          <t>弹窗-卡片详情</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>1002002</v>
+        <v>1002001</v>
       </c>
       <c r="B163" s="0" t="n">
-        <v>1002002</v>
+        <v>1002001</v>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>丢弃</t>
+          <t>赠送</t>
         </is>
       </c>
       <c r="D163" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-道具选择</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>1003001</v>
+        <v>1002002</v>
       </c>
       <c r="B164" s="0" t="n">
-        <v>1003001</v>
+        <v>1002002</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>研究等级.{0}</t>
+          <t>丢弃</t>
         </is>
       </c>
       <c r="D164" s="0" t="inlineStr">
         <is>
-          <t>弹窗-研究详情</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>1003002</v>
+        <v>1003001</v>
       </c>
       <c r="B165" s="0" t="n">
-        <v>1003002</v>
+        <v>1003001</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>研究等级.最大</t>
+          <t>研究等级.{0}</t>
         </is>
       </c>
       <c r="D165" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-研究详情</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>1004001</v>
+        <v>1003002</v>
       </c>
       <c r="B166" s="0" t="n">
-        <v>1004001</v>
+        <v>1003002</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>取个新名字</t>
+          <t>研究等级.最大</t>
         </is>
       </c>
       <c r="D166" s="0" t="inlineStr">
         <is>
-          <t>弹窗-重命名</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>1004002</v>
+        <v>1004001</v>
       </c>
       <c r="B167" s="0" t="n">
-        <v>1004002</v>
+        <v>1004001</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>输入名字...</t>
+          <t>取个新名字</t>
         </is>
       </c>
       <c r="D167" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-重命名</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>1005001</v>
+        <v>1004002</v>
       </c>
       <c r="B168" s="0" t="n">
-        <v>1005001</v>
+        <v>1004002</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>选择魔物</t>
+          <t>输入名字...</t>
         </is>
       </c>
       <c r="D168" s="0" t="inlineStr">
         <is>
-          <t>弹窗-生物选择</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>1005002</v>
+        <v>1005001</v>
       </c>
       <c r="B169" s="0" t="n">
-        <v>1005002</v>
+        <v>1005001</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>当前选择数量{0}/{1}</t>
+          <t>选择魔物</t>
         </is>
       </c>
       <c r="D169" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-生物选择</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>1005003</v>
+        <v>1005002</v>
       </c>
       <c r="B170" s="0" t="n">
-        <v>1005003</v>
+        <v>1005002</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>超过选择数量上限</t>
+          <t>当前选择数量{0}/{1}</t>
         </is>
       </c>
       <c r="D170" s="0" t="inlineStr">
@@ -4121,50 +4121,50 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>2000001</v>
+        <v>1005003</v>
       </c>
       <c r="B171" s="0" t="n">
-        <v>2000001</v>
+        <v>1005003</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>提示</t>
+          <t>超过选择数量上限</t>
         </is>
       </c>
       <c r="D171" s="0" t="inlineStr">
         <is>
-          <t>popup</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>2000002</v>
+        <v>2000001</v>
       </c>
       <c r="B172" s="0" t="n">
-        <v>2000002</v>
+        <v>2000001</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>魔晶</t>
+          <t>提示</t>
         </is>
       </c>
       <c r="D172" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>popup</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>2000003</v>
+        <v>2000002</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>2000003</v>
+        <v>2000002</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>声望</t>
+          <t>魔晶</t>
         </is>
       </c>
       <c r="D173" s="0" t="inlineStr">
@@ -4175,14 +4175,14 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>2000004</v>
+        <v>2000003</v>
       </c>
       <c r="B174" s="0" t="n">
-        <v>2000004</v>
+        <v>2000003</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>排序：稀有度</t>
+          <t>声望</t>
         </is>
       </c>
       <c r="D174" s="0" t="inlineStr">
@@ -4193,14 +4193,14 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>2000005</v>
+        <v>2000004</v>
       </c>
       <c r="B175" s="0" t="n">
-        <v>2000005</v>
+        <v>2000004</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>排序：等级</t>
+          <t>排序：稀有度</t>
         </is>
       </c>
       <c r="D175" s="0" t="inlineStr">
@@ -4211,14 +4211,14 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>2000006</v>
+        <v>2000005</v>
       </c>
       <c r="B176" s="0" t="n">
-        <v>2000006</v>
+        <v>2000005</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>阵容</t>
+          <t>排序：等级</t>
         </is>
       </c>
       <c r="D176" s="0" t="inlineStr">
@@ -4229,14 +4229,14 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>2000007</v>
+        <v>2000006</v>
       </c>
       <c r="B177" s="0" t="n">
-        <v>2000007</v>
+        <v>2000006</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>排序：名字</t>
+          <t>阵容</t>
         </is>
       </c>
       <c r="D177" s="0" t="inlineStr">
@@ -4247,14 +4247,14 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>2000008</v>
+        <v>2000007</v>
       </c>
       <c r="B178" s="0" t="n">
-        <v>2000008</v>
+        <v>2000007</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t>稀有度:{0}</t>
+          <t>排序：名字</t>
         </is>
       </c>
       <c r="D178" s="0" t="inlineStr">
@@ -4265,14 +4265,14 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>2000009</v>
+        <v>2000008</v>
       </c>
       <c r="B179" s="0" t="n">
-        <v>2000009</v>
+        <v>2000008</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t>所属:{0}</t>
+          <t>稀有度:{0}</t>
         </is>
       </c>
       <c r="D179" s="0" t="inlineStr">
@@ -4283,14 +4283,14 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>2000010</v>
+        <v>2000009</v>
       </c>
       <c r="B180" s="0" t="n">
-        <v>2000010</v>
+        <v>2000009</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t>道具名字:{0}</t>
+          <t>所属:{0}</t>
         </is>
       </c>
       <c r="D180" s="0" t="inlineStr">
@@ -4301,14 +4301,14 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>2000011</v>
+        <v>2000010</v>
       </c>
       <c r="B181" s="0" t="n">
-        <v>2000011</v>
+        <v>2000010</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t>同类</t>
+          <t>道具名字:{0}</t>
         </is>
       </c>
       <c r="D181" s="0" t="inlineStr">
@@ -4319,14 +4319,14 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>2000014</v>
+        <v>2000011</v>
       </c>
       <c r="B182" s="0" t="n">
-        <v>2000014</v>
+        <v>2000011</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t>筛选排序</t>
+          <t>同类</t>
         </is>
       </c>
       <c r="D182" s="0" t="inlineStr">
@@ -4337,14 +4337,14 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
-        <v>2000015</v>
+        <v>2000014</v>
       </c>
       <c r="B183" s="0" t="n">
-        <v>2000015</v>
+        <v>2000014</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
-          <t>没有相关道具</t>
+          <t>筛选排序</t>
         </is>
       </c>
       <c r="D183" s="0" t="inlineStr">
@@ -4355,14 +4355,14 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="n">
-        <v>2000016</v>
+        <v>2000015</v>
       </c>
       <c r="B184" s="0" t="n">
-        <v>2000016</v>
+        <v>2000015</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t>没有相关魔物</t>
+          <t>没有相关道具</t>
         </is>
       </c>
       <c r="D184" s="0" t="inlineStr">
@@ -4373,14 +4373,14 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="n">
-        <v>2000017</v>
+        <v>2000016</v>
       </c>
       <c r="B185" s="0" t="n">
-        <v>2000017</v>
+        <v>2000016</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t>没有可孕育的生物</t>
+          <t>没有相关魔物</t>
         </is>
       </c>
       <c r="D185" s="0" t="inlineStr">
@@ -4391,14 +4391,14 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="n">
-        <v>2000018</v>
+        <v>2000017</v>
       </c>
       <c r="B186" s="0" t="n">
-        <v>2000018</v>
+        <v>2000017</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t>稀有度</t>
+          <t>没有可孕育的生物</t>
         </is>
       </c>
       <c r="D186" s="0" t="inlineStr">
@@ -4409,14 +4409,14 @@
     </row>
     <row r="187">
       <c r="A187" s="0" t="n">
-        <v>2000019</v>
+        <v>2000018</v>
       </c>
       <c r="B187" s="0" t="n">
-        <v>2000019</v>
+        <v>2000018</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
-          <t>名字</t>
+          <t>稀有度</t>
         </is>
       </c>
       <c r="D187" s="0" t="inlineStr">
@@ -4427,14 +4427,14 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="n">
-        <v>2000020</v>
+        <v>2000019</v>
       </c>
       <c r="B188" s="0" t="n">
-        <v>2000020</v>
+        <v>2000019</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t>等级</t>
+          <t>名字</t>
         </is>
       </c>
       <c r="D188" s="0" t="inlineStr">
@@ -4445,14 +4445,14 @@
     </row>
     <row r="189">
       <c r="A189" s="0" t="n">
-        <v>2000021</v>
+        <v>2000020</v>
       </c>
       <c r="B189" s="0" t="n">
-        <v>2000021</v>
+        <v>2000020</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
-          <t>战斗</t>
+          <t>等级</t>
         </is>
       </c>
       <c r="D189" s="0" t="inlineStr">
@@ -4463,14 +4463,14 @@
     </row>
     <row r="190" ht="12" customHeight="1" s="1">
       <c r="A190" s="0" t="n">
-        <v>2000022</v>
+        <v>2000021</v>
       </c>
       <c r="B190" s="0" t="n">
-        <v>2000022</v>
+        <v>2000021</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
-          <t>其它</t>
+          <t>战斗</t>
         </is>
       </c>
       <c r="D190" s="0" t="inlineStr">
@@ -4481,14 +4481,14 @@
     </row>
     <row r="191" ht="12" customHeight="1" s="1">
       <c r="A191" s="0" t="n">
-        <v>2000023</v>
+        <v>2000022</v>
       </c>
       <c r="B191" s="0" t="n">
-        <v>2000023</v>
+        <v>2000022</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
-          <t>低等级...</t>
+          <t>其它</t>
         </is>
       </c>
       <c r="D191" s="0" t="inlineStr">
@@ -4499,14 +4499,14 @@
     </row>
     <row r="192" ht="12" customHeight="1" s="1">
       <c r="A192" s="0" t="n">
-        <v>2000024</v>
+        <v>2000023</v>
       </c>
       <c r="B192" s="0" t="n">
-        <v>2000024</v>
+        <v>2000023</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
-          <t>高等级...</t>
+          <t>低等级...</t>
         </is>
       </c>
       <c r="D192" s="0" t="inlineStr">
@@ -4517,50 +4517,50 @@
     </row>
     <row r="193" ht="12" customHeight="1" s="1">
       <c r="A193" s="0" t="n">
-        <v>3000001</v>
+        <v>2000024</v>
       </c>
       <c r="B193" s="0" t="n">
-        <v>3000001</v>
+        <v>2000024</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t>没有足够的魔晶</t>
+          <t>高等级...</t>
         </is>
       </c>
       <c r="D193" s="0" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="194" ht="12" customHeight="1" s="1">
       <c r="A194" s="0" t="n">
-        <v>3000002</v>
+        <v>3000001</v>
       </c>
       <c r="B194" s="0" t="n">
-        <v>3000002</v>
+        <v>3000001</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="D194" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="195" ht="12" customHeight="1" s="1">
       <c r="A195" s="0" t="n">
-        <v>3000003</v>
+        <v>3000002</v>
       </c>
       <c r="B195" s="0" t="n">
-        <v>3000003</v>
+        <v>3000002</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
-          <t>修改名字成功！</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="D195" s="0" t="inlineStr">
@@ -4571,14 +4571,14 @@
     </row>
     <row r="196" ht="12" customHeight="1" s="1">
       <c r="A196" s="0" t="n">
-        <v>3000004</v>
+        <v>3000003</v>
       </c>
       <c r="B196" s="0" t="n">
-        <v>3000004</v>
+        <v>3000003</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物！</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="D196" s="0" t="inlineStr">
@@ -4589,14 +4589,14 @@
     </row>
     <row r="197" ht="12" customHeight="1" s="1">
       <c r="A197" s="0" t="n">
-        <v>3000005</v>
+        <v>3000004</v>
       </c>
       <c r="B197" s="0" t="n">
-        <v>3000005</v>
+        <v>3000004</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t>转生成功！</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="D197" s="0" t="inlineStr">
@@ -4607,50 +4607,50 @@
     </row>
     <row r="198" ht="12" customHeight="1" s="1">
       <c r="A198" s="0" t="n">
-        <v>4000006</v>
+        <v>3000005</v>
       </c>
       <c r="B198" s="0" t="n">
-        <v>4000006</v>
+        <v>3000005</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="D198" s="0" t="inlineStr">
         <is>
-          <t>Achievement-进度</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="199" ht="12" customHeight="1" s="1">
       <c r="A199" s="0" t="n">
-        <v>4000008</v>
+        <v>4000006</v>
       </c>
       <c r="B199" s="0" t="n">
-        <v>4000008</v>
+        <v>4000006</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
-          <t>领取成功！</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="D199" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Achievement-进度</t>
         </is>
       </c>
     </row>
     <row r="200" ht="12" customHeight="1" s="1">
       <c r="A200" s="0" t="n">
-        <v>4000010</v>
+        <v>4000008</v>
       </c>
       <c r="B200" s="0" t="n">
-        <v>4000010</v>
+        <v>4000008</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t>游玩时间</t>
+          <t>领取成功！</t>
         </is>
       </c>
       <c r="D200" s="0" t="inlineStr">
@@ -4661,14 +4661,14 @@
     </row>
     <row r="201" ht="12" customHeight="1" s="1">
       <c r="A201" s="0" t="n">
-        <v>4000011</v>
+        <v>4000010</v>
       </c>
       <c r="B201" s="0" t="n">
-        <v>4000011</v>
+        <v>4000010</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
-          <t>总击杀数</t>
+          <t>游玩时间</t>
         </is>
       </c>
       <c r="D201" s="0" t="inlineStr">
@@ -4679,14 +4679,14 @@
     </row>
     <row r="202" ht="12" customHeight="1" s="1">
       <c r="A202" s="0" t="n">
-        <v>4000012</v>
+        <v>4000011</v>
       </c>
       <c r="B202" s="0" t="n">
-        <v>4000012</v>
+        <v>4000011</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
-          <t>征服通关</t>
+          <t>总击杀数</t>
         </is>
       </c>
       <c r="D202" s="0" t="inlineStr">
@@ -4697,14 +4697,14 @@
     </row>
     <row r="203" ht="12" customHeight="1" s="1">
       <c r="A203" s="0" t="n">
-        <v>4000013</v>
+        <v>4000012</v>
       </c>
       <c r="B203" s="0" t="n">
-        <v>4000013</v>
+        <v>4000012</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
-          <t>难度{0}</t>
+          <t>征服通关</t>
         </is>
       </c>
       <c r="D203" s="0" t="inlineStr">
@@ -4715,14 +4715,14 @@
     </row>
     <row r="204" ht="12" customHeight="1" s="1">
       <c r="A204" s="0" t="n">
-        <v>4000014</v>
+        <v>4000013</v>
       </c>
       <c r="B204" s="0" t="n">
-        <v>4000014</v>
+        <v>4000013</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>难度{0}</t>
         </is>
       </c>
       <c r="D204" s="0" t="inlineStr">
@@ -4733,14 +4733,14 @@
     </row>
     <row r="205" ht="12" customHeight="1" s="1">
       <c r="A205" s="0" t="n">
-        <v>4000015</v>
+        <v>4000014</v>
       </c>
       <c r="B205" s="0" t="n">
-        <v>4000015</v>
+        <v>4000014</v>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
-          <t>总通关次数</t>
+          <t>{0}时{1}分</t>
         </is>
       </c>
       <c r="D205" s="0" t="inlineStr">
@@ -4751,59 +4751,76 @@
     </row>
     <row r="206" ht="12" customHeight="1" s="1">
       <c r="A206" s="0" t="n">
-        <v>4000016</v>
+        <v>4000015</v>
       </c>
       <c r="B206" s="0" t="n">
-        <v>4000016</v>
+        <v>4000015</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}/{1}</t>
+          <t>总通关次数</t>
         </is>
       </c>
       <c r="D206" s="0" t="inlineStr">
         <is>
-          <t>Achievement-等级</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="207" ht="12" customHeight="1" s="1">
       <c r="A207" s="0" t="n">
-        <v>4000017</v>
+        <v>4000016</v>
       </c>
       <c r="B207" s="0" t="n">
-        <v>4000017</v>
+        <v>4000016</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>Lv.{0}/{1}</t>
         </is>
       </c>
       <c r="D207" s="0" t="inlineStr">
         <is>
-          <t>Achievement-已完成</t>
+          <t>Achievement-等级</t>
         </is>
       </c>
     </row>
     <row r="208" ht="12" customHeight="1" s="1">
       <c r="A208" s="0" t="n">
+        <v>4000017</v>
+      </c>
+      <c r="B208" s="0" t="n">
+        <v>4000017</v>
+      </c>
+      <c r="C208" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D208" s="0" t="inlineStr">
+        <is>
+          <t>Achievement-已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="12" customHeight="1" s="1">
+      <c r="A209" s="0" t="n">
         <v>4000018</v>
       </c>
-      <c r="B208" s="0" t="n">
+      <c r="B209" s="0" t="n">
         <v>4000018</v>
       </c>
-      <c r="C208" s="0" t="inlineStr">
+      <c r="C209" s="0" t="inlineStr">
         <is>
           <t>刷新x{0}</t>
         </is>
       </c>
-      <c r="D208" s="0" t="inlineStr">
+      <c r="D209" s="0" t="inlineStr">
         <is>
           <t>深渊馈赠-刷新</t>
         </is>
       </c>
     </row>
-    <row r="209" ht="12" customHeight="1" s="1"/>
     <row r="210" ht="12" customHeight="1" s="1"/>
     <row r="211" ht="12" customHeight="1" s="1"/>
     <row r="212" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D214"/>
+  <dimension ref="A1:D215"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.375" customWidth="1" style="1" min="1" max="1"/>
@@ -3544,18 +3544,18 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="n">
+      <c r="A139" s="0" t="n">
         <v>61013</v>
       </c>
-      <c r="B139" t="n">
+      <c r="B139" s="0" t="n">
         <v>61013</v>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C139" s="0" t="inlineStr">
         <is>
           <t>选择榨汁魔物</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D139" s="0" t="inlineStr">
         <is>
           <t>|</t>
         </is>
@@ -4911,7 +4911,24 @@
         </is>
       </c>
     </row>
-    <row r="215" ht="12" customHeight="1" s="1"/>
+    <row r="215" ht="12" customHeight="1" s="1">
+      <c r="A215" t="n">
+        <v>4000020</v>
+      </c>
+      <c r="B215" t="n">
+        <v>4000020</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>随机生成一条该稀有度增益</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>魔物进阶-随机增益兜底</t>
+        </is>
+      </c>
+    </row>
     <row r="216" ht="12" customHeight="1" s="1"/>
     <row r="217" ht="12" customHeight="1" s="1"/>
     <row r="218" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_ui_text[UI文本_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D215"/>
+  <dimension ref="A1:D217"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.375" customWidth="1" style="1" min="1" max="1"/>
@@ -4102,69 +4102,69 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="0" t="n">
-        <v>1003001</v>
-      </c>
-      <c r="B170" s="0" t="n">
-        <v>1003001</v>
-      </c>
-      <c r="C170" s="0" t="inlineStr">
-        <is>
-          <t>研究等级.{0}</t>
-        </is>
-      </c>
-      <c r="D170" s="0" t="inlineStr">
-        <is>
-          <t>弹窗-研究详情</t>
+      <c r="A170" t="n">
+        <v>1002003</v>
+      </c>
+      <c r="B170" t="n">
+        <v>1002003</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>装备</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>弹窗-道具选择</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="0" t="n">
-        <v>1003002</v>
-      </c>
-      <c r="B171" s="0" t="n">
-        <v>1003002</v>
-      </c>
-      <c r="C171" s="0" t="inlineStr">
-        <is>
-          <t>研究等级.最大</t>
-        </is>
-      </c>
-      <c r="D171" s="0" t="inlineStr">
-        <is>
-          <t>|</t>
+      <c r="A171" t="n">
+        <v>1002004</v>
+      </c>
+      <c r="B171" t="n">
+        <v>1002004</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>是否要丢弃该道具？</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>弹窗-道具选择</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>1004001</v>
+        <v>1003001</v>
       </c>
       <c r="B172" s="0" t="n">
-        <v>1004001</v>
+        <v>1003001</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>取个新名字</t>
+          <t>研究等级.{0}</t>
         </is>
       </c>
       <c r="D172" s="0" t="inlineStr">
         <is>
-          <t>弹窗-重命名</t>
+          <t>弹窗-研究详情</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>1004002</v>
+        <v>1003002</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>1004002</v>
+        <v>1003002</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>输入名字...</t>
+          <t>研究等级.最大</t>
         </is>
       </c>
       <c r="D173" s="0" t="inlineStr">
@@ -4175,32 +4175,32 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>1005001</v>
+        <v>1004001</v>
       </c>
       <c r="B174" s="0" t="n">
-        <v>1005001</v>
+        <v>1004001</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>选择魔物</t>
+          <t>取个新名字</t>
         </is>
       </c>
       <c r="D174" s="0" t="inlineStr">
         <is>
-          <t>弹窗-生物选择</t>
+          <t>弹窗-重命名</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>1005002</v>
+        <v>1004002</v>
       </c>
       <c r="B175" s="0" t="n">
-        <v>1005002</v>
+        <v>1004002</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>当前选择数量{0}/{1}</t>
+          <t>输入名字...</t>
         </is>
       </c>
       <c r="D175" s="0" t="inlineStr">
@@ -4211,50 +4211,50 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>1005003</v>
+        <v>1005001</v>
       </c>
       <c r="B176" s="0" t="n">
-        <v>1005003</v>
+        <v>1005001</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>超过选择数量上限</t>
+          <t>选择魔物</t>
         </is>
       </c>
       <c r="D176" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>弹窗-生物选择</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>2000001</v>
+        <v>1005002</v>
       </c>
       <c r="B177" s="0" t="n">
-        <v>2000001</v>
+        <v>1005002</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>提示</t>
+          <t>当前选择数量{0}/{1}</t>
         </is>
       </c>
       <c r="D177" s="0" t="inlineStr">
         <is>
-          <t>popup</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>2000002</v>
+        <v>1005003</v>
       </c>
       <c r="B178" s="0" t="n">
-        <v>2000002</v>
+        <v>1005003</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t>魔晶</t>
+          <t>超过选择数量上限</t>
         </is>
       </c>
       <c r="D178" s="0" t="inlineStr">
@@ -4265,32 +4265,32 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>2000003</v>
+        <v>2000001</v>
       </c>
       <c r="B179" s="0" t="n">
-        <v>2000003</v>
+        <v>2000001</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t>声望</t>
+          <t>提示</t>
         </is>
       </c>
       <c r="D179" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>popup</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>2000004</v>
+        <v>2000002</v>
       </c>
       <c r="B180" s="0" t="n">
-        <v>2000004</v>
+        <v>2000002</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t>排序：稀有度</t>
+          <t>魔晶</t>
         </is>
       </c>
       <c r="D180" s="0" t="inlineStr">
@@ -4301,14 +4301,14 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>2000005</v>
+        <v>2000003</v>
       </c>
       <c r="B181" s="0" t="n">
-        <v>2000005</v>
+        <v>2000003</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t>排序：等级</t>
+          <t>声望</t>
         </is>
       </c>
       <c r="D181" s="0" t="inlineStr">
@@ -4319,14 +4319,14 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="B182" s="0" t="n">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t>阵容</t>
+          <t>排序：稀有度</t>
         </is>
       </c>
       <c r="D182" s="0" t="inlineStr">
@@ -4337,14 +4337,14 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
-        <v>2000007</v>
+        <v>2000005</v>
       </c>
       <c r="B183" s="0" t="n">
-        <v>2000007</v>
+        <v>2000005</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
-          <t>排序：名字</t>
+          <t>排序：等级</t>
         </is>
       </c>
       <c r="D183" s="0" t="inlineStr">
@@ -4355,14 +4355,14 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="n">
-        <v>2000008</v>
+        <v>2000006</v>
       </c>
       <c r="B184" s="0" t="n">
-        <v>2000008</v>
+        <v>2000006</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t>稀有度:{0}</t>
+          <t>阵容</t>
         </is>
       </c>
       <c r="D184" s="0" t="inlineStr">
@@ -4373,14 +4373,14 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="n">
-        <v>2000009</v>
+        <v>2000007</v>
       </c>
       <c r="B185" s="0" t="n">
-        <v>2000009</v>
+        <v>2000007</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t>所属:{0}</t>
+          <t>排序：名字</t>
         </is>
       </c>
       <c r="D185" s="0" t="inlineStr">
@@ -4391,14 +4391,14 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="n">
-        <v>2000010</v>
+        <v>2000008</v>
       </c>
       <c r="B186" s="0" t="n">
-        <v>2000010</v>
+        <v>2000008</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t>道具名字:{0}</t>
+          <t>稀有度:{0}</t>
         </is>
       </c>
       <c r="D186" s="0" t="inlineStr">
@@ -4409,14 +4409,14 @@
     </row>
     <row r="187">
       <c r="A187" s="0" t="n">
-        <v>2000011</v>
+        <v>2000009</v>
       </c>
       <c r="B187" s="0" t="n">
-        <v>2000011</v>
+        <v>2000009</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
-          <t>同类</t>
+          <t>所属:{0}</t>
         </is>
       </c>
       <c r="D187" s="0" t="inlineStr">
@@ -4427,14 +4427,14 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="n">
-        <v>2000014</v>
+        <v>2000010</v>
       </c>
       <c r="B188" s="0" t="n">
-        <v>2000014</v>
+        <v>2000010</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t>筛选排序</t>
+          <t>道具名字:{0}</t>
         </is>
       </c>
       <c r="D188" s="0" t="inlineStr">
@@ -4445,14 +4445,14 @@
     </row>
     <row r="189">
       <c r="A189" s="0" t="n">
-        <v>2000015</v>
+        <v>2000011</v>
       </c>
       <c r="B189" s="0" t="n">
-        <v>2000015</v>
+        <v>2000011</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
-          <t>没有相关道具</t>
+          <t>同类</t>
         </is>
       </c>
       <c r="D189" s="0" t="inlineStr">
@@ -4463,14 +4463,14 @@
     </row>
     <row r="190">
       <c r="A190" s="0" t="n">
-        <v>2000016</v>
+        <v>2000014</v>
       </c>
       <c r="B190" s="0" t="n">
-        <v>2000016</v>
+        <v>2000014</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
-          <t>没有相关魔物</t>
+          <t>筛选排序</t>
         </is>
       </c>
       <c r="D190" s="0" t="inlineStr">
@@ -4481,14 +4481,14 @@
     </row>
     <row r="191">
       <c r="A191" s="0" t="n">
-        <v>2000017</v>
+        <v>2000015</v>
       </c>
       <c r="B191" s="0" t="n">
-        <v>2000017</v>
+        <v>2000015</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
-          <t>没有可孕育的生物</t>
+          <t>没有相关道具</t>
         </is>
       </c>
       <c r="D191" s="0" t="inlineStr">
@@ -4499,14 +4499,14 @@
     </row>
     <row r="192" ht="12" customHeight="1" s="1">
       <c r="A192" s="0" t="n">
-        <v>2000018</v>
+        <v>2000016</v>
       </c>
       <c r="B192" s="0" t="n">
-        <v>2000018</v>
+        <v>2000016</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
-          <t>稀有度</t>
+          <t>没有相关魔物</t>
         </is>
       </c>
       <c r="D192" s="0" t="inlineStr">
@@ -4517,14 +4517,14 @@
     </row>
     <row r="193" ht="12" customHeight="1" s="1">
       <c r="A193" s="0" t="n">
-        <v>2000019</v>
+        <v>2000017</v>
       </c>
       <c r="B193" s="0" t="n">
-        <v>2000019</v>
+        <v>2000017</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t>名字</t>
+          <t>没有可孕育的生物</t>
         </is>
       </c>
       <c r="D193" s="0" t="inlineStr">
@@ -4535,14 +4535,14 @@
     </row>
     <row r="194" ht="12" customHeight="1" s="1">
       <c r="A194" s="0" t="n">
-        <v>2000020</v>
+        <v>2000018</v>
       </c>
       <c r="B194" s="0" t="n">
-        <v>2000020</v>
+        <v>2000018</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
-          <t>等级</t>
+          <t>稀有度</t>
         </is>
       </c>
       <c r="D194" s="0" t="inlineStr">
@@ -4553,14 +4553,14 @@
     </row>
     <row r="195" ht="12" customHeight="1" s="1">
       <c r="A195" s="0" t="n">
-        <v>2000021</v>
+        <v>2000019</v>
       </c>
       <c r="B195" s="0" t="n">
-        <v>2000021</v>
+        <v>2000019</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
-          <t>战斗</t>
+          <t>名字</t>
         </is>
       </c>
       <c r="D195" s="0" t="inlineStr">
@@ -4571,14 +4571,14 @@
     </row>
     <row r="196" ht="12" customHeight="1" s="1">
       <c r="A196" s="0" t="n">
-        <v>2000022</v>
+        <v>2000020</v>
       </c>
       <c r="B196" s="0" t="n">
-        <v>2000022</v>
+        <v>2000020</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t>其它</t>
+          <t>等级</t>
         </is>
       </c>
       <c r="D196" s="0" t="inlineStr">
@@ -4589,14 +4589,14 @@
     </row>
     <row r="197" ht="12" customHeight="1" s="1">
       <c r="A197" s="0" t="n">
-        <v>2000023</v>
+        <v>2000021</v>
       </c>
       <c r="B197" s="0" t="n">
-        <v>2000023</v>
+        <v>2000021</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t>低等级...</t>
+          <t>战斗</t>
         </is>
       </c>
       <c r="D197" s="0" t="inlineStr">
@@ -4607,14 +4607,14 @@
     </row>
     <row r="198" ht="12" customHeight="1" s="1">
       <c r="A198" s="0" t="n">
-        <v>2000024</v>
+        <v>2000022</v>
       </c>
       <c r="B198" s="0" t="n">
-        <v>2000024</v>
+        <v>2000022</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t>高等级...</t>
+          <t>其它</t>
         </is>
       </c>
       <c r="D198" s="0" t="inlineStr">
@@ -4625,32 +4625,32 @@
     </row>
     <row r="199" ht="12" customHeight="1" s="1">
       <c r="A199" s="0" t="n">
-        <v>3000001</v>
+        <v>2000023</v>
       </c>
       <c r="B199" s="0" t="n">
-        <v>3000001</v>
+        <v>2000023</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
-          <t>没有足够的魔晶</t>
+          <t>低等级...</t>
         </is>
       </c>
       <c r="D199" s="0" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="200" ht="12" customHeight="1" s="1">
       <c r="A200" s="0" t="n">
-        <v>3000002</v>
+        <v>2000024</v>
       </c>
       <c r="B200" s="0" t="n">
-        <v>3000002</v>
+        <v>2000024</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t>没有足够的声望</t>
+          <t>高等级...</t>
         </is>
       </c>
       <c r="D200" s="0" t="inlineStr">
@@ -4661,32 +4661,32 @@
     </row>
     <row r="201" ht="12" customHeight="1" s="1">
       <c r="A201" s="0" t="n">
-        <v>3000003</v>
+        <v>3000001</v>
       </c>
       <c r="B201" s="0" t="n">
-        <v>3000003</v>
+        <v>3000001</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
-          <t>修改名字成功！</t>
+          <t>没有足够的魔晶</t>
         </is>
       </c>
       <c r="D201" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="202" ht="12" customHeight="1" s="1">
       <c r="A202" s="0" t="n">
-        <v>3000004</v>
+        <v>3000002</v>
       </c>
       <c r="B202" s="0" t="n">
-        <v>3000004</v>
+        <v>3000002</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
-          <t>还未选择魔物！</t>
+          <t>没有足够的声望</t>
         </is>
       </c>
       <c r="D202" s="0" t="inlineStr">
@@ -4697,14 +4697,14 @@
     </row>
     <row r="203" ht="12" customHeight="1" s="1">
       <c r="A203" s="0" t="n">
-        <v>3000005</v>
+        <v>3000003</v>
       </c>
       <c r="B203" s="0" t="n">
-        <v>3000005</v>
+        <v>3000003</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
-          <t>转生成功！</t>
+          <t>修改名字成功！</t>
         </is>
       </c>
       <c r="D203" s="0" t="inlineStr">
@@ -4715,32 +4715,32 @@
     </row>
     <row r="204" ht="12" customHeight="1" s="1">
       <c r="A204" s="0" t="n">
-        <v>4000006</v>
+        <v>3000004</v>
       </c>
       <c r="B204" s="0" t="n">
-        <v>4000006</v>
+        <v>3000004</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
-          <t>{0}/{1}</t>
+          <t>还未选择魔物！</t>
         </is>
       </c>
       <c r="D204" s="0" t="inlineStr">
         <is>
-          <t>Achievement-进度</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="205" ht="12" customHeight="1" s="1">
       <c r="A205" s="0" t="n">
-        <v>4000008</v>
+        <v>3000005</v>
       </c>
       <c r="B205" s="0" t="n">
-        <v>4000008</v>
+        <v>3000005</v>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
-          <t>领取成功！</t>
+          <t>转生成功！</t>
         </is>
       </c>
       <c r="D205" s="0" t="inlineStr">
@@ -4751,32 +4751,32 @@
     </row>
     <row r="206" ht="12" customHeight="1" s="1">
       <c r="A206" s="0" t="n">
-        <v>4000010</v>
+        <v>4000006</v>
       </c>
       <c r="B206" s="0" t="n">
-        <v>4000010</v>
+        <v>4000006</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
-          <t>游玩时间</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
       <c r="D206" s="0" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>Achievement-进度</t>
         </is>
       </c>
     </row>
     <row r="207" ht="12" customHeight="1" s="1">
       <c r="A207" s="0" t="n">
-        <v>4000011</v>
+        <v>4000008</v>
       </c>
       <c r="B207" s="0" t="n">
-        <v>4000011</v>
+        <v>4000008</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
-          <t>总击杀数</t>
+          <t>领取成功！</t>
         </is>
       </c>
       <c r="D207" s="0" t="inlineStr">
@@ -4787,14 +4787,14 @@
     </row>
     <row r="208" ht="12" customHeight="1" s="1">
       <c r="A208" s="0" t="n">
-        <v>4000012</v>
+        <v>4000010</v>
       </c>
       <c r="B208" s="0" t="n">
-        <v>4000012</v>
+        <v>4000010</v>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
-          <t>征服通关</t>
+          <t>游玩时间</t>
         </is>
       </c>
       <c r="D208" s="0" t="inlineStr">
@@ -4805,14 +4805,14 @@
     </row>
     <row r="209" ht="12" customHeight="1" s="1">
       <c r="A209" s="0" t="n">
-        <v>4000013</v>
+        <v>4000011</v>
       </c>
       <c r="B209" s="0" t="n">
-        <v>4000013</v>
+        <v>4000011</v>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
-          <t>难度{0}</t>
+          <t>总击杀数</t>
         </is>
       </c>
       <c r="D209" s="0" t="inlineStr">
@@ -4823,14 +4823,14 @@
     </row>
     <row r="210" ht="12" customHeight="1" s="1">
       <c r="A210" s="0" t="n">
-        <v>4000014</v>
+        <v>4000012</v>
       </c>
       <c r="B210" s="0" t="n">
-        <v>4000014</v>
+        <v>4000012</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
-          <t>{0}时{1}分</t>
+          <t>征服通关</t>
         </is>
       </c>
       <c r="D210" s="0" t="inlineStr">
@@ -4841,14 +4841,14 @@
     </row>
     <row r="211" ht="12" customHeight="1" s="1">
       <c r="A211" s="0" t="n">
-        <v>4000015</v>
+        <v>4000013</v>
       </c>
       <c r="B211" s="0" t="n">
-        <v>4000015</v>
+        <v>4000013</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
-          <t>总通关次数</t>
+          <t>难度{0}</t>
         </is>
       </c>
       <c r="D211" s="0" t="inlineStr">
@@ -4859,78 +4859,112 @@
     </row>
     <row r="212" ht="12" customHeight="1" s="1">
       <c r="A212" s="0" t="n">
-        <v>4000016</v>
+        <v>4000014</v>
       </c>
       <c r="B212" s="0" t="n">
-        <v>4000016</v>
+        <v>4000014</v>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
-          <t>Lv.{0}/{1}</t>
+          <t>{0}时{1}分</t>
         </is>
       </c>
       <c r="D212" s="0" t="inlineStr">
         <is>
-          <t>Achievement-等级</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="213" ht="12" customHeight="1" s="1">
       <c r="A213" s="0" t="n">
-        <v>4000017</v>
+        <v>4000015</v>
       </c>
       <c r="B213" s="0" t="n">
-        <v>4000017</v>
+        <v>4000015</v>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>总通关次数</t>
         </is>
       </c>
       <c r="D213" s="0" t="inlineStr">
         <is>
-          <t>Achievement-已完成</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="214" ht="12" customHeight="1" s="1">
       <c r="A214" s="0" t="n">
+        <v>4000016</v>
+      </c>
+      <c r="B214" s="0" t="n">
+        <v>4000016</v>
+      </c>
+      <c r="C214" s="0" t="inlineStr">
+        <is>
+          <t>Lv.{0}/{1}</t>
+        </is>
+      </c>
+      <c r="D214" s="0" t="inlineStr">
+        <is>
+          <t>Achievement-等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="12" customHeight="1" s="1">
+      <c r="A215" s="0" t="n">
+        <v>4000017</v>
+      </c>
+      <c r="B215" s="0" t="n">
+        <v>4000017</v>
+      </c>
+      <c r="C215" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D215" s="0" t="inlineStr">
+        <is>
+          <t>Achievement-已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="12" customHeight="1" s="1">
+      <c r="A216" s="0" t="n">
         <v>4000018</v>
       </c>
-      <c r="B214" s="0" t="n">
+      <c r="B216" s="0" t="n">
         <v>4000018</v>
       </c>
-      <c r="C214" s="0" t="inlineStr">
+      <c r="C216" s="0" t="inlineStr">
         <is>
           <t>刷新x{0}</t>
         </is>
       </c>
-      <c r="D214" s="0" t="inlineStr">
+      <c r="D216" s="0" t="inlineStr">
         <is>
           <t>深渊馈赠-刷新</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="12" customHeight="1" s="1">
-      <c r="A215" t="n">
+    <row r="217" ht="12" customHeight="1" s="1">
+      <c r="A217" s="0" t="n">
         <v>4000020</v>
       </c>
-      <c r="B215" t="n">
+      <c r="B217" s="0" t="n">
         <v>4000020</v>
       </c>
-      <c r="C215" t="inlineStr">
+      <c r="C217" s="0" t="inlineStr">
         <is>
           <t>随机生成一条该稀有度增益</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
+      <c r="D217" s="0" t="inlineStr">
         <is>
           <t>魔物进阶-随机增益兜底</t>
         </is>
       </c>
     </row>
-    <row r="216" ht="12" customHeight="1" s="1"/>
-    <row r="217" ht="12" customHeight="1" s="1"/>
     <row r="218" ht="12" customHeight="1" s="1"/>
     <row r="219" ht="12" customHeight="1" s="1"/>
     <row r="220" ht="12" customHeight="1" s="1"/>
